--- a/output/北塩原村_サービス見込量.xlsx
+++ b/output/北塩原村_サービス見込量.xlsx
@@ -18,6 +18,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_供給制約" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_地域生活支援事業" sheetId="10" state="visible" r:id="rId10"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_村確認事項" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_告示別表第一根拠" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12_別表第五判定" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -230,6 +232,9 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -301,9 +306,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -672,7 +674,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -993,57 +995,111 @@
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="9" t="inlineStr">
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>11_告示別表第一根拠</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>サービス別に告示が勘案を求める要素</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>全体の前提</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>確定</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>令和8年3月31日告示第4号 別表第一と本ブックの積上げ項目の対照表</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="30" customHeight="1">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>12_別表第五判定</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>地域差是正規定の適用判定</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>算定方法の前提</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="inlineStr">
+        <is>
+          <t>村確認待ち</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>本村の過疎区分が確定するまで算定方法は確定しない</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="10" t="inlineStr">
         <is>
           <t>作業の順序</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>1. 村から年齢別・サービス別の匿名利用者一覧を受領し、02_年齢到達者一覧を作成します。</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>2. 令和9〜11年度に18歳・40歳・65歳へ到達する方を抽出し、到達年度と現在の利用サービスを記入します。</t>
         </is>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>3. 65歳到達者は06_65歳移行判定で個別に移行可否を判定します。一律に減算してはいけません。</t>
+          <t>1. 村から年齢別・サービス別の匿名利用者一覧を受領し、02_年齢到達者一覧を作成します。</t>
         </is>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>4. 判定結果を03・04の該当する増減行に転記します。継続利用者と利用者数は数式のため触りません。</t>
+          <t>2. 令和9〜11年度に18歳・40歳・65歳へ到達する方を抽出し、到達年度と現在の利用サービスを記入します。</t>
         </is>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>5. 圏域事業所へ利用可能性を照会し、08_供給制約に記入します。利用希望量が供給を超える場合は差を明示します。</t>
+          <t>3. 65歳到達者は06_65歳移行判定で個別に移行可否を判定します。一律に減算してはいけません。</t>
         </is>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>6. ここまでで得られた値を基本ケースとし、未特定需要（07）のみを低位・中位・高位で補正します。</t>
+          <t>4. 判定結果を03・04の該当する増減行に転記します。継続利用者と利用者数は数式のため触りません。</t>
         </is>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>5. 圏域事業所へ利用可能性を照会し、08_供給制約に記入します。利用希望量が供給を超える場合は差を明示します。</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="22" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>6. ここまでで得られた値を基本ケースとし、未特定需要（07）のみを低位・中位・高位で補正します。</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="22" customHeight="1">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>7. 確定した利用者数・月間サービス量を計画書 第5章の見込量表と、財源構成案ブックの08へ転記します。</t>
         </is>
@@ -1053,13 +1109,13 @@
   <mergeCells count="10">
     <mergeCell ref="A21:E21"/>
     <mergeCell ref="A20:E20"/>
+    <mergeCell ref="A24:E24"/>
     <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A16:E16"/>
+    <mergeCell ref="A25:E25"/>
     <mergeCell ref="A19:E19"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A23:E23"/>
     <mergeCell ref="A22:E22"/>
-    <mergeCell ref="A17:E17"/>
     <mergeCell ref="A18:E18"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1085,7 +1141,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="10" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>地域生活支援事業の見込量</t>
         </is>
@@ -1145,13 +1201,13 @@
           <t>か所</t>
         </is>
       </c>
-      <c r="C6" s="20" t="n">
+      <c r="C6" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="D6" s="20" t="n">
+      <c r="D6" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="E6" s="18" t="n"/>
+      <c r="E6" s="19" t="n"/>
       <c r="F6" s="4" t="inlineStr"/>
       <c r="G6" s="4" t="inlineStr">
         <is>
@@ -1165,18 +1221,18 @@
           <t>成年後見制度利用支援事業</t>
         </is>
       </c>
-      <c r="B7" s="34" t="inlineStr">
+      <c r="B7" s="9" t="inlineStr">
         <is>
           <t>人</t>
         </is>
       </c>
-      <c r="C7" s="29" t="n">
+      <c r="C7" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="D7" s="29" t="n">
+      <c r="D7" s="30" t="n">
         <v>5</v>
       </c>
-      <c r="E7" s="18" t="n"/>
+      <c r="E7" s="19" t="n"/>
       <c r="F7" s="6" t="inlineStr"/>
       <c r="G7" s="6" t="inlineStr">
         <is>
@@ -1195,13 +1251,13 @@
           <t>人</t>
         </is>
       </c>
-      <c r="C8" s="20" t="n">
+      <c r="C8" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="D8" s="20" t="n">
+      <c r="D8" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="E8" s="18" t="n"/>
+      <c r="E8" s="19" t="n"/>
       <c r="F8" s="4" t="inlineStr"/>
       <c r="G8" s="4" t="inlineStr">
         <is>
@@ -1215,18 +1271,18 @@
           <t>日常生活用具給付等事業</t>
         </is>
       </c>
-      <c r="B9" s="34" t="inlineStr">
+      <c r="B9" s="9" t="inlineStr">
         <is>
           <t>件</t>
         </is>
       </c>
-      <c r="C9" s="29" t="n">
+      <c r="C9" s="30" t="n">
         <v>69</v>
       </c>
-      <c r="D9" s="29" t="n">
+      <c r="D9" s="30" t="n">
         <v>72</v>
       </c>
-      <c r="E9" s="18" t="n"/>
+      <c r="E9" s="19" t="n"/>
       <c r="F9" s="6" t="inlineStr"/>
       <c r="G9" s="6" t="inlineStr">
         <is>
@@ -1245,13 +1301,13 @@
           <t>人</t>
         </is>
       </c>
-      <c r="C10" s="20" t="n">
+      <c r="C10" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="D10" s="20" t="n">
+      <c r="D10" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="E10" s="18" t="n"/>
+      <c r="E10" s="19" t="n"/>
       <c r="F10" s="4" t="inlineStr"/>
       <c r="G10" s="4" t="inlineStr">
         <is>
@@ -1265,18 +1321,18 @@
           <t>日中一時支援事業</t>
         </is>
       </c>
-      <c r="B11" s="34" t="inlineStr">
+      <c r="B11" s="9" t="inlineStr">
         <is>
           <t>人</t>
         </is>
       </c>
-      <c r="C11" s="29" t="n">
+      <c r="C11" s="30" t="n">
         <v>2</v>
       </c>
-      <c r="D11" s="29" t="n">
+      <c r="D11" s="30" t="n">
         <v>2</v>
       </c>
-      <c r="E11" s="18" t="n"/>
+      <c r="E11" s="19" t="n"/>
       <c r="F11" s="6" t="inlineStr"/>
       <c r="G11" s="6" t="inlineStr">
         <is>
@@ -1295,13 +1351,13 @@
           <t>人</t>
         </is>
       </c>
-      <c r="C12" s="20" t="n">
+      <c r="C12" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="D12" s="20" t="n">
+      <c r="D12" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="E12" s="18" t="n"/>
+      <c r="E12" s="19" t="n"/>
       <c r="F12" s="4" t="inlineStr"/>
       <c r="G12" s="4" t="inlineStr">
         <is>
@@ -1315,18 +1371,18 @@
           <t>訪問入浴サービス事業</t>
         </is>
       </c>
-      <c r="B13" s="34" t="inlineStr">
+      <c r="B13" s="9" t="inlineStr">
         <is>
           <t>人</t>
         </is>
       </c>
-      <c r="C13" s="29" t="n">
+      <c r="C13" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="D13" s="29" t="n">
+      <c r="D13" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="E13" s="18" t="n"/>
+      <c r="E13" s="19" t="n"/>
       <c r="F13" s="6" t="inlineStr"/>
       <c r="G13" s="6" t="inlineStr">
         <is>
@@ -1345,13 +1401,13 @@
           <t>件</t>
         </is>
       </c>
-      <c r="C14" s="20" t="n">
+      <c r="C14" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="D14" s="20" t="n">
+      <c r="D14" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="E14" s="18" t="n"/>
+      <c r="E14" s="19" t="n"/>
       <c r="F14" s="4" t="inlineStr"/>
       <c r="G14" s="4" t="inlineStr">
         <is>
@@ -1365,18 +1421,18 @@
           <t>自発的活動支援事業</t>
         </is>
       </c>
-      <c r="B15" s="34" t="inlineStr">
+      <c r="B15" s="9" t="inlineStr">
         <is>
           <t>件</t>
         </is>
       </c>
-      <c r="C15" s="29" t="n">
+      <c r="C15" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="D15" s="29" t="n">
+      <c r="D15" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="E15" s="18" t="n"/>
+      <c r="E15" s="19" t="n"/>
       <c r="F15" s="6" t="inlineStr"/>
       <c r="G15" s="6" t="inlineStr">
         <is>
@@ -1410,7 +1466,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="10" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>村への確認・依頼事項（見込量推計関係）</t>
         </is>
@@ -1493,7 +1549,7 @@
           <t>02／06_65歳移行判定</t>
         </is>
       </c>
-      <c r="D7" s="34" t="inlineStr">
+      <c r="D7" s="9" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -1547,7 +1603,7 @@
           <t>02／03_生活介護・就労系</t>
         </is>
       </c>
-      <c r="D9" s="34" t="inlineStr">
+      <c r="D9" s="9" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -1601,7 +1657,7 @@
           <t>04／計画本文の記述</t>
         </is>
       </c>
-      <c r="D11" s="34" t="inlineStr">
+      <c r="D11" s="9" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -1655,7 +1711,7 @@
           <t>02／03</t>
         </is>
       </c>
-      <c r="D13" s="34" t="inlineStr">
+      <c r="D13" s="9" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -1709,7 +1765,7 @@
           <t>06_65歳移行判定</t>
         </is>
       </c>
-      <c r="D15" s="34" t="inlineStr">
+      <c r="D15" s="9" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -1751,6 +1807,736 @@
   <mergeCells count="2">
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C36"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>基本指針 別表第一が勘案を求める要素（サービス別）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>令和8年3月31日 こども家庭庁・厚生労働省告示第4号による改正後の別表第一による。本ブックの積上げ項目が告示の要求を満たしているかの対照表。「努める」とあるものは努力義務、それ以外は算定に当たって勘案すべき要素。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>サービス</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>別表第一が勘案を求める要素</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>本ブックでの反映先</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="42" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>居宅介護</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>現に利用している者の数／ニーズ／施設入所者の地域生活への移行者数／入院中の精神障がい者のうち移行後に利用が見込まれる者の数／平均的な一人当たり利用量</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>03の継続・新規・地域移行行、1人当たり月利用量</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="42" customHeight="1">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>重度訪問介護</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="42" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>同行援護</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>現に利用している者の数／ニーズ／平均的な一人当たり利用量（地域移行・精神科病院からの流入は勘案要素に含まれない）</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="42" customHeight="1">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>行動援護</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>居宅介護と同じ</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="42" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>重度障害者等包括支援</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>居宅介護と同じ</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="42" customHeight="1">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>生活介護</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>居宅介護と同じ。加えて強度行動障害の状態にある者・高次脳機能障害を有する者・医療的ケアを必要とする者について個別に利用者数の見込みを設定するよう努める</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>03。重度者は内数として別掲（村資料受領後）</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="42" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>自立訓練（機能訓練）</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>現に利用している者の数／ニーズ／施設入所者の地域移行者数／平均的な一人当たり利用量</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>05_実績ゼロサービス</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="42" customHeight="1">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>自立訓練（生活訓練）</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>居宅介護と同じ</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>05_実績ゼロサービス</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="42" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>就労選択支援</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>ニーズ／特別支援学校卒業者数／就労移行支援・A型・B型を新たに利用する者の数／現に利用している者の数</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>02_年齢到達者一覧（18歳）／03</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="42" customHeight="1">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>就労移行支援</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>居宅介護と同じ。加えて一般就労への移行者数／特別支援学校卒業者／復職を希望する休職者等</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>02（18歳）／03</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="42" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>就労継続支援A型</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>居宅介護と同じ。加えて一般就労への移行者数／地域の雇用情勢</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="42" customHeight="1">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>就労継続支援B型</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>居宅介護と同じ。加えて一般就労への移行者数。区域内のB型事業所の平均工賃月額について区域ごとの目標水準を設定することが望ましい</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>03。工賃目標は圏域協議事項</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="42" customHeight="1">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>就労定着支援</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>現に利用している者の数／ニーズ／一般就労への移行者数</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="42" customHeight="1">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>療養介護</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>現に利用している者の数／ニーズ</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>05_実績ゼロサービス</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="42" customHeight="1">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>短期入所（福祉型・医療型）</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>居宅介護と同じ。加えて重度障がい者について個別に利用者数の見込みを設定するよう努める</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>03。重度者は内数として別掲</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="42" customHeight="1">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>自立生活援助</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>現に利用している者の数／同居している家族による支援を受けられない障がい者の数／施設入所者の地域移行者数／入院中の精神障がい者のうち移行後の利用見込</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>05_実績ゼロサービス</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="42" customHeight="1">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>共同生活援助</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>居宅介護と同じ。加えて一人暮らしや家庭からGHに入所する者の数／GHから退所する者の数／重度障がい者の個別見込み</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>03。退所者は流出行</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>施設入所支援</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>令和7年度末時点の施設入所者数を基礎とし、地域生活への移行者数を控除の上、GH等での対応が困難な者の利用といった真に必要と判断される数を加えた数。5%以上削減と未達分の上乗せ。居室の個室化等の取組状況の把握</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>03。基準はR7年度末</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>計画相談支援</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>現に利用している者の数／ニーズ／入院中の精神障がい者のうち移行後の利用見込</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>03。請求件数ではなく実人数</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>地域移行支援</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>現に利用している者の数／ニーズ／施設入所者の地域移行者数／入院中の精神障がい者のうち移行後の利用見込。入所又は入院前の居住地を有する市町村が対象者数の見込みを設定する</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>05_実績ゼロサービス。帰属ルールに注意</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="42" customHeight="1">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>地域定着支援</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>現に利用している者の数／単身世帯である障がい者の数／同居している家族による支援を受けられない障がい者の数／施設入所者の地域移行者数</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>05_実績ゼロサービス</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="42" customHeight="1">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>児童発達支援</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>地域における児童の数の推移／現に利用している障がい児の数／ニーズ／重症心身障がい児等のニーズ／医療的ケア児等のニーズ／保育所・認定こども園・幼稚園での受入状況／入所施設から退所した後に利用が見込まれる障がい児の数／平均的な一人当たり利用量</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>04。就学による流出は02（6歳）</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="42" customHeight="1">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>放課後等デイサービス</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>同上（受入状況は放課後児童健全育成事業・小中学校・特別支援学校）</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>04。就学による流入は02（6歳）</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="42" customHeight="1">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>保育所等訪問支援</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>同上（受入状況は保育所・認定こども園・幼稚園・小学校・特別支援学校）</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>05_実績ゼロサービス</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="42" customHeight="1">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>居宅訪問型児童発達支援</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>地域における児童の数の推移／現に利用している障がい児の数／ニーズ／重症心身障がい児等のニーズ／医療的ケア児等のニーズ／平均的な一人当たり利用量</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>05_実績ゼロサービス</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="42" customHeight="1">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>障害児入所支援（福祉型・医療型）</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>地域における児童の数の推移／現に利用している障がい児の数／ニーズ／重症心身障がい児等のニーズ／医療的ケア児等のニーズ</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>10_村確認事項（県所管）</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="42" customHeight="1">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>障害児相談支援</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="42" customHeight="1">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>医療的ケア児等コーディネーター（市町村）</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>地域における医療的ケア児等のニーズ等を勘案して必要となる配置人数の見込みを設定する</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>計画本文 第4章(4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="30" customHeight="1">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>※ 別表第一の標準文言は「…等を勘案して、利用者数及び量の見込みを設定する」であり、利用者数と量（＝利用者数×平均的な一人当たり利用量）を分けて設定することを求めている。本ブック03・04の構成はこれに対応している。</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="30" customHeight="1">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>※ 重度障がい者（強度行動障害の状態にある者・高次脳機能障害を有する者・医療的ケアを必要とする者等）の個別見込みを求めているのは、生活介護・短期入所・共同生活援助の3サービスに限られる（いずれも努力義務）。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A36:C36"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A35:C35"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="52" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>基本指針 別表第五（地域差是正）の適用判定</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>第8期で新設。要件に該当する市町村は、全国の伸び率を用いた算定方法を基本とすることになる。本村が該当するかを確定するまで、見込量の算定方法は確定しない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>■ 条文（第三の二の2(一)ただし書及び別表第五）</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="34" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>別表第五 一の項　⑴ 全部過疎市町村ではないこと　かつ　⑵ 当該サービスの、人口に占めるサービス利用者割合が、⑴を満たす市町村の上位25%の範囲内であること</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="34" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>別表第五 二の項　当該市町村の当該サービスの利用者数の伸び率が全国の伸び率を上回る場合は、令和9〜11年度の見込みを、令和8年度の見込みと全国の伸び率を用いて定める</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="34" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>備考　全部過疎市町村＝過疎地域の持続的発展の支援に関する特別措置法（令和3年法律第19号）の過疎地域のうち過疎区分が全部過疎である市町村／人口＝特定障害福祉サービスは18歳以上人口、特定障害児通所支援は18歳未満人口／伸び率＝令和5年度から令和7年度までの幾何平均／この方法は全国の伸び率が正の値であるときに限る</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="34" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>第三の二の2(一)　⑵ 地域の具体的なニーズ調査を踏まえ、市町村障害福祉計画等において、⑴と異なる算定方法をその必要性及び根拠を添えて示す場合には、当該算定方法</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>■ 判定</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>判定項目</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>入力</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>判定</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>根拠・備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>⑴ 本村の過疎区分</t>
+        </is>
+      </c>
+      <c r="B13" s="16" t="inlineStr">
+        <is>
+          <t>全部過疎（見込）</t>
+        </is>
+      </c>
+      <c r="C13" s="8">
+        <f>IF(B13="全部過疎（見込）","要件⑴を満たさない→別表第五 適用外","要確認")</f>
+        <v/>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>総務省が公表する過疎地域市町村一覧で確認する。北塩原村は過疎地域であり、市町村合併を経ていないため全部過疎と考えられる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>⑵ サービス利用者割合</t>
+        </is>
+      </c>
+      <c r="B14" s="16" t="inlineStr">
+        <is>
+          <t>村資料・国公表データ待ち</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>18歳以上人口（障害児通所支援は18歳未満人口）に占める利用者割合が、全部過疎でない市町村の上位25%以内かどうか。⑴を満たさない場合は判定不要。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>結論</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="n"/>
+      <c r="C15" s="25">
+        <f>IF(C13="要件⑴を満たさない→別表第五 適用外","個別積上げ方式を採用可（第三の二の2(一)本文による）","要判定")</f>
+        <v/>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>⑴かつ⑵の連言であるため、⑴を満たさなければ別表第五 二の項の算定方法は適用されない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="34" customHeight="1">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>※ 仮に本村が全部過疎に該当しない場合でも、第三の二の2(一)⑵により、地域の具体的なニーズ調査を踏まえて別の算定方法を採ることができる。その場合は、個別積上げ方式を採る必要性及び根拠を計画本文に明記することが要件となる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="34" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>※ 別表第五が対象とするのは「特定障害福祉サービス」及び「特定障害児通所支援」であり、全サービスではない。該当サービスの範囲は障害者総合支援法第88条第10項及び児童福祉法第21条の5の15第2項の定義による。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="A7:D7"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A11:D11"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1771,7 +2557,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="10" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>見込量の推計方式</t>
         </is>
@@ -1785,7 +2571,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="9" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>1. 算式</t>
         </is>
@@ -1843,7 +2629,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="inlineStr">
+      <c r="A10" s="10" t="inlineStr">
         <is>
           <t>2. 推計対象の3層</t>
         </is>
@@ -1921,7 +2707,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="9" t="inlineStr">
+      <c r="A16" s="10" t="inlineStr">
         <is>
           <t>3. 年齢到達の扱い</t>
         </is>
@@ -2047,7 +2833,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="9" t="inlineStr">
+      <c r="A25" s="10" t="inlineStr">
         <is>
           <t>4. 県内他団体の推計方法との関係</t>
         </is>
@@ -2165,7 +2951,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="10" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>年齢到達者一覧（匿名台帳）</t>
         </is>
@@ -2244,376 +3030,376 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>（例）001</t>
         </is>
       </c>
-      <c r="B6" s="12" t="inlineStr">
+      <c r="B6" s="13" t="inlineStr">
         <is>
           <t>65歳</t>
         </is>
       </c>
-      <c r="C6" s="12" t="inlineStr">
+      <c r="C6" s="13" t="inlineStr">
         <is>
           <t>令和10年度</t>
         </is>
       </c>
-      <c r="D6" s="12" t="inlineStr">
+      <c r="D6" s="13" t="inlineStr">
         <is>
           <t>65</t>
         </is>
       </c>
-      <c r="E6" s="12" t="inlineStr">
+      <c r="E6" s="13" t="inlineStr">
         <is>
           <t>区分4</t>
         </is>
       </c>
-      <c r="F6" s="13" t="inlineStr">
+      <c r="F6" s="14" t="inlineStr">
         <is>
           <t>生活介護、居宅介護</t>
         </is>
       </c>
-      <c r="G6" s="12" t="inlineStr">
+      <c r="G6" s="13" t="inlineStr">
         <is>
           <t>あり</t>
         </is>
       </c>
-      <c r="H6" s="12" t="inlineStr">
+      <c r="H6" s="13" t="inlineStr">
         <is>
           <t>一部</t>
         </is>
       </c>
-      <c r="I6" s="12" t="inlineStr">
+      <c r="I6" s="13" t="inlineStr">
         <is>
           <t>生活介護は継続</t>
         </is>
       </c>
-      <c r="J6" s="14" t="inlineStr">
+      <c r="J6" s="15" t="inlineStr">
         <is>
           <t>-10人日</t>
         </is>
       </c>
-      <c r="K6" s="13" t="inlineStr">
+      <c r="K6" s="14" t="inlineStr">
         <is>
           <t>例示。実データではありません</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="n"/>
-      <c r="B7" s="15" t="n"/>
-      <c r="C7" s="15" t="n"/>
-      <c r="D7" s="15" t="n"/>
-      <c r="E7" s="15" t="n"/>
-      <c r="F7" s="16" t="n"/>
-      <c r="G7" s="15" t="n"/>
-      <c r="H7" s="15" t="n"/>
-      <c r="I7" s="15" t="n"/>
-      <c r="J7" s="17" t="n"/>
-      <c r="K7" s="16" t="n"/>
+      <c r="A7" s="16" t="n"/>
+      <c r="B7" s="16" t="n"/>
+      <c r="C7" s="16" t="n"/>
+      <c r="D7" s="16" t="n"/>
+      <c r="E7" s="16" t="n"/>
+      <c r="F7" s="17" t="n"/>
+      <c r="G7" s="16" t="n"/>
+      <c r="H7" s="16" t="n"/>
+      <c r="I7" s="16" t="n"/>
+      <c r="J7" s="18" t="n"/>
+      <c r="K7" s="17" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="15" t="n"/>
-      <c r="B8" s="15" t="n"/>
-      <c r="C8" s="15" t="n"/>
-      <c r="D8" s="15" t="n"/>
-      <c r="E8" s="15" t="n"/>
-      <c r="F8" s="16" t="n"/>
-      <c r="G8" s="15" t="n"/>
-      <c r="H8" s="15" t="n"/>
-      <c r="I8" s="15" t="n"/>
-      <c r="J8" s="17" t="n"/>
-      <c r="K8" s="16" t="n"/>
+      <c r="A8" s="16" t="n"/>
+      <c r="B8" s="16" t="n"/>
+      <c r="C8" s="16" t="n"/>
+      <c r="D8" s="16" t="n"/>
+      <c r="E8" s="16" t="n"/>
+      <c r="F8" s="17" t="n"/>
+      <c r="G8" s="16" t="n"/>
+      <c r="H8" s="16" t="n"/>
+      <c r="I8" s="16" t="n"/>
+      <c r="J8" s="18" t="n"/>
+      <c r="K8" s="17" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="15" t="n"/>
-      <c r="B9" s="15" t="n"/>
-      <c r="C9" s="15" t="n"/>
-      <c r="D9" s="15" t="n"/>
-      <c r="E9" s="15" t="n"/>
-      <c r="F9" s="16" t="n"/>
-      <c r="G9" s="15" t="n"/>
-      <c r="H9" s="15" t="n"/>
-      <c r="I9" s="15" t="n"/>
-      <c r="J9" s="17" t="n"/>
-      <c r="K9" s="16" t="n"/>
+      <c r="A9" s="16" t="n"/>
+      <c r="B9" s="16" t="n"/>
+      <c r="C9" s="16" t="n"/>
+      <c r="D9" s="16" t="n"/>
+      <c r="E9" s="16" t="n"/>
+      <c r="F9" s="17" t="n"/>
+      <c r="G9" s="16" t="n"/>
+      <c r="H9" s="16" t="n"/>
+      <c r="I9" s="16" t="n"/>
+      <c r="J9" s="18" t="n"/>
+      <c r="K9" s="17" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="n"/>
-      <c r="B10" s="15" t="n"/>
-      <c r="C10" s="15" t="n"/>
-      <c r="D10" s="15" t="n"/>
-      <c r="E10" s="15" t="n"/>
-      <c r="F10" s="16" t="n"/>
-      <c r="G10" s="15" t="n"/>
-      <c r="H10" s="15" t="n"/>
-      <c r="I10" s="15" t="n"/>
-      <c r="J10" s="17" t="n"/>
-      <c r="K10" s="16" t="n"/>
+      <c r="A10" s="16" t="n"/>
+      <c r="B10" s="16" t="n"/>
+      <c r="C10" s="16" t="n"/>
+      <c r="D10" s="16" t="n"/>
+      <c r="E10" s="16" t="n"/>
+      <c r="F10" s="17" t="n"/>
+      <c r="G10" s="16" t="n"/>
+      <c r="H10" s="16" t="n"/>
+      <c r="I10" s="16" t="n"/>
+      <c r="J10" s="18" t="n"/>
+      <c r="K10" s="17" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="15" t="n"/>
-      <c r="B11" s="15" t="n"/>
-      <c r="C11" s="15" t="n"/>
-      <c r="D11" s="15" t="n"/>
-      <c r="E11" s="15" t="n"/>
-      <c r="F11" s="16" t="n"/>
-      <c r="G11" s="15" t="n"/>
-      <c r="H11" s="15" t="n"/>
-      <c r="I11" s="15" t="n"/>
-      <c r="J11" s="17" t="n"/>
-      <c r="K11" s="16" t="n"/>
+      <c r="A11" s="16" t="n"/>
+      <c r="B11" s="16" t="n"/>
+      <c r="C11" s="16" t="n"/>
+      <c r="D11" s="16" t="n"/>
+      <c r="E11" s="16" t="n"/>
+      <c r="F11" s="17" t="n"/>
+      <c r="G11" s="16" t="n"/>
+      <c r="H11" s="16" t="n"/>
+      <c r="I11" s="16" t="n"/>
+      <c r="J11" s="18" t="n"/>
+      <c r="K11" s="17" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="15" t="n"/>
-      <c r="B12" s="15" t="n"/>
-      <c r="C12" s="15" t="n"/>
-      <c r="D12" s="15" t="n"/>
-      <c r="E12" s="15" t="n"/>
-      <c r="F12" s="16" t="n"/>
-      <c r="G12" s="15" t="n"/>
-      <c r="H12" s="15" t="n"/>
-      <c r="I12" s="15" t="n"/>
-      <c r="J12" s="17" t="n"/>
-      <c r="K12" s="16" t="n"/>
+      <c r="A12" s="16" t="n"/>
+      <c r="B12" s="16" t="n"/>
+      <c r="C12" s="16" t="n"/>
+      <c r="D12" s="16" t="n"/>
+      <c r="E12" s="16" t="n"/>
+      <c r="F12" s="17" t="n"/>
+      <c r="G12" s="16" t="n"/>
+      <c r="H12" s="16" t="n"/>
+      <c r="I12" s="16" t="n"/>
+      <c r="J12" s="18" t="n"/>
+      <c r="K12" s="17" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="15" t="n"/>
-      <c r="B13" s="15" t="n"/>
-      <c r="C13" s="15" t="n"/>
-      <c r="D13" s="15" t="n"/>
-      <c r="E13" s="15" t="n"/>
-      <c r="F13" s="16" t="n"/>
-      <c r="G13" s="15" t="n"/>
-      <c r="H13" s="15" t="n"/>
-      <c r="I13" s="15" t="n"/>
-      <c r="J13" s="17" t="n"/>
-      <c r="K13" s="16" t="n"/>
+      <c r="A13" s="16" t="n"/>
+      <c r="B13" s="16" t="n"/>
+      <c r="C13" s="16" t="n"/>
+      <c r="D13" s="16" t="n"/>
+      <c r="E13" s="16" t="n"/>
+      <c r="F13" s="17" t="n"/>
+      <c r="G13" s="16" t="n"/>
+      <c r="H13" s="16" t="n"/>
+      <c r="I13" s="16" t="n"/>
+      <c r="J13" s="18" t="n"/>
+      <c r="K13" s="17" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="15" t="n"/>
-      <c r="B14" s="15" t="n"/>
-      <c r="C14" s="15" t="n"/>
-      <c r="D14" s="15" t="n"/>
-      <c r="E14" s="15" t="n"/>
-      <c r="F14" s="16" t="n"/>
-      <c r="G14" s="15" t="n"/>
-      <c r="H14" s="15" t="n"/>
-      <c r="I14" s="15" t="n"/>
-      <c r="J14" s="17" t="n"/>
-      <c r="K14" s="16" t="n"/>
+      <c r="A14" s="16" t="n"/>
+      <c r="B14" s="16" t="n"/>
+      <c r="C14" s="16" t="n"/>
+      <c r="D14" s="16" t="n"/>
+      <c r="E14" s="16" t="n"/>
+      <c r="F14" s="17" t="n"/>
+      <c r="G14" s="16" t="n"/>
+      <c r="H14" s="16" t="n"/>
+      <c r="I14" s="16" t="n"/>
+      <c r="J14" s="18" t="n"/>
+      <c r="K14" s="17" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="15" t="n"/>
-      <c r="B15" s="15" t="n"/>
-      <c r="C15" s="15" t="n"/>
-      <c r="D15" s="15" t="n"/>
-      <c r="E15" s="15" t="n"/>
-      <c r="F15" s="16" t="n"/>
-      <c r="G15" s="15" t="n"/>
-      <c r="H15" s="15" t="n"/>
-      <c r="I15" s="15" t="n"/>
-      <c r="J15" s="17" t="n"/>
-      <c r="K15" s="16" t="n"/>
+      <c r="A15" s="16" t="n"/>
+      <c r="B15" s="16" t="n"/>
+      <c r="C15" s="16" t="n"/>
+      <c r="D15" s="16" t="n"/>
+      <c r="E15" s="16" t="n"/>
+      <c r="F15" s="17" t="n"/>
+      <c r="G15" s="16" t="n"/>
+      <c r="H15" s="16" t="n"/>
+      <c r="I15" s="16" t="n"/>
+      <c r="J15" s="18" t="n"/>
+      <c r="K15" s="17" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="15" t="n"/>
-      <c r="B16" s="15" t="n"/>
-      <c r="C16" s="15" t="n"/>
-      <c r="D16" s="15" t="n"/>
-      <c r="E16" s="15" t="n"/>
-      <c r="F16" s="16" t="n"/>
-      <c r="G16" s="15" t="n"/>
-      <c r="H16" s="15" t="n"/>
-      <c r="I16" s="15" t="n"/>
-      <c r="J16" s="17" t="n"/>
-      <c r="K16" s="16" t="n"/>
+      <c r="A16" s="16" t="n"/>
+      <c r="B16" s="16" t="n"/>
+      <c r="C16" s="16" t="n"/>
+      <c r="D16" s="16" t="n"/>
+      <c r="E16" s="16" t="n"/>
+      <c r="F16" s="17" t="n"/>
+      <c r="G16" s="16" t="n"/>
+      <c r="H16" s="16" t="n"/>
+      <c r="I16" s="16" t="n"/>
+      <c r="J16" s="18" t="n"/>
+      <c r="K16" s="17" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="n"/>
-      <c r="B17" s="15" t="n"/>
-      <c r="C17" s="15" t="n"/>
-      <c r="D17" s="15" t="n"/>
-      <c r="E17" s="15" t="n"/>
-      <c r="F17" s="16" t="n"/>
-      <c r="G17" s="15" t="n"/>
-      <c r="H17" s="15" t="n"/>
-      <c r="I17" s="15" t="n"/>
-      <c r="J17" s="17" t="n"/>
-      <c r="K17" s="16" t="n"/>
+      <c r="A17" s="16" t="n"/>
+      <c r="B17" s="16" t="n"/>
+      <c r="C17" s="16" t="n"/>
+      <c r="D17" s="16" t="n"/>
+      <c r="E17" s="16" t="n"/>
+      <c r="F17" s="17" t="n"/>
+      <c r="G17" s="16" t="n"/>
+      <c r="H17" s="16" t="n"/>
+      <c r="I17" s="16" t="n"/>
+      <c r="J17" s="18" t="n"/>
+      <c r="K17" s="17" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="15" t="n"/>
-      <c r="B18" s="15" t="n"/>
-      <c r="C18" s="15" t="n"/>
-      <c r="D18" s="15" t="n"/>
-      <c r="E18" s="15" t="n"/>
-      <c r="F18" s="16" t="n"/>
-      <c r="G18" s="15" t="n"/>
-      <c r="H18" s="15" t="n"/>
-      <c r="I18" s="15" t="n"/>
-      <c r="J18" s="17" t="n"/>
-      <c r="K18" s="16" t="n"/>
+      <c r="A18" s="16" t="n"/>
+      <c r="B18" s="16" t="n"/>
+      <c r="C18" s="16" t="n"/>
+      <c r="D18" s="16" t="n"/>
+      <c r="E18" s="16" t="n"/>
+      <c r="F18" s="17" t="n"/>
+      <c r="G18" s="16" t="n"/>
+      <c r="H18" s="16" t="n"/>
+      <c r="I18" s="16" t="n"/>
+      <c r="J18" s="18" t="n"/>
+      <c r="K18" s="17" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="15" t="n"/>
-      <c r="B19" s="15" t="n"/>
-      <c r="C19" s="15" t="n"/>
-      <c r="D19" s="15" t="n"/>
-      <c r="E19" s="15" t="n"/>
-      <c r="F19" s="16" t="n"/>
-      <c r="G19" s="15" t="n"/>
-      <c r="H19" s="15" t="n"/>
-      <c r="I19" s="15" t="n"/>
-      <c r="J19" s="17" t="n"/>
-      <c r="K19" s="16" t="n"/>
+      <c r="A19" s="16" t="n"/>
+      <c r="B19" s="16" t="n"/>
+      <c r="C19" s="16" t="n"/>
+      <c r="D19" s="16" t="n"/>
+      <c r="E19" s="16" t="n"/>
+      <c r="F19" s="17" t="n"/>
+      <c r="G19" s="16" t="n"/>
+      <c r="H19" s="16" t="n"/>
+      <c r="I19" s="16" t="n"/>
+      <c r="J19" s="18" t="n"/>
+      <c r="K19" s="17" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="15" t="n"/>
-      <c r="B20" s="15" t="n"/>
-      <c r="C20" s="15" t="n"/>
-      <c r="D20" s="15" t="n"/>
-      <c r="E20" s="15" t="n"/>
-      <c r="F20" s="16" t="n"/>
-      <c r="G20" s="15" t="n"/>
-      <c r="H20" s="15" t="n"/>
-      <c r="I20" s="15" t="n"/>
-      <c r="J20" s="17" t="n"/>
-      <c r="K20" s="16" t="n"/>
+      <c r="A20" s="16" t="n"/>
+      <c r="B20" s="16" t="n"/>
+      <c r="C20" s="16" t="n"/>
+      <c r="D20" s="16" t="n"/>
+      <c r="E20" s="16" t="n"/>
+      <c r="F20" s="17" t="n"/>
+      <c r="G20" s="16" t="n"/>
+      <c r="H20" s="16" t="n"/>
+      <c r="I20" s="16" t="n"/>
+      <c r="J20" s="18" t="n"/>
+      <c r="K20" s="17" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="15" t="n"/>
-      <c r="B21" s="15" t="n"/>
-      <c r="C21" s="15" t="n"/>
-      <c r="D21" s="15" t="n"/>
-      <c r="E21" s="15" t="n"/>
-      <c r="F21" s="16" t="n"/>
-      <c r="G21" s="15" t="n"/>
-      <c r="H21" s="15" t="n"/>
-      <c r="I21" s="15" t="n"/>
-      <c r="J21" s="17" t="n"/>
-      <c r="K21" s="16" t="n"/>
+      <c r="A21" s="16" t="n"/>
+      <c r="B21" s="16" t="n"/>
+      <c r="C21" s="16" t="n"/>
+      <c r="D21" s="16" t="n"/>
+      <c r="E21" s="16" t="n"/>
+      <c r="F21" s="17" t="n"/>
+      <c r="G21" s="16" t="n"/>
+      <c r="H21" s="16" t="n"/>
+      <c r="I21" s="16" t="n"/>
+      <c r="J21" s="18" t="n"/>
+      <c r="K21" s="17" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="15" t="n"/>
-      <c r="B22" s="15" t="n"/>
-      <c r="C22" s="15" t="n"/>
-      <c r="D22" s="15" t="n"/>
-      <c r="E22" s="15" t="n"/>
-      <c r="F22" s="16" t="n"/>
-      <c r="G22" s="15" t="n"/>
-      <c r="H22" s="15" t="n"/>
-      <c r="I22" s="15" t="n"/>
-      <c r="J22" s="17" t="n"/>
-      <c r="K22" s="16" t="n"/>
+      <c r="A22" s="16" t="n"/>
+      <c r="B22" s="16" t="n"/>
+      <c r="C22" s="16" t="n"/>
+      <c r="D22" s="16" t="n"/>
+      <c r="E22" s="16" t="n"/>
+      <c r="F22" s="17" t="n"/>
+      <c r="G22" s="16" t="n"/>
+      <c r="H22" s="16" t="n"/>
+      <c r="I22" s="16" t="n"/>
+      <c r="J22" s="18" t="n"/>
+      <c r="K22" s="17" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="15" t="n"/>
-      <c r="B23" s="15" t="n"/>
-      <c r="C23" s="15" t="n"/>
-      <c r="D23" s="15" t="n"/>
-      <c r="E23" s="15" t="n"/>
-      <c r="F23" s="16" t="n"/>
-      <c r="G23" s="15" t="n"/>
-      <c r="H23" s="15" t="n"/>
-      <c r="I23" s="15" t="n"/>
-      <c r="J23" s="17" t="n"/>
-      <c r="K23" s="16" t="n"/>
+      <c r="A23" s="16" t="n"/>
+      <c r="B23" s="16" t="n"/>
+      <c r="C23" s="16" t="n"/>
+      <c r="D23" s="16" t="n"/>
+      <c r="E23" s="16" t="n"/>
+      <c r="F23" s="17" t="n"/>
+      <c r="G23" s="16" t="n"/>
+      <c r="H23" s="16" t="n"/>
+      <c r="I23" s="16" t="n"/>
+      <c r="J23" s="18" t="n"/>
+      <c r="K23" s="17" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="15" t="n"/>
-      <c r="B24" s="15" t="n"/>
-      <c r="C24" s="15" t="n"/>
-      <c r="D24" s="15" t="n"/>
-      <c r="E24" s="15" t="n"/>
-      <c r="F24" s="16" t="n"/>
-      <c r="G24" s="15" t="n"/>
-      <c r="H24" s="15" t="n"/>
-      <c r="I24" s="15" t="n"/>
-      <c r="J24" s="17" t="n"/>
-      <c r="K24" s="16" t="n"/>
+      <c r="A24" s="16" t="n"/>
+      <c r="B24" s="16" t="n"/>
+      <c r="C24" s="16" t="n"/>
+      <c r="D24" s="16" t="n"/>
+      <c r="E24" s="16" t="n"/>
+      <c r="F24" s="17" t="n"/>
+      <c r="G24" s="16" t="n"/>
+      <c r="H24" s="16" t="n"/>
+      <c r="I24" s="16" t="n"/>
+      <c r="J24" s="18" t="n"/>
+      <c r="K24" s="17" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="15" t="n"/>
-      <c r="B25" s="15" t="n"/>
-      <c r="C25" s="15" t="n"/>
-      <c r="D25" s="15" t="n"/>
-      <c r="E25" s="15" t="n"/>
-      <c r="F25" s="16" t="n"/>
-      <c r="G25" s="15" t="n"/>
-      <c r="H25" s="15" t="n"/>
-      <c r="I25" s="15" t="n"/>
-      <c r="J25" s="17" t="n"/>
-      <c r="K25" s="16" t="n"/>
+      <c r="A25" s="16" t="n"/>
+      <c r="B25" s="16" t="n"/>
+      <c r="C25" s="16" t="n"/>
+      <c r="D25" s="16" t="n"/>
+      <c r="E25" s="16" t="n"/>
+      <c r="F25" s="17" t="n"/>
+      <c r="G25" s="16" t="n"/>
+      <c r="H25" s="16" t="n"/>
+      <c r="I25" s="16" t="n"/>
+      <c r="J25" s="18" t="n"/>
+      <c r="K25" s="17" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="15" t="n"/>
-      <c r="B26" s="15" t="n"/>
-      <c r="C26" s="15" t="n"/>
-      <c r="D26" s="15" t="n"/>
-      <c r="E26" s="15" t="n"/>
-      <c r="F26" s="16" t="n"/>
-      <c r="G26" s="15" t="n"/>
-      <c r="H26" s="15" t="n"/>
-      <c r="I26" s="15" t="n"/>
-      <c r="J26" s="17" t="n"/>
-      <c r="K26" s="16" t="n"/>
+      <c r="A26" s="16" t="n"/>
+      <c r="B26" s="16" t="n"/>
+      <c r="C26" s="16" t="n"/>
+      <c r="D26" s="16" t="n"/>
+      <c r="E26" s="16" t="n"/>
+      <c r="F26" s="17" t="n"/>
+      <c r="G26" s="16" t="n"/>
+      <c r="H26" s="16" t="n"/>
+      <c r="I26" s="16" t="n"/>
+      <c r="J26" s="18" t="n"/>
+      <c r="K26" s="17" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="15" t="n"/>
-      <c r="B27" s="15" t="n"/>
-      <c r="C27" s="15" t="n"/>
-      <c r="D27" s="15" t="n"/>
-      <c r="E27" s="15" t="n"/>
-      <c r="F27" s="16" t="n"/>
-      <c r="G27" s="15" t="n"/>
-      <c r="H27" s="15" t="n"/>
-      <c r="I27" s="15" t="n"/>
-      <c r="J27" s="17" t="n"/>
-      <c r="K27" s="16" t="n"/>
+      <c r="A27" s="16" t="n"/>
+      <c r="B27" s="16" t="n"/>
+      <c r="C27" s="16" t="n"/>
+      <c r="D27" s="16" t="n"/>
+      <c r="E27" s="16" t="n"/>
+      <c r="F27" s="17" t="n"/>
+      <c r="G27" s="16" t="n"/>
+      <c r="H27" s="16" t="n"/>
+      <c r="I27" s="16" t="n"/>
+      <c r="J27" s="18" t="n"/>
+      <c r="K27" s="17" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="15" t="n"/>
-      <c r="B28" s="15" t="n"/>
-      <c r="C28" s="15" t="n"/>
-      <c r="D28" s="15" t="n"/>
-      <c r="E28" s="15" t="n"/>
-      <c r="F28" s="16" t="n"/>
-      <c r="G28" s="15" t="n"/>
-      <c r="H28" s="15" t="n"/>
-      <c r="I28" s="15" t="n"/>
-      <c r="J28" s="17" t="n"/>
-      <c r="K28" s="16" t="n"/>
+      <c r="A28" s="16" t="n"/>
+      <c r="B28" s="16" t="n"/>
+      <c r="C28" s="16" t="n"/>
+      <c r="D28" s="16" t="n"/>
+      <c r="E28" s="16" t="n"/>
+      <c r="F28" s="17" t="n"/>
+      <c r="G28" s="16" t="n"/>
+      <c r="H28" s="16" t="n"/>
+      <c r="I28" s="16" t="n"/>
+      <c r="J28" s="18" t="n"/>
+      <c r="K28" s="17" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="15" t="n"/>
-      <c r="B29" s="15" t="n"/>
-      <c r="C29" s="15" t="n"/>
-      <c r="D29" s="15" t="n"/>
-      <c r="E29" s="15" t="n"/>
-      <c r="F29" s="16" t="n"/>
-      <c r="G29" s="15" t="n"/>
-      <c r="H29" s="15" t="n"/>
-      <c r="I29" s="15" t="n"/>
-      <c r="J29" s="17" t="n"/>
-      <c r="K29" s="16" t="n"/>
+      <c r="A29" s="16" t="n"/>
+      <c r="B29" s="16" t="n"/>
+      <c r="C29" s="16" t="n"/>
+      <c r="D29" s="16" t="n"/>
+      <c r="E29" s="16" t="n"/>
+      <c r="F29" s="17" t="n"/>
+      <c r="G29" s="16" t="n"/>
+      <c r="H29" s="16" t="n"/>
+      <c r="I29" s="16" t="n"/>
+      <c r="J29" s="18" t="n"/>
+      <c r="K29" s="17" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="15" t="n"/>
-      <c r="B30" s="15" t="n"/>
-      <c r="C30" s="15" t="n"/>
-      <c r="D30" s="15" t="n"/>
-      <c r="E30" s="15" t="n"/>
-      <c r="F30" s="16" t="n"/>
-      <c r="G30" s="15" t="n"/>
-      <c r="H30" s="15" t="n"/>
-      <c r="I30" s="15" t="n"/>
-      <c r="J30" s="17" t="n"/>
-      <c r="K30" s="16" t="n"/>
+      <c r="A30" s="16" t="n"/>
+      <c r="B30" s="16" t="n"/>
+      <c r="C30" s="16" t="n"/>
+      <c r="D30" s="16" t="n"/>
+      <c r="E30" s="16" t="n"/>
+      <c r="F30" s="17" t="n"/>
+      <c r="G30" s="16" t="n"/>
+      <c r="H30" s="16" t="n"/>
+      <c r="I30" s="16" t="n"/>
+      <c r="J30" s="18" t="n"/>
+      <c r="K30" s="17" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="9" t="inlineStr">
+      <c r="A32" s="10" t="inlineStr">
         <is>
           <t>記入のしかた</t>
         </is>
@@ -2696,7 +3482,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="10" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>障害福祉サービスの個別積上げ</t>
         </is>
@@ -2710,7 +3496,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="9" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>1　居宅介護</t>
         </is>
@@ -2772,18 +3558,18 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C8" s="18" t="n">
+      <c r="C8" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="D8" s="19">
+      <c r="D8" s="20">
         <f>C15</f>
         <v/>
       </c>
-      <c r="E8" s="19">
+      <c r="E8" s="20">
         <f>D15</f>
         <v/>
       </c>
-      <c r="F8" s="19">
+      <c r="F8" s="20">
         <f>E15</f>
         <v/>
       </c>
@@ -2804,10 +3590,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C9" s="20" t="n"/>
-      <c r="D9" s="18" t="n"/>
-      <c r="E9" s="18" t="n"/>
-      <c r="F9" s="18" t="n"/>
+      <c r="C9" s="21" t="n"/>
+      <c r="D9" s="19" t="n"/>
+      <c r="E9" s="19" t="n"/>
+      <c r="F9" s="19" t="n"/>
       <c r="G9" s="4" t="inlineStr">
         <is>
           <t>02_年齢到達者一覧から転記する</t>
@@ -2825,10 +3611,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C10" s="20" t="n"/>
-      <c r="D10" s="18" t="n"/>
-      <c r="E10" s="18" t="n"/>
-      <c r="F10" s="18" t="n"/>
+      <c r="C10" s="21" t="n"/>
+      <c r="D10" s="19" t="n"/>
+      <c r="E10" s="19" t="n"/>
+      <c r="F10" s="19" t="n"/>
       <c r="G10" s="4" t="inlineStr">
         <is>
           <t>移行予定者を個別に確認する</t>
@@ -2846,10 +3632,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C11" s="20" t="n"/>
-      <c r="D11" s="18" t="n"/>
-      <c r="E11" s="18" t="n"/>
-      <c r="F11" s="18" t="n"/>
+      <c r="C11" s="21" t="n"/>
+      <c r="D11" s="19" t="n"/>
+      <c r="E11" s="19" t="n"/>
+      <c r="F11" s="19" t="n"/>
       <c r="G11" s="4" t="inlineStr">
         <is>
           <t>相談支援事業所からの利用開始相談を含む</t>
@@ -2867,10 +3653,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C12" s="21" t="n"/>
-      <c r="D12" s="22" t="n"/>
-      <c r="E12" s="22" t="n"/>
-      <c r="F12" s="22" t="n"/>
+      <c r="C12" s="22" t="n"/>
+      <c r="D12" s="23" t="n"/>
+      <c r="E12" s="23" t="n"/>
+      <c r="F12" s="23" t="n"/>
       <c r="G12" s="4" t="inlineStr">
         <is>
           <t>06_65歳移行判定の結果を反映する。一律に減算しない</t>
@@ -2888,10 +3674,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C13" s="21" t="n"/>
-      <c r="D13" s="22" t="n"/>
-      <c r="E13" s="22" t="n"/>
-      <c r="F13" s="22" t="n"/>
+      <c r="C13" s="22" t="n"/>
+      <c r="D13" s="23" t="n"/>
+      <c r="E13" s="23" t="n"/>
+      <c r="F13" s="23" t="n"/>
       <c r="G13" s="4" t="inlineStr">
         <is>
           <t>就労移行支援からの一般就労等</t>
@@ -2909,10 +3695,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C14" s="21" t="n"/>
-      <c r="D14" s="22" t="n"/>
-      <c r="E14" s="22" t="n"/>
-      <c r="F14" s="22" t="n"/>
+      <c r="C14" s="22" t="n"/>
+      <c r="D14" s="23" t="n"/>
+      <c r="E14" s="23" t="n"/>
+      <c r="F14" s="23" t="n"/>
       <c r="G14" s="4" t="inlineStr">
         <is>
           <t>高齢化が進む本村では主要な減少要因</t>
@@ -2920,29 +3706,29 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="23" t="inlineStr">
+      <c r="A15" s="24" t="inlineStr">
         <is>
           <t>＝　利用者数</t>
         </is>
       </c>
-      <c r="B15" s="24" t="inlineStr">
-        <is>
-          <t>人／月</t>
-        </is>
-      </c>
-      <c r="C15" s="25">
+      <c r="B15" s="25" t="inlineStr">
+        <is>
+          <t>人／月</t>
+        </is>
+      </c>
+      <c r="C15" s="26">
         <f>C8</f>
         <v/>
       </c>
-      <c r="D15" s="25">
+      <c r="D15" s="26">
         <f>D8+SUM(D9:D11)-SUM(D12:D14)</f>
         <v/>
       </c>
-      <c r="E15" s="25">
+      <c r="E15" s="26">
         <f>E8+SUM(E9:E11)-SUM(E12:E14)</f>
         <v/>
       </c>
-      <c r="F15" s="25">
+      <c r="F15" s="26">
         <f>F8+SUM(F9:F11)-SUM(F12:F14)</f>
         <v/>
       </c>
@@ -2963,16 +3749,16 @@
           <t>時間／月</t>
         </is>
       </c>
-      <c r="C16" s="26" t="n">
+      <c r="C16" s="27" t="n">
         <v>10</v>
       </c>
-      <c r="D16" s="26" t="n">
+      <c r="D16" s="27" t="n">
         <v>10</v>
       </c>
-      <c r="E16" s="26" t="n">
+      <c r="E16" s="27" t="n">
         <v>10</v>
       </c>
-      <c r="F16" s="26" t="n">
+      <c r="F16" s="27" t="n">
         <v>10</v>
       </c>
       <c r="G16" s="4" t="inlineStr">
@@ -2982,29 +3768,29 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="23" t="inlineStr">
+      <c r="A17" s="24" t="inlineStr">
         <is>
           <t>＝　月間サービス量</t>
         </is>
       </c>
-      <c r="B17" s="24" t="inlineStr">
+      <c r="B17" s="25" t="inlineStr">
         <is>
           <t>時間／月</t>
         </is>
       </c>
-      <c r="C17" s="27">
+      <c r="C17" s="28">
         <f>ROUND(C15*C16,1)</f>
         <v/>
       </c>
-      <c r="D17" s="27">
+      <c r="D17" s="28">
         <f>ROUND(D15*D16,1)</f>
         <v/>
       </c>
-      <c r="E17" s="27">
+      <c r="E17" s="28">
         <f>ROUND(E15*E16,1)</f>
         <v/>
       </c>
-      <c r="F17" s="27">
+      <c r="F17" s="28">
         <f>ROUND(F15*F16,1)</f>
         <v/>
       </c>
@@ -3015,7 +3801,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="9" t="inlineStr">
+      <c r="A19" s="10" t="inlineStr">
         <is>
           <t>2　生活介護</t>
         </is>
@@ -3077,18 +3863,18 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C22" s="18" t="n">
+      <c r="C22" s="19" t="n">
         <v>6</v>
       </c>
-      <c r="D22" s="19">
+      <c r="D22" s="20">
         <f>C29</f>
         <v/>
       </c>
-      <c r="E22" s="19">
+      <c r="E22" s="20">
         <f>D29</f>
         <v/>
       </c>
-      <c r="F22" s="19">
+      <c r="F22" s="20">
         <f>E29</f>
         <v/>
       </c>
@@ -3109,10 +3895,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C23" s="20" t="n"/>
-      <c r="D23" s="18" t="n"/>
-      <c r="E23" s="18" t="n"/>
-      <c r="F23" s="18" t="n"/>
+      <c r="C23" s="21" t="n"/>
+      <c r="D23" s="19" t="n"/>
+      <c r="E23" s="19" t="n"/>
+      <c r="F23" s="19" t="n"/>
       <c r="G23" s="4" t="inlineStr">
         <is>
           <t>02_年齢到達者一覧から転記する</t>
@@ -3130,10 +3916,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C24" s="20" t="n"/>
-      <c r="D24" s="18" t="n"/>
-      <c r="E24" s="18" t="n"/>
-      <c r="F24" s="18" t="n"/>
+      <c r="C24" s="21" t="n"/>
+      <c r="D24" s="19" t="n"/>
+      <c r="E24" s="19" t="n"/>
+      <c r="F24" s="19" t="n"/>
       <c r="G24" s="4" t="inlineStr">
         <is>
           <t>移行予定者を個別に確認する</t>
@@ -3151,10 +3937,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C25" s="20" t="n"/>
-      <c r="D25" s="18" t="n"/>
-      <c r="E25" s="18" t="n"/>
-      <c r="F25" s="18" t="n"/>
+      <c r="C25" s="21" t="n"/>
+      <c r="D25" s="19" t="n"/>
+      <c r="E25" s="19" t="n"/>
+      <c r="F25" s="19" t="n"/>
       <c r="G25" s="4" t="inlineStr">
         <is>
           <t>相談支援事業所からの利用開始相談を含む</t>
@@ -3172,10 +3958,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C26" s="21" t="n"/>
-      <c r="D26" s="22" t="n"/>
-      <c r="E26" s="22" t="n"/>
-      <c r="F26" s="22" t="n"/>
+      <c r="C26" s="22" t="n"/>
+      <c r="D26" s="23" t="n"/>
+      <c r="E26" s="23" t="n"/>
+      <c r="F26" s="23" t="n"/>
       <c r="G26" s="4" t="inlineStr">
         <is>
           <t>06_65歳移行判定の結果を反映する。一律に減算しない</t>
@@ -3193,10 +3979,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C27" s="21" t="n"/>
-      <c r="D27" s="22" t="n"/>
-      <c r="E27" s="22" t="n"/>
-      <c r="F27" s="22" t="n"/>
+      <c r="C27" s="22" t="n"/>
+      <c r="D27" s="23" t="n"/>
+      <c r="E27" s="23" t="n"/>
+      <c r="F27" s="23" t="n"/>
       <c r="G27" s="4" t="inlineStr">
         <is>
           <t>就労移行支援からの一般就労等</t>
@@ -3214,10 +4000,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C28" s="21" t="n"/>
-      <c r="D28" s="22" t="n"/>
-      <c r="E28" s="22" t="n"/>
-      <c r="F28" s="22" t="n"/>
+      <c r="C28" s="22" t="n"/>
+      <c r="D28" s="23" t="n"/>
+      <c r="E28" s="23" t="n"/>
+      <c r="F28" s="23" t="n"/>
       <c r="G28" s="4" t="inlineStr">
         <is>
           <t>高齢化が進む本村では主要な減少要因</t>
@@ -3225,29 +4011,29 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="23" t="inlineStr">
+      <c r="A29" s="24" t="inlineStr">
         <is>
           <t>＝　利用者数</t>
         </is>
       </c>
-      <c r="B29" s="24" t="inlineStr">
-        <is>
-          <t>人／月</t>
-        </is>
-      </c>
-      <c r="C29" s="25">
+      <c r="B29" s="25" t="inlineStr">
+        <is>
+          <t>人／月</t>
+        </is>
+      </c>
+      <c r="C29" s="26">
         <f>C22</f>
         <v/>
       </c>
-      <c r="D29" s="25">
+      <c r="D29" s="26">
         <f>D22+SUM(D23:D25)-SUM(D26:D28)</f>
         <v/>
       </c>
-      <c r="E29" s="25">
+      <c r="E29" s="26">
         <f>E22+SUM(E23:E25)-SUM(E26:E28)</f>
         <v/>
       </c>
-      <c r="F29" s="25">
+      <c r="F29" s="26">
         <f>F22+SUM(F23:F25)-SUM(F26:F28)</f>
         <v/>
       </c>
@@ -3268,16 +4054,16 @@
           <t>人日／月</t>
         </is>
       </c>
-      <c r="C30" s="26" t="n">
+      <c r="C30" s="27" t="n">
         <v>19.7</v>
       </c>
-      <c r="D30" s="26" t="n">
+      <c r="D30" s="27" t="n">
         <v>19.7</v>
       </c>
-      <c r="E30" s="26" t="n">
+      <c r="E30" s="27" t="n">
         <v>19.7</v>
       </c>
-      <c r="F30" s="26" t="n">
+      <c r="F30" s="27" t="n">
         <v>19.7</v>
       </c>
       <c r="G30" s="4" t="inlineStr">
@@ -3287,29 +4073,29 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="23" t="inlineStr">
+      <c r="A31" s="24" t="inlineStr">
         <is>
           <t>＝　月間サービス量</t>
         </is>
       </c>
-      <c r="B31" s="24" t="inlineStr">
+      <c r="B31" s="25" t="inlineStr">
         <is>
           <t>人日／月</t>
         </is>
       </c>
-      <c r="C31" s="27">
+      <c r="C31" s="28">
         <f>ROUND(C29*C30,1)</f>
         <v/>
       </c>
-      <c r="D31" s="27">
+      <c r="D31" s="28">
         <f>ROUND(D29*D30,1)</f>
         <v/>
       </c>
-      <c r="E31" s="27">
+      <c r="E31" s="28">
         <f>ROUND(E29*E30,1)</f>
         <v/>
       </c>
-      <c r="F31" s="27">
+      <c r="F31" s="28">
         <f>ROUND(F29*F30,1)</f>
         <v/>
       </c>
@@ -3320,7 +4106,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="9" t="inlineStr">
+      <c r="A33" s="10" t="inlineStr">
         <is>
           <t>3　短期入所（福祉型）</t>
         </is>
@@ -3382,18 +4168,18 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C36" s="18" t="n">
+      <c r="C36" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="D36" s="19">
+      <c r="D36" s="20">
         <f>C43</f>
         <v/>
       </c>
-      <c r="E36" s="19">
+      <c r="E36" s="20">
         <f>D43</f>
         <v/>
       </c>
-      <c r="F36" s="19">
+      <c r="F36" s="20">
         <f>E43</f>
         <v/>
       </c>
@@ -3414,10 +4200,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C37" s="20" t="n"/>
-      <c r="D37" s="18" t="n"/>
-      <c r="E37" s="18" t="n"/>
-      <c r="F37" s="18" t="n"/>
+      <c r="C37" s="21" t="n"/>
+      <c r="D37" s="19" t="n"/>
+      <c r="E37" s="19" t="n"/>
+      <c r="F37" s="19" t="n"/>
       <c r="G37" s="4" t="inlineStr">
         <is>
           <t>02_年齢到達者一覧から転記する</t>
@@ -3435,10 +4221,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C38" s="20" t="n"/>
-      <c r="D38" s="18" t="n"/>
-      <c r="E38" s="18" t="n"/>
-      <c r="F38" s="18" t="n"/>
+      <c r="C38" s="21" t="n"/>
+      <c r="D38" s="19" t="n"/>
+      <c r="E38" s="19" t="n"/>
+      <c r="F38" s="19" t="n"/>
       <c r="G38" s="4" t="inlineStr">
         <is>
           <t>移行予定者を個別に確認する</t>
@@ -3456,10 +4242,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C39" s="20" t="n"/>
-      <c r="D39" s="18" t="n"/>
-      <c r="E39" s="18" t="n"/>
-      <c r="F39" s="18" t="n"/>
+      <c r="C39" s="21" t="n"/>
+      <c r="D39" s="19" t="n"/>
+      <c r="E39" s="19" t="n"/>
+      <c r="F39" s="19" t="n"/>
       <c r="G39" s="4" t="inlineStr">
         <is>
           <t>相談支援事業所からの利用開始相談を含む</t>
@@ -3477,10 +4263,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C40" s="21" t="n"/>
-      <c r="D40" s="22" t="n"/>
-      <c r="E40" s="22" t="n"/>
-      <c r="F40" s="22" t="n"/>
+      <c r="C40" s="22" t="n"/>
+      <c r="D40" s="23" t="n"/>
+      <c r="E40" s="23" t="n"/>
+      <c r="F40" s="23" t="n"/>
       <c r="G40" s="4" t="inlineStr">
         <is>
           <t>06_65歳移行判定の結果を反映する。一律に減算しない</t>
@@ -3498,10 +4284,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C41" s="21" t="n"/>
-      <c r="D41" s="22" t="n"/>
-      <c r="E41" s="22" t="n"/>
-      <c r="F41" s="22" t="n"/>
+      <c r="C41" s="22" t="n"/>
+      <c r="D41" s="23" t="n"/>
+      <c r="E41" s="23" t="n"/>
+      <c r="F41" s="23" t="n"/>
       <c r="G41" s="4" t="inlineStr">
         <is>
           <t>就労移行支援からの一般就労等</t>
@@ -3519,10 +4305,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C42" s="21" t="n"/>
-      <c r="D42" s="22" t="n"/>
-      <c r="E42" s="22" t="n"/>
-      <c r="F42" s="22" t="n"/>
+      <c r="C42" s="22" t="n"/>
+      <c r="D42" s="23" t="n"/>
+      <c r="E42" s="23" t="n"/>
+      <c r="F42" s="23" t="n"/>
       <c r="G42" s="4" t="inlineStr">
         <is>
           <t>高齢化が進む本村では主要な減少要因</t>
@@ -3530,29 +4316,29 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="23" t="inlineStr">
+      <c r="A43" s="24" t="inlineStr">
         <is>
           <t>＝　利用者数</t>
         </is>
       </c>
-      <c r="B43" s="24" t="inlineStr">
-        <is>
-          <t>人／月</t>
-        </is>
-      </c>
-      <c r="C43" s="25">
+      <c r="B43" s="25" t="inlineStr">
+        <is>
+          <t>人／月</t>
+        </is>
+      </c>
+      <c r="C43" s="26">
         <f>C36</f>
         <v/>
       </c>
-      <c r="D43" s="25">
+      <c r="D43" s="26">
         <f>D36+SUM(D37:D39)-SUM(D40:D42)</f>
         <v/>
       </c>
-      <c r="E43" s="25">
+      <c r="E43" s="26">
         <f>E36+SUM(E37:E39)-SUM(E40:E42)</f>
         <v/>
       </c>
-      <c r="F43" s="25">
+      <c r="F43" s="26">
         <f>F36+SUM(F37:F39)-SUM(F40:F42)</f>
         <v/>
       </c>
@@ -3573,10 +4359,10 @@
           <t>人日／月</t>
         </is>
       </c>
-      <c r="C44" s="26" t="n"/>
-      <c r="D44" s="26" t="n"/>
-      <c r="E44" s="26" t="n"/>
-      <c r="F44" s="26" t="n"/>
+      <c r="C44" s="27" t="n"/>
+      <c r="D44" s="27" t="n"/>
+      <c r="E44" s="27" t="n"/>
+      <c r="F44" s="27" t="n"/>
       <c r="G44" s="4" t="inlineStr">
         <is>
           <t>利用者ごとの月間予定量の平均</t>
@@ -3584,29 +4370,29 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="23" t="inlineStr">
+      <c r="A45" s="24" t="inlineStr">
         <is>
           <t>＝　月間サービス量</t>
         </is>
       </c>
-      <c r="B45" s="24" t="inlineStr">
+      <c r="B45" s="25" t="inlineStr">
         <is>
           <t>人日／月</t>
         </is>
       </c>
-      <c r="C45" s="27">
+      <c r="C45" s="28">
         <f>ROUND(C43*C44,1)</f>
         <v/>
       </c>
-      <c r="D45" s="27">
+      <c r="D45" s="28">
         <f>ROUND(D43*D44,1)</f>
         <v/>
       </c>
-      <c r="E45" s="27">
+      <c r="E45" s="28">
         <f>ROUND(E43*E44,1)</f>
         <v/>
       </c>
-      <c r="F45" s="27">
+      <c r="F45" s="28">
         <f>ROUND(F43*F44,1)</f>
         <v/>
       </c>
@@ -3617,7 +4403,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="9" t="inlineStr">
+      <c r="A47" s="10" t="inlineStr">
         <is>
           <t>4　自立訓練（生活訓練）</t>
         </is>
@@ -3679,18 +4465,18 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C50" s="18" t="n">
+      <c r="C50" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="D50" s="19">
+      <c r="D50" s="20">
         <f>C57</f>
         <v/>
       </c>
-      <c r="E50" s="19">
+      <c r="E50" s="20">
         <f>D57</f>
         <v/>
       </c>
-      <c r="F50" s="19">
+      <c r="F50" s="20">
         <f>E57</f>
         <v/>
       </c>
@@ -3711,10 +4497,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C51" s="20" t="n"/>
-      <c r="D51" s="18" t="n"/>
-      <c r="E51" s="18" t="n"/>
-      <c r="F51" s="18" t="n"/>
+      <c r="C51" s="21" t="n"/>
+      <c r="D51" s="19" t="n"/>
+      <c r="E51" s="19" t="n"/>
+      <c r="F51" s="19" t="n"/>
       <c r="G51" s="4" t="inlineStr">
         <is>
           <t>02_年齢到達者一覧から転記する</t>
@@ -3732,10 +4518,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C52" s="20" t="n"/>
-      <c r="D52" s="18" t="n"/>
-      <c r="E52" s="18" t="n"/>
-      <c r="F52" s="18" t="n"/>
+      <c r="C52" s="21" t="n"/>
+      <c r="D52" s="19" t="n"/>
+      <c r="E52" s="19" t="n"/>
+      <c r="F52" s="19" t="n"/>
       <c r="G52" s="4" t="inlineStr">
         <is>
           <t>移行予定者を個別に確認する</t>
@@ -3753,10 +4539,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C53" s="20" t="n"/>
-      <c r="D53" s="18" t="n"/>
-      <c r="E53" s="18" t="n"/>
-      <c r="F53" s="18" t="n"/>
+      <c r="C53" s="21" t="n"/>
+      <c r="D53" s="19" t="n"/>
+      <c r="E53" s="19" t="n"/>
+      <c r="F53" s="19" t="n"/>
       <c r="G53" s="4" t="inlineStr">
         <is>
           <t>相談支援事業所からの利用開始相談を含む</t>
@@ -3774,10 +4560,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C54" s="21" t="n"/>
-      <c r="D54" s="22" t="n"/>
-      <c r="E54" s="22" t="n"/>
-      <c r="F54" s="22" t="n"/>
+      <c r="C54" s="22" t="n"/>
+      <c r="D54" s="23" t="n"/>
+      <c r="E54" s="23" t="n"/>
+      <c r="F54" s="23" t="n"/>
       <c r="G54" s="4" t="inlineStr">
         <is>
           <t>06_65歳移行判定の結果を反映する。一律に減算しない</t>
@@ -3795,10 +4581,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C55" s="21" t="n"/>
-      <c r="D55" s="22" t="n"/>
-      <c r="E55" s="22" t="n"/>
-      <c r="F55" s="22" t="n"/>
+      <c r="C55" s="22" t="n"/>
+      <c r="D55" s="23" t="n"/>
+      <c r="E55" s="23" t="n"/>
+      <c r="F55" s="23" t="n"/>
       <c r="G55" s="4" t="inlineStr">
         <is>
           <t>就労移行支援からの一般就労等</t>
@@ -3816,10 +4602,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C56" s="21" t="n"/>
-      <c r="D56" s="22" t="n"/>
-      <c r="E56" s="22" t="n"/>
-      <c r="F56" s="22" t="n"/>
+      <c r="C56" s="22" t="n"/>
+      <c r="D56" s="23" t="n"/>
+      <c r="E56" s="23" t="n"/>
+      <c r="F56" s="23" t="n"/>
       <c r="G56" s="4" t="inlineStr">
         <is>
           <t>高齢化が進む本村では主要な減少要因</t>
@@ -3827,29 +4613,29 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="23" t="inlineStr">
+      <c r="A57" s="24" t="inlineStr">
         <is>
           <t>＝　利用者数</t>
         </is>
       </c>
-      <c r="B57" s="24" t="inlineStr">
-        <is>
-          <t>人／月</t>
-        </is>
-      </c>
-      <c r="C57" s="25">
+      <c r="B57" s="25" t="inlineStr">
+        <is>
+          <t>人／月</t>
+        </is>
+      </c>
+      <c r="C57" s="26">
         <f>C50</f>
         <v/>
       </c>
-      <c r="D57" s="25">
+      <c r="D57" s="26">
         <f>D50+SUM(D51:D53)-SUM(D54:D56)</f>
         <v/>
       </c>
-      <c r="E57" s="25">
+      <c r="E57" s="26">
         <f>E50+SUM(E51:E53)-SUM(E54:E56)</f>
         <v/>
       </c>
-      <c r="F57" s="25">
+      <c r="F57" s="26">
         <f>F50+SUM(F51:F53)-SUM(F54:F56)</f>
         <v/>
       </c>
@@ -3870,16 +4656,16 @@
           <t>人日／月</t>
         </is>
       </c>
-      <c r="C58" s="26" t="n">
+      <c r="C58" s="27" t="n">
         <v>12</v>
       </c>
-      <c r="D58" s="26" t="n">
+      <c r="D58" s="27" t="n">
         <v>12</v>
       </c>
-      <c r="E58" s="26" t="n">
+      <c r="E58" s="27" t="n">
         <v>12</v>
       </c>
-      <c r="F58" s="26" t="n">
+      <c r="F58" s="27" t="n">
         <v>12</v>
       </c>
       <c r="G58" s="4" t="inlineStr">
@@ -3889,29 +4675,29 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="23" t="inlineStr">
+      <c r="A59" s="24" t="inlineStr">
         <is>
           <t>＝　月間サービス量</t>
         </is>
       </c>
-      <c r="B59" s="24" t="inlineStr">
+      <c r="B59" s="25" t="inlineStr">
         <is>
           <t>人日／月</t>
         </is>
       </c>
-      <c r="C59" s="27">
+      <c r="C59" s="28">
         <f>ROUND(C57*C58,1)</f>
         <v/>
       </c>
-      <c r="D59" s="27">
+      <c r="D59" s="28">
         <f>ROUND(D57*D58,1)</f>
         <v/>
       </c>
-      <c r="E59" s="27">
+      <c r="E59" s="28">
         <f>ROUND(E57*E58,1)</f>
         <v/>
       </c>
-      <c r="F59" s="27">
+      <c r="F59" s="28">
         <f>ROUND(F57*F58,1)</f>
         <v/>
       </c>
@@ -3922,7 +4708,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="9" t="inlineStr">
+      <c r="A61" s="10" t="inlineStr">
         <is>
           <t>5　就労選択支援</t>
         </is>
@@ -3984,18 +4770,18 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C64" s="18" t="n">
+      <c r="C64" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="D64" s="19">
+      <c r="D64" s="20">
         <f>C71</f>
         <v/>
       </c>
-      <c r="E64" s="19">
+      <c r="E64" s="20">
         <f>D71</f>
         <v/>
       </c>
-      <c r="F64" s="19">
+      <c r="F64" s="20">
         <f>E71</f>
         <v/>
       </c>
@@ -4016,10 +4802,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C65" s="20" t="n"/>
-      <c r="D65" s="18" t="n"/>
-      <c r="E65" s="18" t="n"/>
-      <c r="F65" s="18" t="n"/>
+      <c r="C65" s="21" t="n"/>
+      <c r="D65" s="19" t="n"/>
+      <c r="E65" s="19" t="n"/>
+      <c r="F65" s="19" t="n"/>
       <c r="G65" s="4" t="inlineStr">
         <is>
           <t>02_年齢到達者一覧から転記する</t>
@@ -4037,10 +4823,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C66" s="20" t="n"/>
-      <c r="D66" s="18" t="n"/>
-      <c r="E66" s="18" t="n"/>
-      <c r="F66" s="18" t="n"/>
+      <c r="C66" s="21" t="n"/>
+      <c r="D66" s="19" t="n"/>
+      <c r="E66" s="19" t="n"/>
+      <c r="F66" s="19" t="n"/>
       <c r="G66" s="4" t="inlineStr">
         <is>
           <t>移行予定者を個別に確認する</t>
@@ -4058,10 +4844,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C67" s="20" t="n"/>
-      <c r="D67" s="18" t="n"/>
-      <c r="E67" s="18" t="n"/>
-      <c r="F67" s="18" t="n"/>
+      <c r="C67" s="21" t="n"/>
+      <c r="D67" s="19" t="n"/>
+      <c r="E67" s="19" t="n"/>
+      <c r="F67" s="19" t="n"/>
       <c r="G67" s="4" t="inlineStr">
         <is>
           <t>相談支援事業所からの利用開始相談を含む</t>
@@ -4079,10 +4865,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C68" s="21" t="n"/>
-      <c r="D68" s="22" t="n"/>
-      <c r="E68" s="22" t="n"/>
-      <c r="F68" s="22" t="n"/>
+      <c r="C68" s="22" t="n"/>
+      <c r="D68" s="23" t="n"/>
+      <c r="E68" s="23" t="n"/>
+      <c r="F68" s="23" t="n"/>
       <c r="G68" s="4" t="inlineStr">
         <is>
           <t>06_65歳移行判定の結果を反映する。一律に減算しない</t>
@@ -4100,10 +4886,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C69" s="21" t="n"/>
-      <c r="D69" s="22" t="n"/>
-      <c r="E69" s="22" t="n"/>
-      <c r="F69" s="22" t="n"/>
+      <c r="C69" s="22" t="n"/>
+      <c r="D69" s="23" t="n"/>
+      <c r="E69" s="23" t="n"/>
+      <c r="F69" s="23" t="n"/>
       <c r="G69" s="4" t="inlineStr">
         <is>
           <t>就労移行支援からの一般就労等</t>
@@ -4121,10 +4907,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C70" s="21" t="n"/>
-      <c r="D70" s="22" t="n"/>
-      <c r="E70" s="22" t="n"/>
-      <c r="F70" s="22" t="n"/>
+      <c r="C70" s="22" t="n"/>
+      <c r="D70" s="23" t="n"/>
+      <c r="E70" s="23" t="n"/>
+      <c r="F70" s="23" t="n"/>
       <c r="G70" s="4" t="inlineStr">
         <is>
           <t>高齢化が進む本村では主要な減少要因</t>
@@ -4132,29 +4918,29 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="23" t="inlineStr">
+      <c r="A71" s="24" t="inlineStr">
         <is>
           <t>＝　利用者数</t>
         </is>
       </c>
-      <c r="B71" s="24" t="inlineStr">
-        <is>
-          <t>人／月</t>
-        </is>
-      </c>
-      <c r="C71" s="25">
+      <c r="B71" s="25" t="inlineStr">
+        <is>
+          <t>人／月</t>
+        </is>
+      </c>
+      <c r="C71" s="26">
         <f>C64</f>
         <v/>
       </c>
-      <c r="D71" s="25">
+      <c r="D71" s="26">
         <f>D64+SUM(D65:D67)-SUM(D68:D70)</f>
         <v/>
       </c>
-      <c r="E71" s="25">
+      <c r="E71" s="26">
         <f>E64+SUM(E65:E67)-SUM(E68:E70)</f>
         <v/>
       </c>
-      <c r="F71" s="25">
+      <c r="F71" s="26">
         <f>F64+SUM(F65:F67)-SUM(F68:F70)</f>
         <v/>
       </c>
@@ -4175,10 +4961,10 @@
           <t>―</t>
         </is>
       </c>
-      <c r="C72" s="26" t="n"/>
-      <c r="D72" s="26" t="n"/>
-      <c r="E72" s="26" t="n"/>
-      <c r="F72" s="26" t="n"/>
+      <c r="C72" s="27" t="n"/>
+      <c r="D72" s="27" t="n"/>
+      <c r="E72" s="27" t="n"/>
+      <c r="F72" s="27" t="n"/>
       <c r="G72" s="4" t="inlineStr">
         <is>
           <t>利用者ごとの月間予定量の平均</t>
@@ -4186,29 +4972,29 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="23" t="inlineStr">
+      <c r="A73" s="24" t="inlineStr">
         <is>
           <t>＝　月間サービス量</t>
         </is>
       </c>
-      <c r="B73" s="24" t="inlineStr">
+      <c r="B73" s="25" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="C73" s="27">
+      <c r="C73" s="28">
         <f>ROUND(C71*C72,1)</f>
         <v/>
       </c>
-      <c r="D73" s="27">
+      <c r="D73" s="28">
         <f>ROUND(D71*D72,1)</f>
         <v/>
       </c>
-      <c r="E73" s="27">
+      <c r="E73" s="28">
         <f>ROUND(E71*E72,1)</f>
         <v/>
       </c>
-      <c r="F73" s="27">
+      <c r="F73" s="28">
         <f>ROUND(F71*F72,1)</f>
         <v/>
       </c>
@@ -4219,7 +5005,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="9" t="inlineStr">
+      <c r="A75" s="10" t="inlineStr">
         <is>
           <t>6　就労移行支援</t>
         </is>
@@ -4281,18 +5067,18 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C78" s="18" t="n">
+      <c r="C78" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="D78" s="19">
+      <c r="D78" s="20">
         <f>C85</f>
         <v/>
       </c>
-      <c r="E78" s="19">
+      <c r="E78" s="20">
         <f>D85</f>
         <v/>
       </c>
-      <c r="F78" s="19">
+      <c r="F78" s="20">
         <f>E85</f>
         <v/>
       </c>
@@ -4313,10 +5099,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C79" s="20" t="n"/>
-      <c r="D79" s="18" t="n"/>
-      <c r="E79" s="18" t="n"/>
-      <c r="F79" s="18" t="n"/>
+      <c r="C79" s="21" t="n"/>
+      <c r="D79" s="19" t="n"/>
+      <c r="E79" s="19" t="n"/>
+      <c r="F79" s="19" t="n"/>
       <c r="G79" s="4" t="inlineStr">
         <is>
           <t>02_年齢到達者一覧から転記する</t>
@@ -4334,10 +5120,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C80" s="20" t="n"/>
-      <c r="D80" s="18" t="n"/>
-      <c r="E80" s="18" t="n"/>
-      <c r="F80" s="18" t="n"/>
+      <c r="C80" s="21" t="n"/>
+      <c r="D80" s="19" t="n"/>
+      <c r="E80" s="19" t="n"/>
+      <c r="F80" s="19" t="n"/>
       <c r="G80" s="4" t="inlineStr">
         <is>
           <t>移行予定者を個別に確認する</t>
@@ -4355,10 +5141,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C81" s="20" t="n"/>
-      <c r="D81" s="18" t="n"/>
-      <c r="E81" s="18" t="n"/>
-      <c r="F81" s="18" t="n"/>
+      <c r="C81" s="21" t="n"/>
+      <c r="D81" s="19" t="n"/>
+      <c r="E81" s="19" t="n"/>
+      <c r="F81" s="19" t="n"/>
       <c r="G81" s="4" t="inlineStr">
         <is>
           <t>相談支援事業所からの利用開始相談を含む</t>
@@ -4376,10 +5162,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C82" s="21" t="n"/>
-      <c r="D82" s="22" t="n"/>
-      <c r="E82" s="22" t="n"/>
-      <c r="F82" s="22" t="n"/>
+      <c r="C82" s="22" t="n"/>
+      <c r="D82" s="23" t="n"/>
+      <c r="E82" s="23" t="n"/>
+      <c r="F82" s="23" t="n"/>
       <c r="G82" s="4" t="inlineStr">
         <is>
           <t>06_65歳移行判定の結果を反映する。一律に減算しない</t>
@@ -4397,10 +5183,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C83" s="21" t="n"/>
-      <c r="D83" s="22" t="n"/>
-      <c r="E83" s="22" t="n"/>
-      <c r="F83" s="22" t="n"/>
+      <c r="C83" s="22" t="n"/>
+      <c r="D83" s="23" t="n"/>
+      <c r="E83" s="23" t="n"/>
+      <c r="F83" s="23" t="n"/>
       <c r="G83" s="4" t="inlineStr">
         <is>
           <t>就労移行支援からの一般就労等</t>
@@ -4418,10 +5204,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C84" s="21" t="n"/>
-      <c r="D84" s="22" t="n"/>
-      <c r="E84" s="22" t="n"/>
-      <c r="F84" s="22" t="n"/>
+      <c r="C84" s="22" t="n"/>
+      <c r="D84" s="23" t="n"/>
+      <c r="E84" s="23" t="n"/>
+      <c r="F84" s="23" t="n"/>
       <c r="G84" s="4" t="inlineStr">
         <is>
           <t>高齢化が進む本村では主要な減少要因</t>
@@ -4429,29 +5215,29 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="23" t="inlineStr">
+      <c r="A85" s="24" t="inlineStr">
         <is>
           <t>＝　利用者数</t>
         </is>
       </c>
-      <c r="B85" s="24" t="inlineStr">
-        <is>
-          <t>人／月</t>
-        </is>
-      </c>
-      <c r="C85" s="25">
+      <c r="B85" s="25" t="inlineStr">
+        <is>
+          <t>人／月</t>
+        </is>
+      </c>
+      <c r="C85" s="26">
         <f>C78</f>
         <v/>
       </c>
-      <c r="D85" s="25">
+      <c r="D85" s="26">
         <f>D78+SUM(D79:D81)-SUM(D82:D84)</f>
         <v/>
       </c>
-      <c r="E85" s="25">
+      <c r="E85" s="26">
         <f>E78+SUM(E79:E81)-SUM(E82:E84)</f>
         <v/>
       </c>
-      <c r="F85" s="25">
+      <c r="F85" s="26">
         <f>F78+SUM(F79:F81)-SUM(F82:F84)</f>
         <v/>
       </c>
@@ -4472,16 +5258,16 @@
           <t>人日／月</t>
         </is>
       </c>
-      <c r="C86" s="26" t="n">
+      <c r="C86" s="27" t="n">
         <v>10</v>
       </c>
-      <c r="D86" s="26" t="n">
+      <c r="D86" s="27" t="n">
         <v>10</v>
       </c>
-      <c r="E86" s="26" t="n">
+      <c r="E86" s="27" t="n">
         <v>10</v>
       </c>
-      <c r="F86" s="26" t="n">
+      <c r="F86" s="27" t="n">
         <v>10</v>
       </c>
       <c r="G86" s="4" t="inlineStr">
@@ -4491,29 +5277,29 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="23" t="inlineStr">
+      <c r="A87" s="24" t="inlineStr">
         <is>
           <t>＝　月間サービス量</t>
         </is>
       </c>
-      <c r="B87" s="24" t="inlineStr">
+      <c r="B87" s="25" t="inlineStr">
         <is>
           <t>人日／月</t>
         </is>
       </c>
-      <c r="C87" s="27">
+      <c r="C87" s="28">
         <f>ROUND(C85*C86,1)</f>
         <v/>
       </c>
-      <c r="D87" s="27">
+      <c r="D87" s="28">
         <f>ROUND(D85*D86,1)</f>
         <v/>
       </c>
-      <c r="E87" s="27">
+      <c r="E87" s="28">
         <f>ROUND(E85*E86,1)</f>
         <v/>
       </c>
-      <c r="F87" s="27">
+      <c r="F87" s="28">
         <f>ROUND(F85*F86,1)</f>
         <v/>
       </c>
@@ -4524,7 +5310,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="9" t="inlineStr">
+      <c r="A89" s="10" t="inlineStr">
         <is>
           <t>7　就労継続支援A型</t>
         </is>
@@ -4586,18 +5372,18 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C92" s="18" t="n">
+      <c r="C92" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="D92" s="19">
+      <c r="D92" s="20">
         <f>C99</f>
         <v/>
       </c>
-      <c r="E92" s="19">
+      <c r="E92" s="20">
         <f>D99</f>
         <v/>
       </c>
-      <c r="F92" s="19">
+      <c r="F92" s="20">
         <f>E99</f>
         <v/>
       </c>
@@ -4618,10 +5404,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C93" s="20" t="n"/>
-      <c r="D93" s="18" t="n"/>
-      <c r="E93" s="18" t="n"/>
-      <c r="F93" s="18" t="n"/>
+      <c r="C93" s="21" t="n"/>
+      <c r="D93" s="19" t="n"/>
+      <c r="E93" s="19" t="n"/>
+      <c r="F93" s="19" t="n"/>
       <c r="G93" s="4" t="inlineStr">
         <is>
           <t>02_年齢到達者一覧から転記する</t>
@@ -4639,10 +5425,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C94" s="20" t="n"/>
-      <c r="D94" s="18" t="n"/>
-      <c r="E94" s="18" t="n"/>
-      <c r="F94" s="18" t="n"/>
+      <c r="C94" s="21" t="n"/>
+      <c r="D94" s="19" t="n"/>
+      <c r="E94" s="19" t="n"/>
+      <c r="F94" s="19" t="n"/>
       <c r="G94" s="4" t="inlineStr">
         <is>
           <t>移行予定者を個別に確認する</t>
@@ -4660,10 +5446,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C95" s="20" t="n"/>
-      <c r="D95" s="18" t="n"/>
-      <c r="E95" s="18" t="n"/>
-      <c r="F95" s="18" t="n"/>
+      <c r="C95" s="21" t="n"/>
+      <c r="D95" s="19" t="n"/>
+      <c r="E95" s="19" t="n"/>
+      <c r="F95" s="19" t="n"/>
       <c r="G95" s="4" t="inlineStr">
         <is>
           <t>相談支援事業所からの利用開始相談を含む</t>
@@ -4681,10 +5467,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C96" s="21" t="n"/>
-      <c r="D96" s="22" t="n"/>
-      <c r="E96" s="22" t="n"/>
-      <c r="F96" s="22" t="n"/>
+      <c r="C96" s="22" t="n"/>
+      <c r="D96" s="23" t="n"/>
+      <c r="E96" s="23" t="n"/>
+      <c r="F96" s="23" t="n"/>
       <c r="G96" s="4" t="inlineStr">
         <is>
           <t>06_65歳移行判定の結果を反映する。一律に減算しない</t>
@@ -4702,10 +5488,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C97" s="21" t="n"/>
-      <c r="D97" s="22" t="n"/>
-      <c r="E97" s="22" t="n"/>
-      <c r="F97" s="22" t="n"/>
+      <c r="C97" s="22" t="n"/>
+      <c r="D97" s="23" t="n"/>
+      <c r="E97" s="23" t="n"/>
+      <c r="F97" s="23" t="n"/>
       <c r="G97" s="4" t="inlineStr">
         <is>
           <t>就労移行支援からの一般就労等</t>
@@ -4723,10 +5509,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C98" s="21" t="n"/>
-      <c r="D98" s="22" t="n"/>
-      <c r="E98" s="22" t="n"/>
-      <c r="F98" s="22" t="n"/>
+      <c r="C98" s="22" t="n"/>
+      <c r="D98" s="23" t="n"/>
+      <c r="E98" s="23" t="n"/>
+      <c r="F98" s="23" t="n"/>
       <c r="G98" s="4" t="inlineStr">
         <is>
           <t>高齢化が進む本村では主要な減少要因</t>
@@ -4734,29 +5520,29 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="23" t="inlineStr">
+      <c r="A99" s="24" t="inlineStr">
         <is>
           <t>＝　利用者数</t>
         </is>
       </c>
-      <c r="B99" s="24" t="inlineStr">
-        <is>
-          <t>人／月</t>
-        </is>
-      </c>
-      <c r="C99" s="25">
+      <c r="B99" s="25" t="inlineStr">
+        <is>
+          <t>人／月</t>
+        </is>
+      </c>
+      <c r="C99" s="26">
         <f>C92</f>
         <v/>
       </c>
-      <c r="D99" s="25">
+      <c r="D99" s="26">
         <f>D92+SUM(D93:D95)-SUM(D96:D98)</f>
         <v/>
       </c>
-      <c r="E99" s="25">
+      <c r="E99" s="26">
         <f>E92+SUM(E93:E95)-SUM(E96:E98)</f>
         <v/>
       </c>
-      <c r="F99" s="25">
+      <c r="F99" s="26">
         <f>F92+SUM(F93:F95)-SUM(F96:F98)</f>
         <v/>
       </c>
@@ -4777,16 +5563,16 @@
           <t>人日／月</t>
         </is>
       </c>
-      <c r="C100" s="26" t="n">
+      <c r="C100" s="27" t="n">
         <v>19</v>
       </c>
-      <c r="D100" s="26" t="n">
+      <c r="D100" s="27" t="n">
         <v>19</v>
       </c>
-      <c r="E100" s="26" t="n">
+      <c r="E100" s="27" t="n">
         <v>19</v>
       </c>
-      <c r="F100" s="26" t="n">
+      <c r="F100" s="27" t="n">
         <v>19</v>
       </c>
       <c r="G100" s="4" t="inlineStr">
@@ -4796,29 +5582,29 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="23" t="inlineStr">
+      <c r="A101" s="24" t="inlineStr">
         <is>
           <t>＝　月間サービス量</t>
         </is>
       </c>
-      <c r="B101" s="24" t="inlineStr">
+      <c r="B101" s="25" t="inlineStr">
         <is>
           <t>人日／月</t>
         </is>
       </c>
-      <c r="C101" s="27">
+      <c r="C101" s="28">
         <f>ROUND(C99*C100,1)</f>
         <v/>
       </c>
-      <c r="D101" s="27">
+      <c r="D101" s="28">
         <f>ROUND(D99*D100,1)</f>
         <v/>
       </c>
-      <c r="E101" s="27">
+      <c r="E101" s="28">
         <f>ROUND(E99*E100,1)</f>
         <v/>
       </c>
-      <c r="F101" s="27">
+      <c r="F101" s="28">
         <f>ROUND(F99*F100,1)</f>
         <v/>
       </c>
@@ -4829,7 +5615,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="9" t="inlineStr">
+      <c r="A103" s="10" t="inlineStr">
         <is>
           <t>8　就労継続支援B型</t>
         </is>
@@ -4891,18 +5677,18 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C106" s="18" t="n">
+      <c r="C106" s="19" t="n">
         <v>11</v>
       </c>
-      <c r="D106" s="19">
+      <c r="D106" s="20">
         <f>C113</f>
         <v/>
       </c>
-      <c r="E106" s="19">
+      <c r="E106" s="20">
         <f>D113</f>
         <v/>
       </c>
-      <c r="F106" s="19">
+      <c r="F106" s="20">
         <f>E113</f>
         <v/>
       </c>
@@ -4923,10 +5709,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C107" s="20" t="n"/>
-      <c r="D107" s="18" t="n"/>
-      <c r="E107" s="18" t="n"/>
-      <c r="F107" s="18" t="n"/>
+      <c r="C107" s="21" t="n"/>
+      <c r="D107" s="19" t="n"/>
+      <c r="E107" s="19" t="n"/>
+      <c r="F107" s="19" t="n"/>
       <c r="G107" s="4" t="inlineStr">
         <is>
           <t>02_年齢到達者一覧から転記する</t>
@@ -4944,10 +5730,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C108" s="20" t="n"/>
-      <c r="D108" s="18" t="n"/>
-      <c r="E108" s="18" t="n"/>
-      <c r="F108" s="18" t="n"/>
+      <c r="C108" s="21" t="n"/>
+      <c r="D108" s="19" t="n"/>
+      <c r="E108" s="19" t="n"/>
+      <c r="F108" s="19" t="n"/>
       <c r="G108" s="4" t="inlineStr">
         <is>
           <t>移行予定者を個別に確認する</t>
@@ -4965,10 +5751,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C109" s="20" t="n"/>
-      <c r="D109" s="18" t="n"/>
-      <c r="E109" s="18" t="n"/>
-      <c r="F109" s="18" t="n"/>
+      <c r="C109" s="21" t="n"/>
+      <c r="D109" s="19" t="n"/>
+      <c r="E109" s="19" t="n"/>
+      <c r="F109" s="19" t="n"/>
       <c r="G109" s="4" t="inlineStr">
         <is>
           <t>相談支援事業所からの利用開始相談を含む</t>
@@ -4986,10 +5772,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C110" s="21" t="n"/>
-      <c r="D110" s="22" t="n"/>
-      <c r="E110" s="22" t="n"/>
-      <c r="F110" s="22" t="n"/>
+      <c r="C110" s="22" t="n"/>
+      <c r="D110" s="23" t="n"/>
+      <c r="E110" s="23" t="n"/>
+      <c r="F110" s="23" t="n"/>
       <c r="G110" s="4" t="inlineStr">
         <is>
           <t>06_65歳移行判定の結果を反映する。一律に減算しない</t>
@@ -5007,10 +5793,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C111" s="21" t="n"/>
-      <c r="D111" s="22" t="n"/>
-      <c r="E111" s="22" t="n"/>
-      <c r="F111" s="22" t="n"/>
+      <c r="C111" s="22" t="n"/>
+      <c r="D111" s="23" t="n"/>
+      <c r="E111" s="23" t="n"/>
+      <c r="F111" s="23" t="n"/>
       <c r="G111" s="4" t="inlineStr">
         <is>
           <t>就労移行支援からの一般就労等</t>
@@ -5028,10 +5814,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C112" s="21" t="n"/>
-      <c r="D112" s="22" t="n"/>
-      <c r="E112" s="22" t="n"/>
-      <c r="F112" s="22" t="n"/>
+      <c r="C112" s="22" t="n"/>
+      <c r="D112" s="23" t="n"/>
+      <c r="E112" s="23" t="n"/>
+      <c r="F112" s="23" t="n"/>
       <c r="G112" s="4" t="inlineStr">
         <is>
           <t>高齢化が進む本村では主要な減少要因</t>
@@ -5039,29 +5825,29 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="23" t="inlineStr">
+      <c r="A113" s="24" t="inlineStr">
         <is>
           <t>＝　利用者数</t>
         </is>
       </c>
-      <c r="B113" s="24" t="inlineStr">
-        <is>
-          <t>人／月</t>
-        </is>
-      </c>
-      <c r="C113" s="25">
+      <c r="B113" s="25" t="inlineStr">
+        <is>
+          <t>人／月</t>
+        </is>
+      </c>
+      <c r="C113" s="26">
         <f>C106</f>
         <v/>
       </c>
-      <c r="D113" s="25">
+      <c r="D113" s="26">
         <f>D106+SUM(D107:D109)-SUM(D110:D112)</f>
         <v/>
       </c>
-      <c r="E113" s="25">
+      <c r="E113" s="26">
         <f>E106+SUM(E107:E109)-SUM(E110:E112)</f>
         <v/>
       </c>
-      <c r="F113" s="25">
+      <c r="F113" s="26">
         <f>F106+SUM(F107:F109)-SUM(F110:F112)</f>
         <v/>
       </c>
@@ -5082,16 +5868,16 @@
           <t>人日／月</t>
         </is>
       </c>
-      <c r="C114" s="26" t="n">
+      <c r="C114" s="27" t="n">
         <v>18.2</v>
       </c>
-      <c r="D114" s="26" t="n">
+      <c r="D114" s="27" t="n">
         <v>18.2</v>
       </c>
-      <c r="E114" s="26" t="n">
+      <c r="E114" s="27" t="n">
         <v>18.2</v>
       </c>
-      <c r="F114" s="26" t="n">
+      <c r="F114" s="27" t="n">
         <v>18.2</v>
       </c>
       <c r="G114" s="4" t="inlineStr">
@@ -5101,29 +5887,29 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="23" t="inlineStr">
+      <c r="A115" s="24" t="inlineStr">
         <is>
           <t>＝　月間サービス量</t>
         </is>
       </c>
-      <c r="B115" s="24" t="inlineStr">
+      <c r="B115" s="25" t="inlineStr">
         <is>
           <t>人日／月</t>
         </is>
       </c>
-      <c r="C115" s="27">
+      <c r="C115" s="28">
         <f>ROUND(C113*C114,1)</f>
         <v/>
       </c>
-      <c r="D115" s="27">
+      <c r="D115" s="28">
         <f>ROUND(D113*D114,1)</f>
         <v/>
       </c>
-      <c r="E115" s="27">
+      <c r="E115" s="28">
         <f>ROUND(E113*E114,1)</f>
         <v/>
       </c>
-      <c r="F115" s="27">
+      <c r="F115" s="28">
         <f>ROUND(F113*F114,1)</f>
         <v/>
       </c>
@@ -5134,7 +5920,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="9" t="inlineStr">
+      <c r="A117" s="10" t="inlineStr">
         <is>
           <t>9　就労定着支援</t>
         </is>
@@ -5196,18 +5982,18 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C120" s="18" t="n">
+      <c r="C120" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="D120" s="19">
+      <c r="D120" s="20">
         <f>C127</f>
         <v/>
       </c>
-      <c r="E120" s="19">
+      <c r="E120" s="20">
         <f>D127</f>
         <v/>
       </c>
-      <c r="F120" s="19">
+      <c r="F120" s="20">
         <f>E127</f>
         <v/>
       </c>
@@ -5228,10 +6014,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C121" s="20" t="n"/>
-      <c r="D121" s="18" t="n"/>
-      <c r="E121" s="18" t="n"/>
-      <c r="F121" s="18" t="n"/>
+      <c r="C121" s="21" t="n"/>
+      <c r="D121" s="19" t="n"/>
+      <c r="E121" s="19" t="n"/>
+      <c r="F121" s="19" t="n"/>
       <c r="G121" s="4" t="inlineStr">
         <is>
           <t>02_年齢到達者一覧から転記する</t>
@@ -5249,10 +6035,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C122" s="20" t="n"/>
-      <c r="D122" s="18" t="n"/>
-      <c r="E122" s="18" t="n"/>
-      <c r="F122" s="18" t="n"/>
+      <c r="C122" s="21" t="n"/>
+      <c r="D122" s="19" t="n"/>
+      <c r="E122" s="19" t="n"/>
+      <c r="F122" s="19" t="n"/>
       <c r="G122" s="4" t="inlineStr">
         <is>
           <t>移行予定者を個別に確認する</t>
@@ -5270,10 +6056,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C123" s="20" t="n"/>
-      <c r="D123" s="18" t="n"/>
-      <c r="E123" s="18" t="n"/>
-      <c r="F123" s="18" t="n"/>
+      <c r="C123" s="21" t="n"/>
+      <c r="D123" s="19" t="n"/>
+      <c r="E123" s="19" t="n"/>
+      <c r="F123" s="19" t="n"/>
       <c r="G123" s="4" t="inlineStr">
         <is>
           <t>相談支援事業所からの利用開始相談を含む</t>
@@ -5291,10 +6077,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C124" s="21" t="n"/>
-      <c r="D124" s="22" t="n"/>
-      <c r="E124" s="22" t="n"/>
-      <c r="F124" s="22" t="n"/>
+      <c r="C124" s="22" t="n"/>
+      <c r="D124" s="23" t="n"/>
+      <c r="E124" s="23" t="n"/>
+      <c r="F124" s="23" t="n"/>
       <c r="G124" s="4" t="inlineStr">
         <is>
           <t>06_65歳移行判定の結果を反映する。一律に減算しない</t>
@@ -5312,10 +6098,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C125" s="21" t="n"/>
-      <c r="D125" s="22" t="n"/>
-      <c r="E125" s="22" t="n"/>
-      <c r="F125" s="22" t="n"/>
+      <c r="C125" s="22" t="n"/>
+      <c r="D125" s="23" t="n"/>
+      <c r="E125" s="23" t="n"/>
+      <c r="F125" s="23" t="n"/>
       <c r="G125" s="4" t="inlineStr">
         <is>
           <t>就労移行支援からの一般就労等</t>
@@ -5333,10 +6119,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C126" s="21" t="n"/>
-      <c r="D126" s="22" t="n"/>
-      <c r="E126" s="22" t="n"/>
-      <c r="F126" s="22" t="n"/>
+      <c r="C126" s="22" t="n"/>
+      <c r="D126" s="23" t="n"/>
+      <c r="E126" s="23" t="n"/>
+      <c r="F126" s="23" t="n"/>
       <c r="G126" s="4" t="inlineStr">
         <is>
           <t>高齢化が進む本村では主要な減少要因</t>
@@ -5344,29 +6130,29 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="23" t="inlineStr">
+      <c r="A127" s="24" t="inlineStr">
         <is>
           <t>＝　利用者数</t>
         </is>
       </c>
-      <c r="B127" s="24" t="inlineStr">
-        <is>
-          <t>人／月</t>
-        </is>
-      </c>
-      <c r="C127" s="25">
+      <c r="B127" s="25" t="inlineStr">
+        <is>
+          <t>人／月</t>
+        </is>
+      </c>
+      <c r="C127" s="26">
         <f>C120</f>
         <v/>
       </c>
-      <c r="D127" s="25">
+      <c r="D127" s="26">
         <f>D120+SUM(D121:D123)-SUM(D124:D126)</f>
         <v/>
       </c>
-      <c r="E127" s="25">
+      <c r="E127" s="26">
         <f>E120+SUM(E121:E123)-SUM(E124:E126)</f>
         <v/>
       </c>
-      <c r="F127" s="25">
+      <c r="F127" s="26">
         <f>F120+SUM(F121:F123)-SUM(F124:F126)</f>
         <v/>
       </c>
@@ -5387,10 +6173,10 @@
           <t>―</t>
         </is>
       </c>
-      <c r="C128" s="26" t="n"/>
-      <c r="D128" s="26" t="n"/>
-      <c r="E128" s="26" t="n"/>
-      <c r="F128" s="26" t="n"/>
+      <c r="C128" s="27" t="n"/>
+      <c r="D128" s="27" t="n"/>
+      <c r="E128" s="27" t="n"/>
+      <c r="F128" s="27" t="n"/>
       <c r="G128" s="4" t="inlineStr">
         <is>
           <t>利用者ごとの月間予定量の平均</t>
@@ -5398,29 +6184,29 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="23" t="inlineStr">
+      <c r="A129" s="24" t="inlineStr">
         <is>
           <t>＝　月間サービス量</t>
         </is>
       </c>
-      <c r="B129" s="24" t="inlineStr">
+      <c r="B129" s="25" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="C129" s="27">
+      <c r="C129" s="28">
         <f>ROUND(C127*C128,1)</f>
         <v/>
       </c>
-      <c r="D129" s="27">
+      <c r="D129" s="28">
         <f>ROUND(D127*D128,1)</f>
         <v/>
       </c>
-      <c r="E129" s="27">
+      <c r="E129" s="28">
         <f>ROUND(E127*E128,1)</f>
         <v/>
       </c>
-      <c r="F129" s="27">
+      <c r="F129" s="28">
         <f>ROUND(F127*F128,1)</f>
         <v/>
       </c>
@@ -5431,7 +6217,7 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="9" t="inlineStr">
+      <c r="A131" s="10" t="inlineStr">
         <is>
           <t>10　共同生活援助</t>
         </is>
@@ -5493,18 +6279,18 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C134" s="18" t="n">
+      <c r="C134" s="19" t="n">
         <v>8</v>
       </c>
-      <c r="D134" s="19">
+      <c r="D134" s="20">
         <f>C141</f>
         <v/>
       </c>
-      <c r="E134" s="19">
+      <c r="E134" s="20">
         <f>D141</f>
         <v/>
       </c>
-      <c r="F134" s="19">
+      <c r="F134" s="20">
         <f>E141</f>
         <v/>
       </c>
@@ -5525,10 +6311,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C135" s="20" t="n"/>
-      <c r="D135" s="18" t="n"/>
-      <c r="E135" s="18" t="n"/>
-      <c r="F135" s="18" t="n"/>
+      <c r="C135" s="21" t="n"/>
+      <c r="D135" s="19" t="n"/>
+      <c r="E135" s="19" t="n"/>
+      <c r="F135" s="19" t="n"/>
       <c r="G135" s="4" t="inlineStr">
         <is>
           <t>02_年齢到達者一覧から転記する</t>
@@ -5546,10 +6332,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C136" s="20" t="n"/>
-      <c r="D136" s="18" t="n"/>
-      <c r="E136" s="18" t="n"/>
-      <c r="F136" s="18" t="n"/>
+      <c r="C136" s="21" t="n"/>
+      <c r="D136" s="19" t="n"/>
+      <c r="E136" s="19" t="n"/>
+      <c r="F136" s="19" t="n"/>
       <c r="G136" s="4" t="inlineStr">
         <is>
           <t>移行予定者を個別に確認する</t>
@@ -5567,10 +6353,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C137" s="20" t="n"/>
-      <c r="D137" s="18" t="n"/>
-      <c r="E137" s="18" t="n"/>
-      <c r="F137" s="18" t="n"/>
+      <c r="C137" s="21" t="n"/>
+      <c r="D137" s="19" t="n"/>
+      <c r="E137" s="19" t="n"/>
+      <c r="F137" s="19" t="n"/>
       <c r="G137" s="4" t="inlineStr">
         <is>
           <t>相談支援事業所からの利用開始相談を含む</t>
@@ -5588,10 +6374,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C138" s="21" t="n"/>
-      <c r="D138" s="22" t="n"/>
-      <c r="E138" s="22" t="n"/>
-      <c r="F138" s="22" t="n"/>
+      <c r="C138" s="22" t="n"/>
+      <c r="D138" s="23" t="n"/>
+      <c r="E138" s="23" t="n"/>
+      <c r="F138" s="23" t="n"/>
       <c r="G138" s="4" t="inlineStr">
         <is>
           <t>06_65歳移行判定の結果を反映する。一律に減算しない</t>
@@ -5609,10 +6395,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C139" s="21" t="n"/>
-      <c r="D139" s="22" t="n"/>
-      <c r="E139" s="22" t="n"/>
-      <c r="F139" s="22" t="n"/>
+      <c r="C139" s="22" t="n"/>
+      <c r="D139" s="23" t="n"/>
+      <c r="E139" s="23" t="n"/>
+      <c r="F139" s="23" t="n"/>
       <c r="G139" s="4" t="inlineStr">
         <is>
           <t>就労移行支援からの一般就労等</t>
@@ -5630,10 +6416,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C140" s="21" t="n"/>
-      <c r="D140" s="22" t="n"/>
-      <c r="E140" s="22" t="n"/>
-      <c r="F140" s="22" t="n"/>
+      <c r="C140" s="22" t="n"/>
+      <c r="D140" s="23" t="n"/>
+      <c r="E140" s="23" t="n"/>
+      <c r="F140" s="23" t="n"/>
       <c r="G140" s="4" t="inlineStr">
         <is>
           <t>高齢化が進む本村では主要な減少要因</t>
@@ -5641,29 +6427,29 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="23" t="inlineStr">
+      <c r="A141" s="24" t="inlineStr">
         <is>
           <t>＝　利用者数</t>
         </is>
       </c>
-      <c r="B141" s="24" t="inlineStr">
-        <is>
-          <t>人／月</t>
-        </is>
-      </c>
-      <c r="C141" s="25">
+      <c r="B141" s="25" t="inlineStr">
+        <is>
+          <t>人／月</t>
+        </is>
+      </c>
+      <c r="C141" s="26">
         <f>C134</f>
         <v/>
       </c>
-      <c r="D141" s="25">
+      <c r="D141" s="26">
         <f>D134+SUM(D135:D137)-SUM(D138:D140)</f>
         <v/>
       </c>
-      <c r="E141" s="25">
+      <c r="E141" s="26">
         <f>E134+SUM(E135:E137)-SUM(E138:E140)</f>
         <v/>
       </c>
-      <c r="F141" s="25">
+      <c r="F141" s="26">
         <f>F134+SUM(F135:F137)-SUM(F138:F140)</f>
         <v/>
       </c>
@@ -5684,10 +6470,10 @@
           <t>―</t>
         </is>
       </c>
-      <c r="C142" s="26" t="n"/>
-      <c r="D142" s="26" t="n"/>
-      <c r="E142" s="26" t="n"/>
-      <c r="F142" s="26" t="n"/>
+      <c r="C142" s="27" t="n"/>
+      <c r="D142" s="27" t="n"/>
+      <c r="E142" s="27" t="n"/>
+      <c r="F142" s="27" t="n"/>
       <c r="G142" s="4" t="inlineStr">
         <is>
           <t>利用者ごとの月間予定量の平均</t>
@@ -5695,29 +6481,29 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="23" t="inlineStr">
+      <c r="A143" s="24" t="inlineStr">
         <is>
           <t>＝　月間サービス量</t>
         </is>
       </c>
-      <c r="B143" s="24" t="inlineStr">
+      <c r="B143" s="25" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="C143" s="27">
+      <c r="C143" s="28">
         <f>ROUND(C141*C142,1)</f>
         <v/>
       </c>
-      <c r="D143" s="27">
+      <c r="D143" s="28">
         <f>ROUND(D141*D142,1)</f>
         <v/>
       </c>
-      <c r="E143" s="27">
+      <c r="E143" s="28">
         <f>ROUND(E141*E142,1)</f>
         <v/>
       </c>
-      <c r="F143" s="27">
+      <c r="F143" s="28">
         <f>ROUND(F141*F142,1)</f>
         <v/>
       </c>
@@ -5728,7 +6514,7 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="9" t="inlineStr">
+      <c r="A145" s="10" t="inlineStr">
         <is>
           <t>11　施設入所支援</t>
         </is>
@@ -5790,18 +6576,18 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C148" s="18" t="n">
+      <c r="C148" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="D148" s="19">
+      <c r="D148" s="20">
         <f>C155</f>
         <v/>
       </c>
-      <c r="E148" s="19">
+      <c r="E148" s="20">
         <f>D155</f>
         <v/>
       </c>
-      <c r="F148" s="19">
+      <c r="F148" s="20">
         <f>E155</f>
         <v/>
       </c>
@@ -5822,10 +6608,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C149" s="20" t="n"/>
-      <c r="D149" s="18" t="n"/>
-      <c r="E149" s="18" t="n"/>
-      <c r="F149" s="18" t="n"/>
+      <c r="C149" s="21" t="n"/>
+      <c r="D149" s="19" t="n"/>
+      <c r="E149" s="19" t="n"/>
+      <c r="F149" s="19" t="n"/>
       <c r="G149" s="4" t="inlineStr">
         <is>
           <t>02_年齢到達者一覧から転記する</t>
@@ -5843,10 +6629,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C150" s="20" t="n"/>
-      <c r="D150" s="18" t="n"/>
-      <c r="E150" s="18" t="n"/>
-      <c r="F150" s="18" t="n"/>
+      <c r="C150" s="21" t="n"/>
+      <c r="D150" s="19" t="n"/>
+      <c r="E150" s="19" t="n"/>
+      <c r="F150" s="19" t="n"/>
       <c r="G150" s="4" t="inlineStr">
         <is>
           <t>移行予定者を個別に確認する</t>
@@ -5864,10 +6650,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C151" s="20" t="n"/>
-      <c r="D151" s="18" t="n"/>
-      <c r="E151" s="18" t="n"/>
-      <c r="F151" s="18" t="n"/>
+      <c r="C151" s="21" t="n"/>
+      <c r="D151" s="19" t="n"/>
+      <c r="E151" s="19" t="n"/>
+      <c r="F151" s="19" t="n"/>
       <c r="G151" s="4" t="inlineStr">
         <is>
           <t>相談支援事業所からの利用開始相談を含む</t>
@@ -5885,10 +6671,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C152" s="21" t="n"/>
-      <c r="D152" s="22" t="n"/>
-      <c r="E152" s="22" t="n"/>
-      <c r="F152" s="22" t="n"/>
+      <c r="C152" s="22" t="n"/>
+      <c r="D152" s="23" t="n"/>
+      <c r="E152" s="23" t="n"/>
+      <c r="F152" s="23" t="n"/>
       <c r="G152" s="4" t="inlineStr">
         <is>
           <t>06_65歳移行判定の結果を反映する。一律に減算しない</t>
@@ -5906,10 +6692,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C153" s="21" t="n"/>
-      <c r="D153" s="22" t="n"/>
-      <c r="E153" s="22" t="n"/>
-      <c r="F153" s="22" t="n"/>
+      <c r="C153" s="22" t="n"/>
+      <c r="D153" s="23" t="n"/>
+      <c r="E153" s="23" t="n"/>
+      <c r="F153" s="23" t="n"/>
       <c r="G153" s="4" t="inlineStr">
         <is>
           <t>就労移行支援からの一般就労等</t>
@@ -5927,10 +6713,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C154" s="21" t="n"/>
-      <c r="D154" s="22" t="n"/>
-      <c r="E154" s="22" t="n"/>
-      <c r="F154" s="22" t="n"/>
+      <c r="C154" s="22" t="n"/>
+      <c r="D154" s="23" t="n"/>
+      <c r="E154" s="23" t="n"/>
+      <c r="F154" s="23" t="n"/>
       <c r="G154" s="4" t="inlineStr">
         <is>
           <t>高齢化が進む本村では主要な減少要因</t>
@@ -5938,29 +6724,29 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="23" t="inlineStr">
+      <c r="A155" s="24" t="inlineStr">
         <is>
           <t>＝　利用者数</t>
         </is>
       </c>
-      <c r="B155" s="24" t="inlineStr">
-        <is>
-          <t>人／月</t>
-        </is>
-      </c>
-      <c r="C155" s="25">
+      <c r="B155" s="25" t="inlineStr">
+        <is>
+          <t>人／月</t>
+        </is>
+      </c>
+      <c r="C155" s="26">
         <f>C148</f>
         <v/>
       </c>
-      <c r="D155" s="25">
+      <c r="D155" s="26">
         <f>D148+SUM(D149:D151)-SUM(D152:D154)</f>
         <v/>
       </c>
-      <c r="E155" s="25">
+      <c r="E155" s="26">
         <f>E148+SUM(E149:E151)-SUM(E152:E154)</f>
         <v/>
       </c>
-      <c r="F155" s="25">
+      <c r="F155" s="26">
         <f>F148+SUM(F149:F151)-SUM(F152:F154)</f>
         <v/>
       </c>
@@ -5981,10 +6767,10 @@
           <t>―</t>
         </is>
       </c>
-      <c r="C156" s="26" t="n"/>
-      <c r="D156" s="26" t="n"/>
-      <c r="E156" s="26" t="n"/>
-      <c r="F156" s="26" t="n"/>
+      <c r="C156" s="27" t="n"/>
+      <c r="D156" s="27" t="n"/>
+      <c r="E156" s="27" t="n"/>
+      <c r="F156" s="27" t="n"/>
       <c r="G156" s="4" t="inlineStr">
         <is>
           <t>利用者ごとの月間予定量の平均</t>
@@ -5992,29 +6778,29 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="23" t="inlineStr">
+      <c r="A157" s="24" t="inlineStr">
         <is>
           <t>＝　月間サービス量</t>
         </is>
       </c>
-      <c r="B157" s="24" t="inlineStr">
+      <c r="B157" s="25" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="C157" s="27">
+      <c r="C157" s="28">
         <f>ROUND(C155*C156,1)</f>
         <v/>
       </c>
-      <c r="D157" s="27">
+      <c r="D157" s="28">
         <f>ROUND(D155*D156,1)</f>
         <v/>
       </c>
-      <c r="E157" s="27">
+      <c r="E157" s="28">
         <f>ROUND(E155*E156,1)</f>
         <v/>
       </c>
-      <c r="F157" s="27">
+      <c r="F157" s="28">
         <f>ROUND(F155*F156,1)</f>
         <v/>
       </c>
@@ -6025,7 +6811,7 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="9" t="inlineStr">
+      <c r="A159" s="10" t="inlineStr">
         <is>
           <t>12　計画相談支援</t>
         </is>
@@ -6087,18 +6873,18 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C162" s="18" t="n">
+      <c r="C162" s="19" t="n">
         <v>22</v>
       </c>
-      <c r="D162" s="19">
+      <c r="D162" s="20">
         <f>C169</f>
         <v/>
       </c>
-      <c r="E162" s="19">
+      <c r="E162" s="20">
         <f>D169</f>
         <v/>
       </c>
-      <c r="F162" s="19">
+      <c r="F162" s="20">
         <f>E169</f>
         <v/>
       </c>
@@ -6119,10 +6905,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C163" s="20" t="n"/>
-      <c r="D163" s="18" t="n"/>
-      <c r="E163" s="18" t="n"/>
-      <c r="F163" s="18" t="n"/>
+      <c r="C163" s="21" t="n"/>
+      <c r="D163" s="19" t="n"/>
+      <c r="E163" s="19" t="n"/>
+      <c r="F163" s="19" t="n"/>
       <c r="G163" s="4" t="inlineStr">
         <is>
           <t>02_年齢到達者一覧から転記する</t>
@@ -6140,10 +6926,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C164" s="20" t="n"/>
-      <c r="D164" s="18" t="n"/>
-      <c r="E164" s="18" t="n"/>
-      <c r="F164" s="18" t="n"/>
+      <c r="C164" s="21" t="n"/>
+      <c r="D164" s="19" t="n"/>
+      <c r="E164" s="19" t="n"/>
+      <c r="F164" s="19" t="n"/>
       <c r="G164" s="4" t="inlineStr">
         <is>
           <t>移行予定者を個別に確認する</t>
@@ -6161,10 +6947,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C165" s="20" t="n"/>
-      <c r="D165" s="18" t="n"/>
-      <c r="E165" s="18" t="n"/>
-      <c r="F165" s="18" t="n"/>
+      <c r="C165" s="21" t="n"/>
+      <c r="D165" s="19" t="n"/>
+      <c r="E165" s="19" t="n"/>
+      <c r="F165" s="19" t="n"/>
       <c r="G165" s="4" t="inlineStr">
         <is>
           <t>相談支援事業所からの利用開始相談を含む</t>
@@ -6182,10 +6968,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C166" s="21" t="n"/>
-      <c r="D166" s="22" t="n"/>
-      <c r="E166" s="22" t="n"/>
-      <c r="F166" s="22" t="n"/>
+      <c r="C166" s="22" t="n"/>
+      <c r="D166" s="23" t="n"/>
+      <c r="E166" s="23" t="n"/>
+      <c r="F166" s="23" t="n"/>
       <c r="G166" s="4" t="inlineStr">
         <is>
           <t>06_65歳移行判定の結果を反映する。一律に減算しない</t>
@@ -6203,10 +6989,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C167" s="21" t="n"/>
-      <c r="D167" s="22" t="n"/>
-      <c r="E167" s="22" t="n"/>
-      <c r="F167" s="22" t="n"/>
+      <c r="C167" s="22" t="n"/>
+      <c r="D167" s="23" t="n"/>
+      <c r="E167" s="23" t="n"/>
+      <c r="F167" s="23" t="n"/>
       <c r="G167" s="4" t="inlineStr">
         <is>
           <t>就労移行支援からの一般就労等</t>
@@ -6224,10 +7010,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C168" s="21" t="n"/>
-      <c r="D168" s="22" t="n"/>
-      <c r="E168" s="22" t="n"/>
-      <c r="F168" s="22" t="n"/>
+      <c r="C168" s="22" t="n"/>
+      <c r="D168" s="23" t="n"/>
+      <c r="E168" s="23" t="n"/>
+      <c r="F168" s="23" t="n"/>
       <c r="G168" s="4" t="inlineStr">
         <is>
           <t>高齢化が進む本村では主要な減少要因</t>
@@ -6235,29 +7021,29 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="23" t="inlineStr">
+      <c r="A169" s="24" t="inlineStr">
         <is>
           <t>＝　利用者数</t>
         </is>
       </c>
-      <c r="B169" s="24" t="inlineStr">
-        <is>
-          <t>人／月</t>
-        </is>
-      </c>
-      <c r="C169" s="25">
+      <c r="B169" s="25" t="inlineStr">
+        <is>
+          <t>人／月</t>
+        </is>
+      </c>
+      <c r="C169" s="26">
         <f>C162</f>
         <v/>
       </c>
-      <c r="D169" s="25">
+      <c r="D169" s="26">
         <f>D162+SUM(D163:D165)-SUM(D166:D168)</f>
         <v/>
       </c>
-      <c r="E169" s="25">
+      <c r="E169" s="26">
         <f>E162+SUM(E163:E165)-SUM(E166:E168)</f>
         <v/>
       </c>
-      <c r="F169" s="25">
+      <c r="F169" s="26">
         <f>F162+SUM(F163:F165)-SUM(F166:F168)</f>
         <v/>
       </c>
@@ -6278,10 +7064,10 @@
           <t>―</t>
         </is>
       </c>
-      <c r="C170" s="26" t="n"/>
-      <c r="D170" s="26" t="n"/>
-      <c r="E170" s="26" t="n"/>
-      <c r="F170" s="26" t="n"/>
+      <c r="C170" s="27" t="n"/>
+      <c r="D170" s="27" t="n"/>
+      <c r="E170" s="27" t="n"/>
+      <c r="F170" s="27" t="n"/>
       <c r="G170" s="4" t="inlineStr">
         <is>
           <t>利用者ごとの月間予定量の平均</t>
@@ -6289,29 +7075,29 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="23" t="inlineStr">
+      <c r="A171" s="24" t="inlineStr">
         <is>
           <t>＝　月間サービス量</t>
         </is>
       </c>
-      <c r="B171" s="24" t="inlineStr">
+      <c r="B171" s="25" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="C171" s="27">
+      <c r="C171" s="28">
         <f>ROUND(C169*C170,1)</f>
         <v/>
       </c>
-      <c r="D171" s="27">
+      <c r="D171" s="28">
         <f>ROUND(D169*D170,1)</f>
         <v/>
       </c>
-      <c r="E171" s="27">
+      <c r="E171" s="28">
         <f>ROUND(E169*E170,1)</f>
         <v/>
       </c>
-      <c r="F171" s="27">
+      <c r="F171" s="28">
         <f>ROUND(F169*F170,1)</f>
         <v/>
       </c>
@@ -6381,7 +7167,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="10" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>障がい児通所支援等の個別積上げ</t>
         </is>
@@ -6395,7 +7181,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="28" t="inlineStr">
+      <c r="A5" s="29" t="inlineStr">
         <is>
           <t>1　児童発達支援</t>
         </is>
@@ -6457,18 +7243,18 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C8" s="18" t="n">
+      <c r="C8" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="D8" s="19">
+      <c r="D8" s="20">
         <f>C14</f>
         <v/>
       </c>
-      <c r="E8" s="19">
+      <c r="E8" s="20">
         <f>D14</f>
         <v/>
       </c>
-      <c r="F8" s="19">
+      <c r="F8" s="20">
         <f>E14</f>
         <v/>
       </c>
@@ -6489,10 +7275,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C9" s="20" t="n"/>
-      <c r="D9" s="18" t="n"/>
-      <c r="E9" s="18" t="n"/>
-      <c r="F9" s="18" t="n"/>
+      <c r="C9" s="21" t="n"/>
+      <c r="D9" s="19" t="n"/>
+      <c r="E9" s="19" t="n"/>
+      <c r="F9" s="19" t="n"/>
       <c r="G9" s="4" t="inlineStr">
         <is>
           <t>新規の発達相談・診断からの流入</t>
@@ -6510,10 +7296,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C10" s="20" t="n"/>
-      <c r="D10" s="18" t="n"/>
-      <c r="E10" s="18" t="n"/>
-      <c r="F10" s="18" t="n"/>
+      <c r="C10" s="21" t="n"/>
+      <c r="D10" s="19" t="n"/>
+      <c r="E10" s="19" t="n"/>
+      <c r="F10" s="19" t="n"/>
       <c r="G10" s="4" t="inlineStr">
         <is>
           <t>児童発達支援から放課後等デイサービスへの移行等</t>
@@ -6531,10 +7317,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C11" s="21" t="n"/>
-      <c r="D11" s="22" t="n"/>
-      <c r="E11" s="22" t="n"/>
-      <c r="F11" s="22" t="n"/>
+      <c r="C11" s="22" t="n"/>
+      <c r="D11" s="23" t="n"/>
+      <c r="E11" s="23" t="n"/>
+      <c r="F11" s="23" t="n"/>
       <c r="G11" s="4" t="inlineStr">
         <is>
           <t>児童発達支援からの流出</t>
@@ -6552,10 +7338,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C12" s="21" t="n"/>
-      <c r="D12" s="22" t="n"/>
-      <c r="E12" s="22" t="n"/>
-      <c r="F12" s="22" t="n"/>
+      <c r="C12" s="22" t="n"/>
+      <c r="D12" s="23" t="n"/>
+      <c r="E12" s="23" t="n"/>
+      <c r="F12" s="23" t="n"/>
       <c r="G12" s="4" t="inlineStr">
         <is>
           <t>成人の障害福祉サービスへ。03の流入と一致させる</t>
@@ -6573,36 +7359,36 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C13" s="21" t="n"/>
-      <c r="D13" s="22" t="n"/>
-      <c r="E13" s="22" t="n"/>
-      <c r="F13" s="22" t="n"/>
+      <c r="C13" s="22" t="n"/>
+      <c r="D13" s="23" t="n"/>
+      <c r="E13" s="23" t="n"/>
+      <c r="F13" s="23" t="n"/>
       <c r="G13" s="4" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="23" t="inlineStr">
+      <c r="A14" s="24" t="inlineStr">
         <is>
           <t>＝　利用者数</t>
         </is>
       </c>
-      <c r="B14" s="24" t="inlineStr">
-        <is>
-          <t>人／月</t>
-        </is>
-      </c>
-      <c r="C14" s="25">
+      <c r="B14" s="25" t="inlineStr">
+        <is>
+          <t>人／月</t>
+        </is>
+      </c>
+      <c r="C14" s="26">
         <f>C8</f>
         <v/>
       </c>
-      <c r="D14" s="25">
+      <c r="D14" s="26">
         <f>D8+SUM(D9:D10)-SUM(D11:D13)</f>
         <v/>
       </c>
-      <c r="E14" s="25">
+      <c r="E14" s="26">
         <f>E8+SUM(E9:E10)-SUM(E11:E13)</f>
         <v/>
       </c>
-      <c r="F14" s="25">
+      <c r="F14" s="26">
         <f>F8+SUM(F9:F10)-SUM(F11:F13)</f>
         <v/>
       </c>
@@ -6623,10 +7409,10 @@
           <t>人日／月</t>
         </is>
       </c>
-      <c r="C15" s="26" t="n"/>
-      <c r="D15" s="26" t="n"/>
-      <c r="E15" s="26" t="n"/>
-      <c r="F15" s="26" t="n"/>
+      <c r="C15" s="27" t="n"/>
+      <c r="D15" s="27" t="n"/>
+      <c r="E15" s="27" t="n"/>
+      <c r="F15" s="27" t="n"/>
       <c r="G15" s="4" t="inlineStr">
         <is>
           <t>利用者ごとの月間予定量の平均</t>
@@ -6634,29 +7420,29 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="23" t="inlineStr">
+      <c r="A16" s="24" t="inlineStr">
         <is>
           <t>＝　月間サービス量</t>
         </is>
       </c>
-      <c r="B16" s="24" t="inlineStr">
+      <c r="B16" s="25" t="inlineStr">
         <is>
           <t>人日／月</t>
         </is>
       </c>
-      <c r="C16" s="27">
+      <c r="C16" s="28">
         <f>ROUND(C14*C15,1)</f>
         <v/>
       </c>
-      <c r="D16" s="27">
+      <c r="D16" s="28">
         <f>ROUND(D14*D15,1)</f>
         <v/>
       </c>
-      <c r="E16" s="27">
+      <c r="E16" s="28">
         <f>ROUND(E14*E15,1)</f>
         <v/>
       </c>
-      <c r="F16" s="27">
+      <c r="F16" s="28">
         <f>ROUND(F14*F15,1)</f>
         <v/>
       </c>
@@ -6667,7 +7453,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="28" t="inlineStr">
+      <c r="A18" s="29" t="inlineStr">
         <is>
           <t>2　放課後等デイサービス</t>
         </is>
@@ -6729,18 +7515,18 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C21" s="18" t="n">
+      <c r="C21" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="D21" s="19">
+      <c r="D21" s="20">
         <f>C27</f>
         <v/>
       </c>
-      <c r="E21" s="19">
+      <c r="E21" s="20">
         <f>D27</f>
         <v/>
       </c>
-      <c r="F21" s="19">
+      <c r="F21" s="20">
         <f>E27</f>
         <v/>
       </c>
@@ -6761,10 +7547,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C22" s="20" t="n"/>
-      <c r="D22" s="18" t="n"/>
-      <c r="E22" s="18" t="n"/>
-      <c r="F22" s="18" t="n"/>
+      <c r="C22" s="21" t="n"/>
+      <c r="D22" s="19" t="n"/>
+      <c r="E22" s="19" t="n"/>
+      <c r="F22" s="19" t="n"/>
       <c r="G22" s="4" t="inlineStr">
         <is>
           <t>新規の発達相談・診断からの流入</t>
@@ -6782,10 +7568,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C23" s="20" t="n"/>
-      <c r="D23" s="18" t="n"/>
-      <c r="E23" s="18" t="n"/>
-      <c r="F23" s="18" t="n"/>
+      <c r="C23" s="21" t="n"/>
+      <c r="D23" s="19" t="n"/>
+      <c r="E23" s="19" t="n"/>
+      <c r="F23" s="19" t="n"/>
       <c r="G23" s="4" t="inlineStr">
         <is>
           <t>児童発達支援から放課後等デイサービスへの移行等</t>
@@ -6803,10 +7589,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C24" s="21" t="n"/>
-      <c r="D24" s="22" t="n"/>
-      <c r="E24" s="22" t="n"/>
-      <c r="F24" s="22" t="n"/>
+      <c r="C24" s="22" t="n"/>
+      <c r="D24" s="23" t="n"/>
+      <c r="E24" s="23" t="n"/>
+      <c r="F24" s="23" t="n"/>
       <c r="G24" s="4" t="inlineStr">
         <is>
           <t>児童発達支援からの流出</t>
@@ -6824,10 +7610,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C25" s="21" t="n"/>
-      <c r="D25" s="22" t="n"/>
-      <c r="E25" s="22" t="n"/>
-      <c r="F25" s="22" t="n"/>
+      <c r="C25" s="22" t="n"/>
+      <c r="D25" s="23" t="n"/>
+      <c r="E25" s="23" t="n"/>
+      <c r="F25" s="23" t="n"/>
       <c r="G25" s="4" t="inlineStr">
         <is>
           <t>成人の障害福祉サービスへ。03の流入と一致させる</t>
@@ -6845,36 +7631,36 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C26" s="21" t="n"/>
-      <c r="D26" s="22" t="n"/>
-      <c r="E26" s="22" t="n"/>
-      <c r="F26" s="22" t="n"/>
+      <c r="C26" s="22" t="n"/>
+      <c r="D26" s="23" t="n"/>
+      <c r="E26" s="23" t="n"/>
+      <c r="F26" s="23" t="n"/>
       <c r="G26" s="4" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="23" t="inlineStr">
+      <c r="A27" s="24" t="inlineStr">
         <is>
           <t>＝　利用者数</t>
         </is>
       </c>
-      <c r="B27" s="24" t="inlineStr">
-        <is>
-          <t>人／月</t>
-        </is>
-      </c>
-      <c r="C27" s="25">
+      <c r="B27" s="25" t="inlineStr">
+        <is>
+          <t>人／月</t>
+        </is>
+      </c>
+      <c r="C27" s="26">
         <f>C21</f>
         <v/>
       </c>
-      <c r="D27" s="25">
+      <c r="D27" s="26">
         <f>D21+SUM(D22:D23)-SUM(D24:D26)</f>
         <v/>
       </c>
-      <c r="E27" s="25">
+      <c r="E27" s="26">
         <f>E21+SUM(E22:E23)-SUM(E24:E26)</f>
         <v/>
       </c>
-      <c r="F27" s="25">
+      <c r="F27" s="26">
         <f>F21+SUM(F22:F23)-SUM(F24:F26)</f>
         <v/>
       </c>
@@ -6895,16 +7681,16 @@
           <t>人日／月</t>
         </is>
       </c>
-      <c r="C28" s="26" t="n">
+      <c r="C28" s="27" t="n">
         <v>2</v>
       </c>
-      <c r="D28" s="26" t="n">
+      <c r="D28" s="27" t="n">
         <v>2</v>
       </c>
-      <c r="E28" s="26" t="n">
+      <c r="E28" s="27" t="n">
         <v>2</v>
       </c>
-      <c r="F28" s="26" t="n">
+      <c r="F28" s="27" t="n">
         <v>2</v>
       </c>
       <c r="G28" s="4" t="inlineStr">
@@ -6914,29 +7700,29 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="23" t="inlineStr">
+      <c r="A29" s="24" t="inlineStr">
         <is>
           <t>＝　月間サービス量</t>
         </is>
       </c>
-      <c r="B29" s="24" t="inlineStr">
+      <c r="B29" s="25" t="inlineStr">
         <is>
           <t>人日／月</t>
         </is>
       </c>
-      <c r="C29" s="27">
+      <c r="C29" s="28">
         <f>ROUND(C27*C28,1)</f>
         <v/>
       </c>
-      <c r="D29" s="27">
+      <c r="D29" s="28">
         <f>ROUND(D27*D28,1)</f>
         <v/>
       </c>
-      <c r="E29" s="27">
+      <c r="E29" s="28">
         <f>ROUND(E27*E28,1)</f>
         <v/>
       </c>
-      <c r="F29" s="27">
+      <c r="F29" s="28">
         <f>ROUND(F27*F28,1)</f>
         <v/>
       </c>
@@ -6947,7 +7733,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="28" t="inlineStr">
+      <c r="A31" s="29" t="inlineStr">
         <is>
           <t>3　保育所等訪問支援</t>
         </is>
@@ -7009,18 +7795,18 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C34" s="18" t="n">
+      <c r="C34" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="D34" s="19">
+      <c r="D34" s="20">
         <f>C40</f>
         <v/>
       </c>
-      <c r="E34" s="19">
+      <c r="E34" s="20">
         <f>D40</f>
         <v/>
       </c>
-      <c r="F34" s="19">
+      <c r="F34" s="20">
         <f>E40</f>
         <v/>
       </c>
@@ -7041,10 +7827,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C35" s="20" t="n"/>
-      <c r="D35" s="18" t="n"/>
-      <c r="E35" s="18" t="n"/>
-      <c r="F35" s="18" t="n"/>
+      <c r="C35" s="21" t="n"/>
+      <c r="D35" s="19" t="n"/>
+      <c r="E35" s="19" t="n"/>
+      <c r="F35" s="19" t="n"/>
       <c r="G35" s="4" t="inlineStr">
         <is>
           <t>新規の発達相談・診断からの流入</t>
@@ -7062,10 +7848,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C36" s="20" t="n"/>
-      <c r="D36" s="18" t="n"/>
-      <c r="E36" s="18" t="n"/>
-      <c r="F36" s="18" t="n"/>
+      <c r="C36" s="21" t="n"/>
+      <c r="D36" s="19" t="n"/>
+      <c r="E36" s="19" t="n"/>
+      <c r="F36" s="19" t="n"/>
       <c r="G36" s="4" t="inlineStr">
         <is>
           <t>児童発達支援から放課後等デイサービスへの移行等</t>
@@ -7083,10 +7869,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C37" s="21" t="n"/>
-      <c r="D37" s="22" t="n"/>
-      <c r="E37" s="22" t="n"/>
-      <c r="F37" s="22" t="n"/>
+      <c r="C37" s="22" t="n"/>
+      <c r="D37" s="23" t="n"/>
+      <c r="E37" s="23" t="n"/>
+      <c r="F37" s="23" t="n"/>
       <c r="G37" s="4" t="inlineStr">
         <is>
           <t>児童発達支援からの流出</t>
@@ -7104,10 +7890,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C38" s="21" t="n"/>
-      <c r="D38" s="22" t="n"/>
-      <c r="E38" s="22" t="n"/>
-      <c r="F38" s="22" t="n"/>
+      <c r="C38" s="22" t="n"/>
+      <c r="D38" s="23" t="n"/>
+      <c r="E38" s="23" t="n"/>
+      <c r="F38" s="23" t="n"/>
       <c r="G38" s="4" t="inlineStr">
         <is>
           <t>成人の障害福祉サービスへ。03の流入と一致させる</t>
@@ -7125,36 +7911,36 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C39" s="21" t="n"/>
-      <c r="D39" s="22" t="n"/>
-      <c r="E39" s="22" t="n"/>
-      <c r="F39" s="22" t="n"/>
+      <c r="C39" s="22" t="n"/>
+      <c r="D39" s="23" t="n"/>
+      <c r="E39" s="23" t="n"/>
+      <c r="F39" s="23" t="n"/>
       <c r="G39" s="4" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="23" t="inlineStr">
+      <c r="A40" s="24" t="inlineStr">
         <is>
           <t>＝　利用者数</t>
         </is>
       </c>
-      <c r="B40" s="24" t="inlineStr">
-        <is>
-          <t>人／月</t>
-        </is>
-      </c>
-      <c r="C40" s="25">
+      <c r="B40" s="25" t="inlineStr">
+        <is>
+          <t>人／月</t>
+        </is>
+      </c>
+      <c r="C40" s="26">
         <f>C34</f>
         <v/>
       </c>
-      <c r="D40" s="25">
+      <c r="D40" s="26">
         <f>D34+SUM(D35:D36)-SUM(D37:D39)</f>
         <v/>
       </c>
-      <c r="E40" s="25">
+      <c r="E40" s="26">
         <f>E34+SUM(E35:E36)-SUM(E37:E39)</f>
         <v/>
       </c>
-      <c r="F40" s="25">
+      <c r="F40" s="26">
         <f>F34+SUM(F35:F36)-SUM(F37:F39)</f>
         <v/>
       </c>
@@ -7175,10 +7961,10 @@
           <t>―</t>
         </is>
       </c>
-      <c r="C41" s="26" t="n"/>
-      <c r="D41" s="26" t="n"/>
-      <c r="E41" s="26" t="n"/>
-      <c r="F41" s="26" t="n"/>
+      <c r="C41" s="27" t="n"/>
+      <c r="D41" s="27" t="n"/>
+      <c r="E41" s="27" t="n"/>
+      <c r="F41" s="27" t="n"/>
       <c r="G41" s="4" t="inlineStr">
         <is>
           <t>利用者ごとの月間予定量の平均</t>
@@ -7186,29 +7972,29 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="23" t="inlineStr">
+      <c r="A42" s="24" t="inlineStr">
         <is>
           <t>＝　月間サービス量</t>
         </is>
       </c>
-      <c r="B42" s="24" t="inlineStr">
+      <c r="B42" s="25" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="C42" s="27">
+      <c r="C42" s="28">
         <f>ROUND(C40*C41,1)</f>
         <v/>
       </c>
-      <c r="D42" s="27">
+      <c r="D42" s="28">
         <f>ROUND(D40*D41,1)</f>
         <v/>
       </c>
-      <c r="E42" s="27">
+      <c r="E42" s="28">
         <f>ROUND(E40*E41,1)</f>
         <v/>
       </c>
-      <c r="F42" s="27">
+      <c r="F42" s="28">
         <f>ROUND(F40*F41,1)</f>
         <v/>
       </c>
@@ -7219,7 +8005,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="28" t="inlineStr">
+      <c r="A44" s="29" t="inlineStr">
         <is>
           <t>4　居宅訪問型児童発達支援</t>
         </is>
@@ -7281,18 +8067,18 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C47" s="18" t="n">
+      <c r="C47" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="D47" s="19">
+      <c r="D47" s="20">
         <f>C53</f>
         <v/>
       </c>
-      <c r="E47" s="19">
+      <c r="E47" s="20">
         <f>D53</f>
         <v/>
       </c>
-      <c r="F47" s="19">
+      <c r="F47" s="20">
         <f>E53</f>
         <v/>
       </c>
@@ -7313,10 +8099,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C48" s="20" t="n"/>
-      <c r="D48" s="18" t="n"/>
-      <c r="E48" s="18" t="n"/>
-      <c r="F48" s="18" t="n"/>
+      <c r="C48" s="21" t="n"/>
+      <c r="D48" s="19" t="n"/>
+      <c r="E48" s="19" t="n"/>
+      <c r="F48" s="19" t="n"/>
       <c r="G48" s="4" t="inlineStr">
         <is>
           <t>新規の発達相談・診断からの流入</t>
@@ -7334,10 +8120,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C49" s="20" t="n"/>
-      <c r="D49" s="18" t="n"/>
-      <c r="E49" s="18" t="n"/>
-      <c r="F49" s="18" t="n"/>
+      <c r="C49" s="21" t="n"/>
+      <c r="D49" s="19" t="n"/>
+      <c r="E49" s="19" t="n"/>
+      <c r="F49" s="19" t="n"/>
       <c r="G49" s="4" t="inlineStr">
         <is>
           <t>児童発達支援から放課後等デイサービスへの移行等</t>
@@ -7355,10 +8141,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C50" s="21" t="n"/>
-      <c r="D50" s="22" t="n"/>
-      <c r="E50" s="22" t="n"/>
-      <c r="F50" s="22" t="n"/>
+      <c r="C50" s="22" t="n"/>
+      <c r="D50" s="23" t="n"/>
+      <c r="E50" s="23" t="n"/>
+      <c r="F50" s="23" t="n"/>
       <c r="G50" s="4" t="inlineStr">
         <is>
           <t>児童発達支援からの流出</t>
@@ -7376,10 +8162,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C51" s="21" t="n"/>
-      <c r="D51" s="22" t="n"/>
-      <c r="E51" s="22" t="n"/>
-      <c r="F51" s="22" t="n"/>
+      <c r="C51" s="22" t="n"/>
+      <c r="D51" s="23" t="n"/>
+      <c r="E51" s="23" t="n"/>
+      <c r="F51" s="23" t="n"/>
       <c r="G51" s="4" t="inlineStr">
         <is>
           <t>成人の障害福祉サービスへ。03の流入と一致させる</t>
@@ -7397,36 +8183,36 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C52" s="21" t="n"/>
-      <c r="D52" s="22" t="n"/>
-      <c r="E52" s="22" t="n"/>
-      <c r="F52" s="22" t="n"/>
+      <c r="C52" s="22" t="n"/>
+      <c r="D52" s="23" t="n"/>
+      <c r="E52" s="23" t="n"/>
+      <c r="F52" s="23" t="n"/>
       <c r="G52" s="4" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="23" t="inlineStr">
+      <c r="A53" s="24" t="inlineStr">
         <is>
           <t>＝　利用者数</t>
         </is>
       </c>
-      <c r="B53" s="24" t="inlineStr">
-        <is>
-          <t>人／月</t>
-        </is>
-      </c>
-      <c r="C53" s="25">
+      <c r="B53" s="25" t="inlineStr">
+        <is>
+          <t>人／月</t>
+        </is>
+      </c>
+      <c r="C53" s="26">
         <f>C47</f>
         <v/>
       </c>
-      <c r="D53" s="25">
+      <c r="D53" s="26">
         <f>D47+SUM(D48:D49)-SUM(D50:D52)</f>
         <v/>
       </c>
-      <c r="E53" s="25">
+      <c r="E53" s="26">
         <f>E47+SUM(E48:E49)-SUM(E50:E52)</f>
         <v/>
       </c>
-      <c r="F53" s="25">
+      <c r="F53" s="26">
         <f>F47+SUM(F48:F49)-SUM(F50:F52)</f>
         <v/>
       </c>
@@ -7447,10 +8233,10 @@
           <t>―</t>
         </is>
       </c>
-      <c r="C54" s="26" t="n"/>
-      <c r="D54" s="26" t="n"/>
-      <c r="E54" s="26" t="n"/>
-      <c r="F54" s="26" t="n"/>
+      <c r="C54" s="27" t="n"/>
+      <c r="D54" s="27" t="n"/>
+      <c r="E54" s="27" t="n"/>
+      <c r="F54" s="27" t="n"/>
       <c r="G54" s="4" t="inlineStr">
         <is>
           <t>利用者ごとの月間予定量の平均</t>
@@ -7458,29 +8244,29 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="23" t="inlineStr">
+      <c r="A55" s="24" t="inlineStr">
         <is>
           <t>＝　月間サービス量</t>
         </is>
       </c>
-      <c r="B55" s="24" t="inlineStr">
+      <c r="B55" s="25" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="C55" s="27">
+      <c r="C55" s="28">
         <f>ROUND(C53*C54,1)</f>
         <v/>
       </c>
-      <c r="D55" s="27">
+      <c r="D55" s="28">
         <f>ROUND(D53*D54,1)</f>
         <v/>
       </c>
-      <c r="E55" s="27">
+      <c r="E55" s="28">
         <f>ROUND(E53*E54,1)</f>
         <v/>
       </c>
-      <c r="F55" s="27">
+      <c r="F55" s="28">
         <f>ROUND(F53*F54,1)</f>
         <v/>
       </c>
@@ -7491,7 +8277,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="28" t="inlineStr">
+      <c r="A57" s="29" t="inlineStr">
         <is>
           <t>5　医療型児童発達支援</t>
         </is>
@@ -7553,18 +8339,18 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C60" s="18" t="n">
+      <c r="C60" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="D60" s="19">
+      <c r="D60" s="20">
         <f>C66</f>
         <v/>
       </c>
-      <c r="E60" s="19">
+      <c r="E60" s="20">
         <f>D66</f>
         <v/>
       </c>
-      <c r="F60" s="19">
+      <c r="F60" s="20">
         <f>E66</f>
         <v/>
       </c>
@@ -7585,10 +8371,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C61" s="20" t="n"/>
-      <c r="D61" s="18" t="n"/>
-      <c r="E61" s="18" t="n"/>
-      <c r="F61" s="18" t="n"/>
+      <c r="C61" s="21" t="n"/>
+      <c r="D61" s="19" t="n"/>
+      <c r="E61" s="19" t="n"/>
+      <c r="F61" s="19" t="n"/>
       <c r="G61" s="4" t="inlineStr">
         <is>
           <t>新規の発達相談・診断からの流入</t>
@@ -7606,10 +8392,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C62" s="20" t="n"/>
-      <c r="D62" s="18" t="n"/>
-      <c r="E62" s="18" t="n"/>
-      <c r="F62" s="18" t="n"/>
+      <c r="C62" s="21" t="n"/>
+      <c r="D62" s="19" t="n"/>
+      <c r="E62" s="19" t="n"/>
+      <c r="F62" s="19" t="n"/>
       <c r="G62" s="4" t="inlineStr">
         <is>
           <t>児童発達支援から放課後等デイサービスへの移行等</t>
@@ -7627,10 +8413,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C63" s="21" t="n"/>
-      <c r="D63" s="22" t="n"/>
-      <c r="E63" s="22" t="n"/>
-      <c r="F63" s="22" t="n"/>
+      <c r="C63" s="22" t="n"/>
+      <c r="D63" s="23" t="n"/>
+      <c r="E63" s="23" t="n"/>
+      <c r="F63" s="23" t="n"/>
       <c r="G63" s="4" t="inlineStr">
         <is>
           <t>児童発達支援からの流出</t>
@@ -7648,10 +8434,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C64" s="21" t="n"/>
-      <c r="D64" s="22" t="n"/>
-      <c r="E64" s="22" t="n"/>
-      <c r="F64" s="22" t="n"/>
+      <c r="C64" s="22" t="n"/>
+      <c r="D64" s="23" t="n"/>
+      <c r="E64" s="23" t="n"/>
+      <c r="F64" s="23" t="n"/>
       <c r="G64" s="4" t="inlineStr">
         <is>
           <t>成人の障害福祉サービスへ。03の流入と一致させる</t>
@@ -7669,36 +8455,36 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C65" s="21" t="n"/>
-      <c r="D65" s="22" t="n"/>
-      <c r="E65" s="22" t="n"/>
-      <c r="F65" s="22" t="n"/>
+      <c r="C65" s="22" t="n"/>
+      <c r="D65" s="23" t="n"/>
+      <c r="E65" s="23" t="n"/>
+      <c r="F65" s="23" t="n"/>
       <c r="G65" s="4" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" s="23" t="inlineStr">
+      <c r="A66" s="24" t="inlineStr">
         <is>
           <t>＝　利用者数</t>
         </is>
       </c>
-      <c r="B66" s="24" t="inlineStr">
-        <is>
-          <t>人／月</t>
-        </is>
-      </c>
-      <c r="C66" s="25">
+      <c r="B66" s="25" t="inlineStr">
+        <is>
+          <t>人／月</t>
+        </is>
+      </c>
+      <c r="C66" s="26">
         <f>C60</f>
         <v/>
       </c>
-      <c r="D66" s="25">
+      <c r="D66" s="26">
         <f>D60+SUM(D61:D62)-SUM(D63:D65)</f>
         <v/>
       </c>
-      <c r="E66" s="25">
+      <c r="E66" s="26">
         <f>E60+SUM(E61:E62)-SUM(E63:E65)</f>
         <v/>
       </c>
-      <c r="F66" s="25">
+      <c r="F66" s="26">
         <f>F60+SUM(F61:F62)-SUM(F63:F65)</f>
         <v/>
       </c>
@@ -7719,10 +8505,10 @@
           <t>―</t>
         </is>
       </c>
-      <c r="C67" s="26" t="n"/>
-      <c r="D67" s="26" t="n"/>
-      <c r="E67" s="26" t="n"/>
-      <c r="F67" s="26" t="n"/>
+      <c r="C67" s="27" t="n"/>
+      <c r="D67" s="27" t="n"/>
+      <c r="E67" s="27" t="n"/>
+      <c r="F67" s="27" t="n"/>
       <c r="G67" s="4" t="inlineStr">
         <is>
           <t>利用者ごとの月間予定量の平均</t>
@@ -7730,29 +8516,29 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="23" t="inlineStr">
+      <c r="A68" s="24" t="inlineStr">
         <is>
           <t>＝　月間サービス量</t>
         </is>
       </c>
-      <c r="B68" s="24" t="inlineStr">
+      <c r="B68" s="25" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="C68" s="27">
+      <c r="C68" s="28">
         <f>ROUND(C66*C67,1)</f>
         <v/>
       </c>
-      <c r="D68" s="27">
+      <c r="D68" s="28">
         <f>ROUND(D66*D67,1)</f>
         <v/>
       </c>
-      <c r="E68" s="27">
+      <c r="E68" s="28">
         <f>ROUND(E66*E67,1)</f>
         <v/>
       </c>
-      <c r="F68" s="27">
+      <c r="F68" s="28">
         <f>ROUND(F66*F67,1)</f>
         <v/>
       </c>
@@ -7763,7 +8549,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="28" t="inlineStr">
+      <c r="A70" s="29" t="inlineStr">
         <is>
           <t>6　障がい児相談支援</t>
         </is>
@@ -7825,18 +8611,18 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C73" s="18" t="n">
+      <c r="C73" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="D73" s="19">
+      <c r="D73" s="20">
         <f>C79</f>
         <v/>
       </c>
-      <c r="E73" s="19">
+      <c r="E73" s="20">
         <f>D79</f>
         <v/>
       </c>
-      <c r="F73" s="19">
+      <c r="F73" s="20">
         <f>E79</f>
         <v/>
       </c>
@@ -7857,10 +8643,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C74" s="20" t="n"/>
-      <c r="D74" s="18" t="n"/>
-      <c r="E74" s="18" t="n"/>
-      <c r="F74" s="18" t="n"/>
+      <c r="C74" s="21" t="n"/>
+      <c r="D74" s="19" t="n"/>
+      <c r="E74" s="19" t="n"/>
+      <c r="F74" s="19" t="n"/>
       <c r="G74" s="4" t="inlineStr">
         <is>
           <t>新規の発達相談・診断からの流入</t>
@@ -7878,10 +8664,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C75" s="20" t="n"/>
-      <c r="D75" s="18" t="n"/>
-      <c r="E75" s="18" t="n"/>
-      <c r="F75" s="18" t="n"/>
+      <c r="C75" s="21" t="n"/>
+      <c r="D75" s="19" t="n"/>
+      <c r="E75" s="19" t="n"/>
+      <c r="F75" s="19" t="n"/>
       <c r="G75" s="4" t="inlineStr">
         <is>
           <t>児童発達支援から放課後等デイサービスへの移行等</t>
@@ -7899,10 +8685,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C76" s="21" t="n"/>
-      <c r="D76" s="22" t="n"/>
-      <c r="E76" s="22" t="n"/>
-      <c r="F76" s="22" t="n"/>
+      <c r="C76" s="22" t="n"/>
+      <c r="D76" s="23" t="n"/>
+      <c r="E76" s="23" t="n"/>
+      <c r="F76" s="23" t="n"/>
       <c r="G76" s="4" t="inlineStr">
         <is>
           <t>児童発達支援からの流出</t>
@@ -7920,10 +8706,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C77" s="21" t="n"/>
-      <c r="D77" s="22" t="n"/>
-      <c r="E77" s="22" t="n"/>
-      <c r="F77" s="22" t="n"/>
+      <c r="C77" s="22" t="n"/>
+      <c r="D77" s="23" t="n"/>
+      <c r="E77" s="23" t="n"/>
+      <c r="F77" s="23" t="n"/>
       <c r="G77" s="4" t="inlineStr">
         <is>
           <t>成人の障害福祉サービスへ。03の流入と一致させる</t>
@@ -7941,36 +8727,36 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C78" s="21" t="n"/>
-      <c r="D78" s="22" t="n"/>
-      <c r="E78" s="22" t="n"/>
-      <c r="F78" s="22" t="n"/>
+      <c r="C78" s="22" t="n"/>
+      <c r="D78" s="23" t="n"/>
+      <c r="E78" s="23" t="n"/>
+      <c r="F78" s="23" t="n"/>
       <c r="G78" s="4" t="inlineStr"/>
     </row>
     <row r="79">
-      <c r="A79" s="23" t="inlineStr">
+      <c r="A79" s="24" t="inlineStr">
         <is>
           <t>＝　利用者数</t>
         </is>
       </c>
-      <c r="B79" s="24" t="inlineStr">
-        <is>
-          <t>人／月</t>
-        </is>
-      </c>
-      <c r="C79" s="25">
+      <c r="B79" s="25" t="inlineStr">
+        <is>
+          <t>人／月</t>
+        </is>
+      </c>
+      <c r="C79" s="26">
         <f>C73</f>
         <v/>
       </c>
-      <c r="D79" s="25">
+      <c r="D79" s="26">
         <f>D73+SUM(D74:D75)-SUM(D76:D78)</f>
         <v/>
       </c>
-      <c r="E79" s="25">
+      <c r="E79" s="26">
         <f>E73+SUM(E74:E75)-SUM(E76:E78)</f>
         <v/>
       </c>
-      <c r="F79" s="25">
+      <c r="F79" s="26">
         <f>F73+SUM(F74:F75)-SUM(F76:F78)</f>
         <v/>
       </c>
@@ -7991,10 +8777,10 @@
           <t>―</t>
         </is>
       </c>
-      <c r="C80" s="26" t="n"/>
-      <c r="D80" s="26" t="n"/>
-      <c r="E80" s="26" t="n"/>
-      <c r="F80" s="26" t="n"/>
+      <c r="C80" s="27" t="n"/>
+      <c r="D80" s="27" t="n"/>
+      <c r="E80" s="27" t="n"/>
+      <c r="F80" s="27" t="n"/>
       <c r="G80" s="4" t="inlineStr">
         <is>
           <t>利用者ごとの月間予定量の平均</t>
@@ -8002,29 +8788,29 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="23" t="inlineStr">
+      <c r="A81" s="24" t="inlineStr">
         <is>
           <t>＝　月間サービス量</t>
         </is>
       </c>
-      <c r="B81" s="24" t="inlineStr">
+      <c r="B81" s="25" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="C81" s="27">
+      <c r="C81" s="28">
         <f>ROUND(C79*C80,1)</f>
         <v/>
       </c>
-      <c r="D81" s="27">
+      <c r="D81" s="28">
         <f>ROUND(D79*D80,1)</f>
         <v/>
       </c>
-      <c r="E81" s="27">
+      <c r="E81" s="28">
         <f>ROUND(E79*E80,1)</f>
         <v/>
       </c>
-      <c r="F81" s="27">
+      <c r="F81" s="28">
         <f>ROUND(F79*F80,1)</f>
         <v/>
       </c>
@@ -8082,7 +8868,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="10" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>実績ゼロのサービスの確認</t>
         </is>
@@ -8139,13 +8925,13 @@
           <t>重度訪問介護</t>
         </is>
       </c>
-      <c r="B6" s="20" t="n">
+      <c r="B6" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="C6" s="18" t="n"/>
-      <c r="D6" s="18" t="n"/>
-      <c r="E6" s="18" t="n"/>
-      <c r="F6" s="15" t="n"/>
+      <c r="C6" s="19" t="n"/>
+      <c r="D6" s="19" t="n"/>
+      <c r="E6" s="19" t="n"/>
+      <c r="F6" s="16" t="n"/>
       <c r="G6" s="4" t="inlineStr">
         <is>
           <t>重度の肢体不自由者等。対象者の有無を個別に確認</t>
@@ -8158,13 +8944,13 @@
           <t>同行援護</t>
         </is>
       </c>
-      <c r="B7" s="29" t="n">
+      <c r="B7" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="C7" s="18" t="n"/>
-      <c r="D7" s="18" t="n"/>
-      <c r="E7" s="18" t="n"/>
-      <c r="F7" s="15" t="n"/>
+      <c r="C7" s="19" t="n"/>
+      <c r="D7" s="19" t="n"/>
+      <c r="E7" s="19" t="n"/>
+      <c r="F7" s="16" t="n"/>
       <c r="G7" s="6" t="inlineStr">
         <is>
           <t>視覚障がい者の外出支援。介護保険に相当サービスなし</t>
@@ -8177,13 +8963,13 @@
           <t>行動援護</t>
         </is>
       </c>
-      <c r="B8" s="20" t="n">
+      <c r="B8" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="C8" s="18" t="n"/>
-      <c r="D8" s="18" t="n"/>
-      <c r="E8" s="18" t="n"/>
-      <c r="F8" s="15" t="n"/>
+      <c r="C8" s="19" t="n"/>
+      <c r="D8" s="19" t="n"/>
+      <c r="E8" s="19" t="n"/>
+      <c r="F8" s="16" t="n"/>
       <c r="G8" s="4" t="inlineStr">
         <is>
           <t>強度行動障害等。介護保険に相当サービスなし</t>
@@ -8196,13 +8982,13 @@
           <t>重度障がい者等包括支援</t>
         </is>
       </c>
-      <c r="B9" s="29" t="n">
+      <c r="B9" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="C9" s="18" t="n"/>
-      <c r="D9" s="18" t="n"/>
-      <c r="E9" s="18" t="n"/>
-      <c r="F9" s="15" t="n"/>
+      <c r="C9" s="19" t="n"/>
+      <c r="D9" s="19" t="n"/>
+      <c r="E9" s="19" t="n"/>
+      <c r="F9" s="16" t="n"/>
       <c r="G9" s="6" t="inlineStr">
         <is>
           <t>最重度者向け。圏域の供給を確認</t>
@@ -8215,13 +9001,13 @@
           <t>療養介護</t>
         </is>
       </c>
-      <c r="B10" s="20" t="n">
+      <c r="B10" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="C10" s="18" t="n"/>
-      <c r="D10" s="18" t="n"/>
-      <c r="E10" s="18" t="n"/>
-      <c r="F10" s="15" t="n"/>
+      <c r="C10" s="19" t="n"/>
+      <c r="D10" s="19" t="n"/>
+      <c r="E10" s="19" t="n"/>
+      <c r="F10" s="16" t="n"/>
       <c r="G10" s="4" t="inlineStr">
         <is>
           <t>医療機関での長期療養。対象者の有無を確認</t>
@@ -8234,13 +9020,13 @@
           <t>自立訓練（機能訓練）</t>
         </is>
       </c>
-      <c r="B11" s="29" t="n">
+      <c r="B11" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="C11" s="18" t="n"/>
-      <c r="D11" s="18" t="n"/>
-      <c r="E11" s="18" t="n"/>
-      <c r="F11" s="15" t="n"/>
+      <c r="C11" s="19" t="n"/>
+      <c r="D11" s="19" t="n"/>
+      <c r="E11" s="19" t="n"/>
+      <c r="F11" s="16" t="n"/>
       <c r="G11" s="6" t="inlineStr">
         <is>
           <t>リハビリ需要は介護保険側に流れている可能性</t>
@@ -8253,13 +9039,13 @@
           <t>自立生活援助</t>
         </is>
       </c>
-      <c r="B12" s="20" t="n">
+      <c r="B12" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="C12" s="18" t="n"/>
-      <c r="D12" s="18" t="n"/>
-      <c r="E12" s="18" t="n"/>
-      <c r="F12" s="15" t="n"/>
+      <c r="C12" s="19" t="n"/>
+      <c r="D12" s="19" t="n"/>
+      <c r="E12" s="19" t="n"/>
+      <c r="F12" s="16" t="n"/>
       <c r="G12" s="4" t="inlineStr">
         <is>
           <t>一人暮らしへの移行支援。地域移行と連動</t>
@@ -8272,13 +9058,13 @@
           <t>地域移行支援</t>
         </is>
       </c>
-      <c r="B13" s="29" t="n">
+      <c r="B13" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="C13" s="18" t="n"/>
-      <c r="D13" s="18" t="n"/>
-      <c r="E13" s="18" t="n"/>
-      <c r="F13" s="15" t="n"/>
+      <c r="C13" s="19" t="n"/>
+      <c r="D13" s="19" t="n"/>
+      <c r="E13" s="19" t="n"/>
+      <c r="F13" s="16" t="n"/>
       <c r="G13" s="6" t="inlineStr">
         <is>
           <t>施設・精神科病院からの地域移行。成果目標（１）（２）と連動</t>
@@ -8291,13 +9077,13 @@
           <t>地域定着支援</t>
         </is>
       </c>
-      <c r="B14" s="20" t="n">
+      <c r="B14" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="C14" s="18" t="n"/>
-      <c r="D14" s="18" t="n"/>
-      <c r="E14" s="18" t="n"/>
-      <c r="F14" s="15" t="n"/>
+      <c r="C14" s="19" t="n"/>
+      <c r="D14" s="19" t="n"/>
+      <c r="E14" s="19" t="n"/>
+      <c r="F14" s="16" t="n"/>
       <c r="G14" s="4" t="inlineStr">
         <is>
           <t>単身生活者の緊急時対応。地域生活支援拠点と連動</t>
@@ -8338,7 +9124,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="10" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>65歳到達に伴う介護保険への移行判定</t>
         </is>
@@ -8352,7 +9138,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="9" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>1. サービス区分（制度整理・確定）</t>
         </is>
@@ -8387,7 +9173,7 @@
           <t>居宅介護</t>
         </is>
       </c>
-      <c r="B7" s="30" t="inlineStr">
+      <c r="B7" s="31" t="inlineStr">
         <is>
           <t>相当あり</t>
         </is>
@@ -8410,7 +9196,7 @@
           <t>生活介護</t>
         </is>
       </c>
-      <c r="B8" s="30" t="inlineStr">
+      <c r="B8" s="31" t="inlineStr">
         <is>
           <t>相当あり</t>
         </is>
@@ -8433,7 +9219,7 @@
           <t>短期入所</t>
         </is>
       </c>
-      <c r="B9" s="30" t="inlineStr">
+      <c r="B9" s="31" t="inlineStr">
         <is>
           <t>相当あり</t>
         </is>
@@ -8456,7 +9242,7 @@
           <t>自立訓練（機能訓練）</t>
         </is>
       </c>
-      <c r="B10" s="30" t="inlineStr">
+      <c r="B10" s="31" t="inlineStr">
         <is>
           <t>相当あり</t>
         </is>
@@ -8479,7 +9265,7 @@
           <t>共同生活援助</t>
         </is>
       </c>
-      <c r="B11" s="31" t="inlineStr">
+      <c r="B11" s="32" t="inlineStr">
         <is>
           <t>相当なし</t>
         </is>
@@ -8502,7 +9288,7 @@
           <t>施設入所支援</t>
         </is>
       </c>
-      <c r="B12" s="31" t="inlineStr">
+      <c r="B12" s="32" t="inlineStr">
         <is>
           <t>相当なし</t>
         </is>
@@ -8525,7 +9311,7 @@
           <t>就労移行支援</t>
         </is>
       </c>
-      <c r="B13" s="31" t="inlineStr">
+      <c r="B13" s="32" t="inlineStr">
         <is>
           <t>相当なし</t>
         </is>
@@ -8548,7 +9334,7 @@
           <t>就労継続支援A型・B型</t>
         </is>
       </c>
-      <c r="B14" s="31" t="inlineStr">
+      <c r="B14" s="32" t="inlineStr">
         <is>
           <t>相当なし</t>
         </is>
@@ -8571,7 +9357,7 @@
           <t>就労定着支援・就労選択支援</t>
         </is>
       </c>
-      <c r="B15" s="31" t="inlineStr">
+      <c r="B15" s="32" t="inlineStr">
         <is>
           <t>相当なし</t>
         </is>
@@ -8594,7 +9380,7 @@
           <t>同行援護・行動援護</t>
         </is>
       </c>
-      <c r="B16" s="31" t="inlineStr">
+      <c r="B16" s="32" t="inlineStr">
         <is>
           <t>相当なし</t>
         </is>
@@ -8640,7 +9426,7 @@
           <t>計画相談支援</t>
         </is>
       </c>
-      <c r="B18" s="30" t="inlineStr">
+      <c r="B18" s="31" t="inlineStr">
         <is>
           <t>相当あり</t>
         </is>
@@ -8658,7 +9444,7 @@
       <c r="E18" s="6" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="9" t="inlineStr">
+      <c r="A20" s="10" t="inlineStr">
         <is>
           <t>2. 到達者別の判定（入力）</t>
         </is>
@@ -8692,91 +9478,91 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="15" t="n"/>
-      <c r="B22" s="15" t="n"/>
-      <c r="C22" s="16" t="n"/>
-      <c r="D22" s="16" t="n"/>
-      <c r="E22" s="17" t="n"/>
+      <c r="A22" s="16" t="n"/>
+      <c r="B22" s="16" t="n"/>
+      <c r="C22" s="17" t="n"/>
+      <c r="D22" s="17" t="n"/>
+      <c r="E22" s="18" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="15" t="n"/>
-      <c r="B23" s="15" t="n"/>
-      <c r="C23" s="16" t="n"/>
-      <c r="D23" s="16" t="n"/>
-      <c r="E23" s="17" t="n"/>
+      <c r="A23" s="16" t="n"/>
+      <c r="B23" s="16" t="n"/>
+      <c r="C23" s="17" t="n"/>
+      <c r="D23" s="17" t="n"/>
+      <c r="E23" s="18" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="15" t="n"/>
-      <c r="B24" s="15" t="n"/>
-      <c r="C24" s="16" t="n"/>
-      <c r="D24" s="16" t="n"/>
-      <c r="E24" s="17" t="n"/>
+      <c r="A24" s="16" t="n"/>
+      <c r="B24" s="16" t="n"/>
+      <c r="C24" s="17" t="n"/>
+      <c r="D24" s="17" t="n"/>
+      <c r="E24" s="18" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="15" t="n"/>
-      <c r="B25" s="15" t="n"/>
-      <c r="C25" s="16" t="n"/>
-      <c r="D25" s="16" t="n"/>
-      <c r="E25" s="17" t="n"/>
+      <c r="A25" s="16" t="n"/>
+      <c r="B25" s="16" t="n"/>
+      <c r="C25" s="17" t="n"/>
+      <c r="D25" s="17" t="n"/>
+      <c r="E25" s="18" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="15" t="n"/>
-      <c r="B26" s="15" t="n"/>
-      <c r="C26" s="16" t="n"/>
-      <c r="D26" s="16" t="n"/>
-      <c r="E26" s="17" t="n"/>
+      <c r="A26" s="16" t="n"/>
+      <c r="B26" s="16" t="n"/>
+      <c r="C26" s="17" t="n"/>
+      <c r="D26" s="17" t="n"/>
+      <c r="E26" s="18" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="15" t="n"/>
-      <c r="B27" s="15" t="n"/>
-      <c r="C27" s="16" t="n"/>
-      <c r="D27" s="16" t="n"/>
-      <c r="E27" s="17" t="n"/>
+      <c r="A27" s="16" t="n"/>
+      <c r="B27" s="16" t="n"/>
+      <c r="C27" s="17" t="n"/>
+      <c r="D27" s="17" t="n"/>
+      <c r="E27" s="18" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="15" t="n"/>
-      <c r="B28" s="15" t="n"/>
-      <c r="C28" s="16" t="n"/>
-      <c r="D28" s="16" t="n"/>
-      <c r="E28" s="17" t="n"/>
+      <c r="A28" s="16" t="n"/>
+      <c r="B28" s="16" t="n"/>
+      <c r="C28" s="17" t="n"/>
+      <c r="D28" s="17" t="n"/>
+      <c r="E28" s="18" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="15" t="n"/>
-      <c r="B29" s="15" t="n"/>
-      <c r="C29" s="16" t="n"/>
-      <c r="D29" s="16" t="n"/>
-      <c r="E29" s="17" t="n"/>
+      <c r="A29" s="16" t="n"/>
+      <c r="B29" s="16" t="n"/>
+      <c r="C29" s="17" t="n"/>
+      <c r="D29" s="17" t="n"/>
+      <c r="E29" s="18" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="15" t="n"/>
-      <c r="B30" s="15" t="n"/>
-      <c r="C30" s="16" t="n"/>
-      <c r="D30" s="16" t="n"/>
-      <c r="E30" s="17" t="n"/>
+      <c r="A30" s="16" t="n"/>
+      <c r="B30" s="16" t="n"/>
+      <c r="C30" s="17" t="n"/>
+      <c r="D30" s="17" t="n"/>
+      <c r="E30" s="18" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="15" t="n"/>
-      <c r="B31" s="15" t="n"/>
-      <c r="C31" s="16" t="n"/>
-      <c r="D31" s="16" t="n"/>
-      <c r="E31" s="17" t="n"/>
+      <c r="A31" s="16" t="n"/>
+      <c r="B31" s="16" t="n"/>
+      <c r="C31" s="17" t="n"/>
+      <c r="D31" s="17" t="n"/>
+      <c r="E31" s="18" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="15" t="n"/>
-      <c r="B32" s="15" t="n"/>
-      <c r="C32" s="16" t="n"/>
-      <c r="D32" s="16" t="n"/>
-      <c r="E32" s="17" t="n"/>
+      <c r="A32" s="16" t="n"/>
+      <c r="B32" s="16" t="n"/>
+      <c r="C32" s="17" t="n"/>
+      <c r="D32" s="17" t="n"/>
+      <c r="E32" s="18" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="15" t="n"/>
-      <c r="B33" s="15" t="n"/>
-      <c r="C33" s="16" t="n"/>
-      <c r="D33" s="16" t="n"/>
-      <c r="E33" s="17" t="n"/>
+      <c r="A33" s="16" t="n"/>
+      <c r="B33" s="16" t="n"/>
+      <c r="C33" s="17" t="n"/>
+      <c r="D33" s="17" t="n"/>
+      <c r="E33" s="18" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="9" t="inlineStr">
+      <c r="A35" s="10" t="inlineStr">
         <is>
           <t>3. 判定にあたって確認する事項</t>
         </is>
@@ -8808,9 +9594,9 @@
           <t>支援内容・時間・専門性が介護保険サービスで代替できるか。代替できない場合は障害福祉を継続する</t>
         </is>
       </c>
-      <c r="C37" s="32" t="n"/>
-      <c r="D37" s="32" t="n"/>
-      <c r="E37" s="33" t="n"/>
+      <c r="C37" s="33" t="n"/>
+      <c r="D37" s="33" t="n"/>
+      <c r="E37" s="34" t="n"/>
     </row>
     <row r="38" ht="40" customHeight="1">
       <c r="A38" s="6" t="inlineStr">
@@ -8823,9 +9609,9 @@
           <t>村内に事業所がないため、圏域の介護保険事業所が受け入れ可能かを確認する。共生型サービスの指定を受けている事業所があれば、同一事業所での継続利用が可能</t>
         </is>
       </c>
-      <c r="C38" s="32" t="n"/>
-      <c r="D38" s="32" t="n"/>
-      <c r="E38" s="33" t="n"/>
+      <c r="C38" s="33" t="n"/>
+      <c r="D38" s="33" t="n"/>
+      <c r="E38" s="34" t="n"/>
     </row>
     <row r="39" ht="40" customHeight="1">
       <c r="A39" s="4" t="inlineStr">
@@ -8838,9 +9624,9 @@
           <t>①65歳に達する日前5年間の支給決定 ②65歳に達する日の前日の属する年度の市町村民税非課税または生活保護 ③65歳に達する日の前日に障害支援区分2以上 ④65歳まで介護保険サービス未利用。該当すれば介護保険移行後の利用者負担が償還される</t>
         </is>
       </c>
-      <c r="C39" s="32" t="n"/>
-      <c r="D39" s="32" t="n"/>
-      <c r="E39" s="33" t="n"/>
+      <c r="C39" s="33" t="n"/>
+      <c r="D39" s="33" t="n"/>
+      <c r="E39" s="34" t="n"/>
     </row>
     <row r="40" ht="40" customHeight="1">
       <c r="A40" s="6" t="inlineStr">
@@ -8853,9 +9639,9 @@
           <t>介護保険の支給限度基準額では必要量に満たない場合、不足分を障害福祉サービスで上乗せできる。この場合は障害福祉の見込量から全額を減らさない</t>
         </is>
       </c>
-      <c r="C40" s="32" t="n"/>
-      <c r="D40" s="32" t="n"/>
-      <c r="E40" s="33" t="n"/>
+      <c r="C40" s="33" t="n"/>
+      <c r="D40" s="33" t="n"/>
+      <c r="E40" s="34" t="n"/>
     </row>
     <row r="41" ht="40" customHeight="1">
       <c r="A41" s="4" t="inlineStr">
@@ -8868,9 +9654,9 @@
           <t>本人・家族の意向を聴取したうえで支給決定を行う</t>
         </is>
       </c>
-      <c r="C41" s="32" t="n"/>
-      <c r="D41" s="32" t="n"/>
-      <c r="E41" s="33" t="n"/>
+      <c r="C41" s="33" t="n"/>
+      <c r="D41" s="33" t="n"/>
+      <c r="E41" s="34" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -8908,7 +9694,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="10" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>未特定の潜在需要（第3層）</t>
         </is>
@@ -8969,9 +9755,9 @@
           <t>全サービス</t>
         </is>
       </c>
-      <c r="C6" s="26" t="n"/>
-      <c r="D6" s="26" t="n"/>
-      <c r="E6" s="26" t="n"/>
+      <c r="C6" s="27" t="n"/>
+      <c r="D6" s="27" t="n"/>
+      <c r="E6" s="27" t="n"/>
       <c r="F6" s="4" t="inlineStr">
         <is>
           <t>アンケート問29-2・問33</t>
@@ -8994,9 +9780,9 @@
           <t>計画相談支援、各サービス</t>
         </is>
       </c>
-      <c r="C7" s="26" t="n"/>
-      <c r="D7" s="26" t="n"/>
-      <c r="E7" s="26" t="n"/>
+      <c r="C7" s="27" t="n"/>
+      <c r="D7" s="27" t="n"/>
+      <c r="E7" s="27" t="n"/>
       <c r="F7" s="6" t="inlineStr">
         <is>
           <t>相談実績（村資料待ち）</t>
@@ -9019,9 +9805,9 @@
           <t>移動支援、日中一時支援等</t>
         </is>
       </c>
-      <c r="C8" s="26" t="n"/>
-      <c r="D8" s="26" t="n"/>
-      <c r="E8" s="26" t="n"/>
+      <c r="C8" s="27" t="n"/>
+      <c r="D8" s="27" t="n"/>
+      <c r="E8" s="27" t="n"/>
       <c r="F8" s="4" t="inlineStr">
         <is>
           <t>アンケート自由記述</t>
@@ -9044,9 +9830,9 @@
           <t>障害児通所支援、精神関係</t>
         </is>
       </c>
-      <c r="C9" s="26" t="n"/>
-      <c r="D9" s="26" t="n"/>
-      <c r="E9" s="26" t="n"/>
+      <c r="C9" s="27" t="n"/>
+      <c r="D9" s="27" t="n"/>
+      <c r="E9" s="27" t="n"/>
       <c r="F9" s="6" t="inlineStr">
         <is>
           <t>手帳交付実績（村資料待ち）</t>
@@ -9069,9 +9855,9 @@
           <t>全サービス</t>
         </is>
       </c>
-      <c r="C10" s="26" t="n"/>
-      <c r="D10" s="26" t="n"/>
-      <c r="E10" s="26" t="n"/>
+      <c r="C10" s="27" t="n"/>
+      <c r="D10" s="27" t="n"/>
+      <c r="E10" s="27" t="n"/>
       <c r="F10" s="4" t="inlineStr">
         <is>
           <t>圏域4町村の協議</t>
@@ -9094,9 +9880,9 @@
           <t>短期入所、共同生活援助、施設入所支援</t>
         </is>
       </c>
-      <c r="C11" s="26" t="n"/>
-      <c r="D11" s="26" t="n"/>
-      <c r="E11" s="26" t="n"/>
+      <c r="C11" s="27" t="n"/>
+      <c r="D11" s="27" t="n"/>
+      <c r="E11" s="27" t="n"/>
       <c r="F11" s="6" t="inlineStr">
         <is>
           <t>アンケート問8〜問11</t>
@@ -9144,7 +9930,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="10" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>供給制約（利用希望量と利用可能量の分離）</t>
         </is>
@@ -9206,10 +9992,10 @@
           <t>圏域（喜多方市・会津若松市等）</t>
         </is>
       </c>
-      <c r="C6" s="18" t="n"/>
-      <c r="D6" s="18" t="n"/>
-      <c r="E6" s="15" t="n"/>
-      <c r="F6" s="15" t="n"/>
+      <c r="C6" s="19" t="n"/>
+      <c r="D6" s="19" t="n"/>
+      <c r="E6" s="16" t="n"/>
+      <c r="F6" s="16" t="n"/>
       <c r="G6" s="4" t="inlineStr">
         <is>
           <t>特別支援学校卒業者の受入枠。送迎範囲に北塩原村が含まれるか</t>
@@ -9227,10 +10013,10 @@
           <t>喜多方市・会津若松市等</t>
         </is>
       </c>
-      <c r="C7" s="18" t="n"/>
-      <c r="D7" s="18" t="n"/>
-      <c r="E7" s="15" t="n"/>
-      <c r="F7" s="15" t="n"/>
+      <c r="C7" s="19" t="n"/>
+      <c r="D7" s="19" t="n"/>
+      <c r="E7" s="16" t="n"/>
+      <c r="F7" s="16" t="n"/>
       <c r="G7" s="6" t="inlineStr">
         <is>
           <t>給付費が令和2年度比2.08倍。定員に対する余力を確認</t>
@@ -9248,10 +10034,10 @@
           <t>圏域（協議会設置圏域ごとに設置）</t>
         </is>
       </c>
-      <c r="C8" s="18" t="n"/>
-      <c r="D8" s="18" t="n"/>
-      <c r="E8" s="15" t="n"/>
-      <c r="F8" s="15" t="n"/>
+      <c r="C8" s="19" t="n"/>
+      <c r="D8" s="19" t="n"/>
+      <c r="E8" s="16" t="n"/>
+      <c r="F8" s="16" t="n"/>
       <c r="G8" s="4" t="inlineStr">
         <is>
           <t>圏域内に事業所があるか。ない場合の確保方策</t>
@@ -9269,10 +10055,10 @@
           <t>圏域</t>
         </is>
       </c>
-      <c r="C9" s="18" t="n"/>
-      <c r="D9" s="18" t="n"/>
-      <c r="E9" s="15" t="n"/>
-      <c r="F9" s="15" t="n"/>
+      <c r="C9" s="19" t="n"/>
+      <c r="D9" s="19" t="n"/>
+      <c r="E9" s="16" t="n"/>
+      <c r="F9" s="16" t="n"/>
       <c r="G9" s="6" t="inlineStr">
         <is>
           <t>空室の有無。親亡き後の受入余力</t>
@@ -9290,10 +10076,10 @@
           <t>圏域</t>
         </is>
       </c>
-      <c r="C10" s="18" t="n"/>
-      <c r="D10" s="18" t="n"/>
-      <c r="E10" s="15" t="n"/>
-      <c r="F10" s="15" t="n"/>
+      <c r="C10" s="19" t="n"/>
+      <c r="D10" s="19" t="n"/>
+      <c r="E10" s="16" t="n"/>
+      <c r="F10" s="16" t="n"/>
       <c r="G10" s="4" t="inlineStr">
         <is>
           <t>緊急時の受入可否。地域生活支援拠点と連動</t>
@@ -9311,10 +10097,10 @@
           <t>圏域</t>
         </is>
       </c>
-      <c r="C11" s="18" t="n"/>
-      <c r="D11" s="18" t="n"/>
-      <c r="E11" s="15" t="n"/>
-      <c r="F11" s="15" t="n"/>
+      <c r="C11" s="19" t="n"/>
+      <c r="D11" s="19" t="n"/>
+      <c r="E11" s="16" t="n"/>
+      <c r="F11" s="16" t="n"/>
       <c r="G11" s="6" t="inlineStr">
         <is>
           <t>訪問可能地区。冬季の提供体制</t>
@@ -9332,10 +10118,10 @@
           <t>猪苗代町・喜多方市等</t>
         </is>
       </c>
-      <c r="C12" s="18" t="n"/>
-      <c r="D12" s="18" t="n"/>
-      <c r="E12" s="15" t="n"/>
-      <c r="F12" s="15" t="n"/>
+      <c r="C12" s="19" t="n"/>
+      <c r="D12" s="19" t="n"/>
+      <c r="E12" s="16" t="n"/>
+      <c r="F12" s="16" t="n"/>
       <c r="G12" s="4" t="inlineStr">
         <is>
           <t>相談支援専門員の担当可能件数。セルフプラン解消の可否</t>
@@ -9353,10 +10139,10 @@
           <t>圏域（村内0か所）</t>
         </is>
       </c>
-      <c r="C13" s="18" t="n"/>
-      <c r="D13" s="18" t="n"/>
-      <c r="E13" s="15" t="n"/>
-      <c r="F13" s="15" t="n"/>
+      <c r="C13" s="19" t="n"/>
+      <c r="D13" s="19" t="n"/>
+      <c r="E13" s="16" t="n"/>
+      <c r="F13" s="16" t="n"/>
       <c r="G13" s="6" t="inlineStr">
         <is>
           <t>通所距離と保護者の送迎負担</t>
@@ -9374,10 +10160,10 @@
           <t>圏域</t>
         </is>
       </c>
-      <c r="C14" s="18" t="n"/>
-      <c r="D14" s="18" t="n"/>
-      <c r="E14" s="15" t="n"/>
-      <c r="F14" s="15" t="n"/>
+      <c r="C14" s="19" t="n"/>
+      <c r="D14" s="19" t="n"/>
+      <c r="E14" s="16" t="n"/>
+      <c r="F14" s="16" t="n"/>
       <c r="G14" s="4" t="inlineStr">
         <is>
           <t>長期休暇中の受入。送迎</t>
@@ -9395,10 +10181,10 @@
           <t>圏域</t>
         </is>
       </c>
-      <c r="C15" s="18" t="n"/>
-      <c r="D15" s="18" t="n"/>
-      <c r="E15" s="15" t="n"/>
-      <c r="F15" s="15" t="n"/>
+      <c r="C15" s="19" t="n"/>
+      <c r="D15" s="19" t="n"/>
+      <c r="E15" s="16" t="n"/>
+      <c r="F15" s="16" t="n"/>
       <c r="G15" s="6" t="inlineStr">
         <is>
           <t>訪問可能範囲</t>
@@ -9416,10 +10202,10 @@
           <t>圏域</t>
         </is>
       </c>
-      <c r="C16" s="18" t="n"/>
-      <c r="D16" s="18" t="n"/>
-      <c r="E16" s="15" t="n"/>
-      <c r="F16" s="15" t="n"/>
+      <c r="C16" s="19" t="n"/>
+      <c r="D16" s="19" t="n"/>
+      <c r="E16" s="16" t="n"/>
+      <c r="F16" s="16" t="n"/>
       <c r="G16" s="4" t="inlineStr">
         <is>
           <t>65歳移行後の受け皿。共生型サービスの指定を受けているか</t>

--- a/output/北塩原村_サービス見込量.xlsx
+++ b/output/北塩原村_サービス見込量.xlsx
@@ -206,7 +206,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -230,9 +230,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -306,7 +303,13 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1038,19 +1041,19 @@
           <t>算定方法の前提</t>
         </is>
       </c>
-      <c r="D16" s="9" t="inlineStr">
-        <is>
-          <t>村確認待ち</t>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>確定</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>本村の過疎区分が確定するまで算定方法は確定しない</t>
+          <t>全域が過疎（過疎法第2条）のため適用対象外。個別積上げ方式を採用できる</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="10" t="inlineStr">
+      <c r="A18" s="9" t="inlineStr">
         <is>
           <t>作業の順序</t>
         </is>
@@ -1141,7 +1144,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>地域生活支援事業の見込量</t>
         </is>
@@ -1201,13 +1204,13 @@
           <t>か所</t>
         </is>
       </c>
-      <c r="C6" s="21" t="n">
+      <c r="C6" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="D6" s="21" t="n">
+      <c r="D6" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="E6" s="19" t="n"/>
+      <c r="E6" s="18" t="n"/>
       <c r="F6" s="4" t="inlineStr"/>
       <c r="G6" s="4" t="inlineStr">
         <is>
@@ -1221,18 +1224,18 @@
           <t>成年後見制度利用支援事業</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="34" t="inlineStr">
         <is>
           <t>人</t>
         </is>
       </c>
-      <c r="C7" s="30" t="n">
+      <c r="C7" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="D7" s="30" t="n">
+      <c r="D7" s="29" t="n">
         <v>5</v>
       </c>
-      <c r="E7" s="19" t="n"/>
+      <c r="E7" s="18" t="n"/>
       <c r="F7" s="6" t="inlineStr"/>
       <c r="G7" s="6" t="inlineStr">
         <is>
@@ -1251,13 +1254,13 @@
           <t>人</t>
         </is>
       </c>
-      <c r="C8" s="21" t="n">
+      <c r="C8" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="D8" s="21" t="n">
+      <c r="D8" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="E8" s="19" t="n"/>
+      <c r="E8" s="18" t="n"/>
       <c r="F8" s="4" t="inlineStr"/>
       <c r="G8" s="4" t="inlineStr">
         <is>
@@ -1271,18 +1274,18 @@
           <t>日常生活用具給付等事業</t>
         </is>
       </c>
-      <c r="B9" s="9" t="inlineStr">
+      <c r="B9" s="34" t="inlineStr">
         <is>
           <t>件</t>
         </is>
       </c>
-      <c r="C9" s="30" t="n">
+      <c r="C9" s="29" t="n">
         <v>69</v>
       </c>
-      <c r="D9" s="30" t="n">
+      <c r="D9" s="29" t="n">
         <v>72</v>
       </c>
-      <c r="E9" s="19" t="n"/>
+      <c r="E9" s="18" t="n"/>
       <c r="F9" s="6" t="inlineStr"/>
       <c r="G9" s="6" t="inlineStr">
         <is>
@@ -1301,13 +1304,13 @@
           <t>人</t>
         </is>
       </c>
-      <c r="C10" s="21" t="n">
+      <c r="C10" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="D10" s="21" t="n">
+      <c r="D10" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="E10" s="19" t="n"/>
+      <c r="E10" s="18" t="n"/>
       <c r="F10" s="4" t="inlineStr"/>
       <c r="G10" s="4" t="inlineStr">
         <is>
@@ -1321,18 +1324,18 @@
           <t>日中一時支援事業</t>
         </is>
       </c>
-      <c r="B11" s="9" t="inlineStr">
+      <c r="B11" s="34" t="inlineStr">
         <is>
           <t>人</t>
         </is>
       </c>
-      <c r="C11" s="30" t="n">
+      <c r="C11" s="29" t="n">
         <v>2</v>
       </c>
-      <c r="D11" s="30" t="n">
+      <c r="D11" s="29" t="n">
         <v>2</v>
       </c>
-      <c r="E11" s="19" t="n"/>
+      <c r="E11" s="18" t="n"/>
       <c r="F11" s="6" t="inlineStr"/>
       <c r="G11" s="6" t="inlineStr">
         <is>
@@ -1351,13 +1354,13 @@
           <t>人</t>
         </is>
       </c>
-      <c r="C12" s="21" t="n">
+      <c r="C12" s="20" t="n">
         <v>3</v>
       </c>
-      <c r="D12" s="21" t="n">
+      <c r="D12" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="E12" s="19" t="n"/>
+      <c r="E12" s="18" t="n"/>
       <c r="F12" s="4" t="inlineStr"/>
       <c r="G12" s="4" t="inlineStr">
         <is>
@@ -1371,18 +1374,18 @@
           <t>訪問入浴サービス事業</t>
         </is>
       </c>
-      <c r="B13" s="9" t="inlineStr">
+      <c r="B13" s="34" t="inlineStr">
         <is>
           <t>人</t>
         </is>
       </c>
-      <c r="C13" s="30" t="n">
+      <c r="C13" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="D13" s="30" t="n">
+      <c r="D13" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="E13" s="19" t="n"/>
+      <c r="E13" s="18" t="n"/>
       <c r="F13" s="6" t="inlineStr"/>
       <c r="G13" s="6" t="inlineStr">
         <is>
@@ -1401,13 +1404,13 @@
           <t>件</t>
         </is>
       </c>
-      <c r="C14" s="21" t="n">
+      <c r="C14" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="D14" s="21" t="n">
+      <c r="D14" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="E14" s="19" t="n"/>
+      <c r="E14" s="18" t="n"/>
       <c r="F14" s="4" t="inlineStr"/>
       <c r="G14" s="4" t="inlineStr">
         <is>
@@ -1421,18 +1424,18 @@
           <t>自発的活動支援事業</t>
         </is>
       </c>
-      <c r="B15" s="9" t="inlineStr">
+      <c r="B15" s="34" t="inlineStr">
         <is>
           <t>件</t>
         </is>
       </c>
-      <c r="C15" s="30" t="n">
+      <c r="C15" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="D15" s="30" t="n">
+      <c r="D15" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="E15" s="19" t="n"/>
+      <c r="E15" s="18" t="n"/>
       <c r="F15" s="6" t="inlineStr"/>
       <c r="G15" s="6" t="inlineStr">
         <is>
@@ -1466,7 +1469,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>村への確認・依頼事項（見込量推計関係）</t>
         </is>
@@ -1549,7 +1552,7 @@
           <t>02／06_65歳移行判定</t>
         </is>
       </c>
-      <c r="D7" s="9" t="inlineStr">
+      <c r="D7" s="34" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -1603,7 +1606,7 @@
           <t>02／03_生活介護・就労系</t>
         </is>
       </c>
-      <c r="D9" s="9" t="inlineStr">
+      <c r="D9" s="34" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -1657,7 +1660,7 @@
           <t>04／計画本文の記述</t>
         </is>
       </c>
-      <c r="D11" s="9" t="inlineStr">
+      <c r="D11" s="34" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -1711,7 +1714,7 @@
           <t>02／03</t>
         </is>
       </c>
-      <c r="D13" s="9" t="inlineStr">
+      <c r="D13" s="34" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -1765,7 +1768,7 @@
           <t>06_65歳移行判定</t>
         </is>
       </c>
-      <c r="D15" s="9" t="inlineStr">
+      <c r="D15" s="34" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -1827,7 +1830,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>基本指針 別表第一が勘案を求める要素（サービス別）</t>
         </is>
@@ -2368,13 +2371,13 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
     <col width="52" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>基本指針 別表第五（地域差是正）の適用判定</t>
         </is>
@@ -2383,12 +2386,12 @@
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>第8期で新設。要件に該当する市町村は、全国の伸び率を用いた算定方法を基本とすることになる。本村が該当するかを確定するまで、見込量の算定方法は確定しない。</t>
+          <t>第8期で新設。要件に該当する市町村は、全国の伸び率を用いた算定方法を基本とすることになる。本村は過疎法第2条により全域が過疎地域に該当するため（福島県「県内の過疎・中山間地域の指定状況」令和7年4月1日現在）、同表一の項⑴を満たさず適用対象外。個別積上げ方式を原則どおり採用できる。</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="10" t="inlineStr">
+      <c r="A5" s="9" t="inlineStr">
         <is>
           <t>■ 条文（第三の二の2(一)ただし書及び別表第五）</t>
         </is>
@@ -2423,7 +2426,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="10" t="inlineStr">
+      <c r="A11" s="9" t="inlineStr">
         <is>
           <t>■ 判定</t>
         </is>
@@ -2451,70 +2454,70 @@
         </is>
       </c>
     </row>
-    <row r="13">
+    <row r="13" ht="46" customHeight="1">
       <c r="A13" s="4" t="inlineStr">
         <is>
           <t>⑴ 本村の過疎区分</t>
         </is>
       </c>
-      <c r="B13" s="16" t="inlineStr">
-        <is>
-          <t>全部過疎（見込）</t>
+      <c r="B13" s="36" t="inlineStr">
+        <is>
+          <t>全部過疎（確定）</t>
         </is>
       </c>
       <c r="C13" s="8">
-        <f>IF(B13="全部過疎（見込）","要件⑴を満たさない→別表第五 適用外","要確認")</f>
+        <f>IF(B13="全部過疎（確定）","要件⑴を満たさない→別表第五 適用外","要確認")</f>
         <v/>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>総務省が公表する過疎地域市町村一覧で確認する。北塩原村は過疎地域であり、市町村合併を経ていないため全部過疎と考えられる。</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
+          <t>福島県「県内の過疎・中山間地域の指定状況」（令和7年4月1日現在）において、北塩原村は過疎法第2条により全域が過疎地域に該当する市町村（◎）と表示されている。旧北山村・旧大塩村・旧檜原村の3区域とも過疎地域・振興山村地域・特定農山村地域に該当。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="46" customHeight="1">
       <c r="A14" s="6" t="inlineStr">
         <is>
           <t>⑵ サービス利用者割合</t>
         </is>
       </c>
-      <c r="B14" s="16" t="inlineStr">
-        <is>
-          <t>村資料・国公表データ待ち</t>
-        </is>
-      </c>
-      <c r="C14" s="9" t="inlineStr">
+      <c r="B14" s="34" t="inlineStr">
+        <is>
+          <t>判定不要</t>
+        </is>
+      </c>
+      <c r="C14" s="34" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>18歳以上人口（障害児通所支援は18歳未満人口）に占める利用者割合が、全部過疎でない市町村の上位25%以内かどうか。⑴を満たさない場合は判定不要。</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
+          <t>18歳以上人口（障害児通所支援は18歳未満人口）に占める利用者割合が、全部過疎でない市町村の上位25%以内かどうか。⑴を満たさないため判定不要。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="46" customHeight="1">
       <c r="A15" s="4" t="inlineStr">
         <is>
           <t>結論</t>
         </is>
       </c>
       <c r="B15" s="8" t="n"/>
-      <c r="C15" s="25">
+      <c r="C15" s="24">
         <f>IF(C13="要件⑴を満たさない→別表第五 適用外","個別積上げ方式を採用可（第三の二の2(一)本文による）","要判定")</f>
         <v/>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>⑴かつ⑵の連言であるため、⑴を満たさなければ別表第五 二の項の算定方法は適用されない。</t>
+          <t>⑴かつ⑵の連言であるため、⑴を満たさない本村には別表第五 二の項の算定方法は適用されない。第三の二の2(一)本文の一般則により、実績分析・意向・心身の状況を勘案して設定する。</t>
         </is>
       </c>
     </row>
     <row r="17" ht="34" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>※ 仮に本村が全部過疎に該当しない場合でも、第三の二の2(一)⑵により、地域の具体的なニーズ調査を踏まえて別の算定方法を採ることができる。その場合は、個別積上げ方式を採る必要性及び根拠を計画本文に明記することが要件となる。</t>
+          <t>※ あわせて本村は福島県過疎・中山間地域振興条例の中山間地域（全域）にも該当する。基本指針 第一の一の3は「中山間・人口減少地域においては、共生型サービスや基準該当障害福祉サービス、多機能型、従たる事業所等の現行制度の活用等も図りつつ、サービス提供体制を維持・確保していくことが重要」としており、見直し事項⑩「人口減少地域におけるサービスの維持・確保」に正面から該当する。</t>
         </is>
       </c>
     </row>
@@ -2557,7 +2560,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>見込量の推計方式</t>
         </is>
@@ -2571,7 +2574,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="10" t="inlineStr">
+      <c r="A5" s="9" t="inlineStr">
         <is>
           <t>1. 算式</t>
         </is>
@@ -2629,7 +2632,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="10" t="inlineStr">
+      <c r="A10" s="9" t="inlineStr">
         <is>
           <t>2. 推計対象の3層</t>
         </is>
@@ -2707,7 +2710,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="10" t="inlineStr">
+      <c r="A16" s="9" t="inlineStr">
         <is>
           <t>3. 年齢到達の扱い</t>
         </is>
@@ -2833,7 +2836,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="10" t="inlineStr">
+      <c r="A25" s="9" t="inlineStr">
         <is>
           <t>4. 県内他団体の推計方法との関係</t>
         </is>
@@ -2951,7 +2954,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>年齢到達者一覧（匿名台帳）</t>
         </is>
@@ -3030,376 +3033,376 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>（例）001</t>
         </is>
       </c>
-      <c r="B6" s="13" t="inlineStr">
+      <c r="B6" s="12" t="inlineStr">
         <is>
           <t>65歳</t>
         </is>
       </c>
-      <c r="C6" s="13" t="inlineStr">
+      <c r="C6" s="12" t="inlineStr">
         <is>
           <t>令和10年度</t>
         </is>
       </c>
-      <c r="D6" s="13" t="inlineStr">
+      <c r="D6" s="12" t="inlineStr">
         <is>
           <t>65</t>
         </is>
       </c>
-      <c r="E6" s="13" t="inlineStr">
+      <c r="E6" s="12" t="inlineStr">
         <is>
           <t>区分4</t>
         </is>
       </c>
-      <c r="F6" s="14" t="inlineStr">
+      <c r="F6" s="13" t="inlineStr">
         <is>
           <t>生活介護、居宅介護</t>
         </is>
       </c>
-      <c r="G6" s="13" t="inlineStr">
+      <c r="G6" s="12" t="inlineStr">
         <is>
           <t>あり</t>
         </is>
       </c>
-      <c r="H6" s="13" t="inlineStr">
+      <c r="H6" s="12" t="inlineStr">
         <is>
           <t>一部</t>
         </is>
       </c>
-      <c r="I6" s="13" t="inlineStr">
+      <c r="I6" s="12" t="inlineStr">
         <is>
           <t>生活介護は継続</t>
         </is>
       </c>
-      <c r="J6" s="15" t="inlineStr">
+      <c r="J6" s="14" t="inlineStr">
         <is>
           <t>-10人日</t>
         </is>
       </c>
-      <c r="K6" s="14" t="inlineStr">
+      <c r="K6" s="13" t="inlineStr">
         <is>
           <t>例示。実データではありません</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="16" t="n"/>
-      <c r="B7" s="16" t="n"/>
-      <c r="C7" s="16" t="n"/>
-      <c r="D7" s="16" t="n"/>
-      <c r="E7" s="16" t="n"/>
-      <c r="F7" s="17" t="n"/>
-      <c r="G7" s="16" t="n"/>
-      <c r="H7" s="16" t="n"/>
-      <c r="I7" s="16" t="n"/>
-      <c r="J7" s="18" t="n"/>
-      <c r="K7" s="17" t="n"/>
+      <c r="A7" s="15" t="n"/>
+      <c r="B7" s="15" t="n"/>
+      <c r="C7" s="15" t="n"/>
+      <c r="D7" s="15" t="n"/>
+      <c r="E7" s="15" t="n"/>
+      <c r="F7" s="16" t="n"/>
+      <c r="G7" s="15" t="n"/>
+      <c r="H7" s="15" t="n"/>
+      <c r="I7" s="15" t="n"/>
+      <c r="J7" s="17" t="n"/>
+      <c r="K7" s="16" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="16" t="n"/>
-      <c r="B8" s="16" t="n"/>
-      <c r="C8" s="16" t="n"/>
-      <c r="D8" s="16" t="n"/>
-      <c r="E8" s="16" t="n"/>
-      <c r="F8" s="17" t="n"/>
-      <c r="G8" s="16" t="n"/>
-      <c r="H8" s="16" t="n"/>
-      <c r="I8" s="16" t="n"/>
-      <c r="J8" s="18" t="n"/>
-      <c r="K8" s="17" t="n"/>
+      <c r="A8" s="15" t="n"/>
+      <c r="B8" s="15" t="n"/>
+      <c r="C8" s="15" t="n"/>
+      <c r="D8" s="15" t="n"/>
+      <c r="E8" s="15" t="n"/>
+      <c r="F8" s="16" t="n"/>
+      <c r="G8" s="15" t="n"/>
+      <c r="H8" s="15" t="n"/>
+      <c r="I8" s="15" t="n"/>
+      <c r="J8" s="17" t="n"/>
+      <c r="K8" s="16" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="16" t="n"/>
-      <c r="B9" s="16" t="n"/>
-      <c r="C9" s="16" t="n"/>
-      <c r="D9" s="16" t="n"/>
-      <c r="E9" s="16" t="n"/>
-      <c r="F9" s="17" t="n"/>
-      <c r="G9" s="16" t="n"/>
-      <c r="H9" s="16" t="n"/>
-      <c r="I9" s="16" t="n"/>
-      <c r="J9" s="18" t="n"/>
-      <c r="K9" s="17" t="n"/>
+      <c r="A9" s="15" t="n"/>
+      <c r="B9" s="15" t="n"/>
+      <c r="C9" s="15" t="n"/>
+      <c r="D9" s="15" t="n"/>
+      <c r="E9" s="15" t="n"/>
+      <c r="F9" s="16" t="n"/>
+      <c r="G9" s="15" t="n"/>
+      <c r="H9" s="15" t="n"/>
+      <c r="I9" s="15" t="n"/>
+      <c r="J9" s="17" t="n"/>
+      <c r="K9" s="16" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="16" t="n"/>
-      <c r="B10" s="16" t="n"/>
-      <c r="C10" s="16" t="n"/>
-      <c r="D10" s="16" t="n"/>
-      <c r="E10" s="16" t="n"/>
-      <c r="F10" s="17" t="n"/>
-      <c r="G10" s="16" t="n"/>
-      <c r="H10" s="16" t="n"/>
-      <c r="I10" s="16" t="n"/>
-      <c r="J10" s="18" t="n"/>
-      <c r="K10" s="17" t="n"/>
+      <c r="A10" s="15" t="n"/>
+      <c r="B10" s="15" t="n"/>
+      <c r="C10" s="15" t="n"/>
+      <c r="D10" s="15" t="n"/>
+      <c r="E10" s="15" t="n"/>
+      <c r="F10" s="16" t="n"/>
+      <c r="G10" s="15" t="n"/>
+      <c r="H10" s="15" t="n"/>
+      <c r="I10" s="15" t="n"/>
+      <c r="J10" s="17" t="n"/>
+      <c r="K10" s="16" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="16" t="n"/>
-      <c r="B11" s="16" t="n"/>
-      <c r="C11" s="16" t="n"/>
-      <c r="D11" s="16" t="n"/>
-      <c r="E11" s="16" t="n"/>
-      <c r="F11" s="17" t="n"/>
-      <c r="G11" s="16" t="n"/>
-      <c r="H11" s="16" t="n"/>
-      <c r="I11" s="16" t="n"/>
-      <c r="J11" s="18" t="n"/>
-      <c r="K11" s="17" t="n"/>
+      <c r="A11" s="15" t="n"/>
+      <c r="B11" s="15" t="n"/>
+      <c r="C11" s="15" t="n"/>
+      <c r="D11" s="15" t="n"/>
+      <c r="E11" s="15" t="n"/>
+      <c r="F11" s="16" t="n"/>
+      <c r="G11" s="15" t="n"/>
+      <c r="H11" s="15" t="n"/>
+      <c r="I11" s="15" t="n"/>
+      <c r="J11" s="17" t="n"/>
+      <c r="K11" s="16" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="16" t="n"/>
-      <c r="B12" s="16" t="n"/>
-      <c r="C12" s="16" t="n"/>
-      <c r="D12" s="16" t="n"/>
-      <c r="E12" s="16" t="n"/>
-      <c r="F12" s="17" t="n"/>
-      <c r="G12" s="16" t="n"/>
-      <c r="H12" s="16" t="n"/>
-      <c r="I12" s="16" t="n"/>
-      <c r="J12" s="18" t="n"/>
-      <c r="K12" s="17" t="n"/>
+      <c r="A12" s="15" t="n"/>
+      <c r="B12" s="15" t="n"/>
+      <c r="C12" s="15" t="n"/>
+      <c r="D12" s="15" t="n"/>
+      <c r="E12" s="15" t="n"/>
+      <c r="F12" s="16" t="n"/>
+      <c r="G12" s="15" t="n"/>
+      <c r="H12" s="15" t="n"/>
+      <c r="I12" s="15" t="n"/>
+      <c r="J12" s="17" t="n"/>
+      <c r="K12" s="16" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="16" t="n"/>
-      <c r="B13" s="16" t="n"/>
-      <c r="C13" s="16" t="n"/>
-      <c r="D13" s="16" t="n"/>
-      <c r="E13" s="16" t="n"/>
-      <c r="F13" s="17" t="n"/>
-      <c r="G13" s="16" t="n"/>
-      <c r="H13" s="16" t="n"/>
-      <c r="I13" s="16" t="n"/>
-      <c r="J13" s="18" t="n"/>
-      <c r="K13" s="17" t="n"/>
+      <c r="A13" s="15" t="n"/>
+      <c r="B13" s="15" t="n"/>
+      <c r="C13" s="15" t="n"/>
+      <c r="D13" s="15" t="n"/>
+      <c r="E13" s="15" t="n"/>
+      <c r="F13" s="16" t="n"/>
+      <c r="G13" s="15" t="n"/>
+      <c r="H13" s="15" t="n"/>
+      <c r="I13" s="15" t="n"/>
+      <c r="J13" s="17" t="n"/>
+      <c r="K13" s="16" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="16" t="n"/>
-      <c r="B14" s="16" t="n"/>
-      <c r="C14" s="16" t="n"/>
-      <c r="D14" s="16" t="n"/>
-      <c r="E14" s="16" t="n"/>
-      <c r="F14" s="17" t="n"/>
-      <c r="G14" s="16" t="n"/>
-      <c r="H14" s="16" t="n"/>
-      <c r="I14" s="16" t="n"/>
-      <c r="J14" s="18" t="n"/>
-      <c r="K14" s="17" t="n"/>
+      <c r="A14" s="15" t="n"/>
+      <c r="B14" s="15" t="n"/>
+      <c r="C14" s="15" t="n"/>
+      <c r="D14" s="15" t="n"/>
+      <c r="E14" s="15" t="n"/>
+      <c r="F14" s="16" t="n"/>
+      <c r="G14" s="15" t="n"/>
+      <c r="H14" s="15" t="n"/>
+      <c r="I14" s="15" t="n"/>
+      <c r="J14" s="17" t="n"/>
+      <c r="K14" s="16" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="16" t="n"/>
-      <c r="B15" s="16" t="n"/>
-      <c r="C15" s="16" t="n"/>
-      <c r="D15" s="16" t="n"/>
-      <c r="E15" s="16" t="n"/>
-      <c r="F15" s="17" t="n"/>
-      <c r="G15" s="16" t="n"/>
-      <c r="H15" s="16" t="n"/>
-      <c r="I15" s="16" t="n"/>
-      <c r="J15" s="18" t="n"/>
-      <c r="K15" s="17" t="n"/>
+      <c r="A15" s="15" t="n"/>
+      <c r="B15" s="15" t="n"/>
+      <c r="C15" s="15" t="n"/>
+      <c r="D15" s="15" t="n"/>
+      <c r="E15" s="15" t="n"/>
+      <c r="F15" s="16" t="n"/>
+      <c r="G15" s="15" t="n"/>
+      <c r="H15" s="15" t="n"/>
+      <c r="I15" s="15" t="n"/>
+      <c r="J15" s="17" t="n"/>
+      <c r="K15" s="16" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="16" t="n"/>
-      <c r="B16" s="16" t="n"/>
-      <c r="C16" s="16" t="n"/>
-      <c r="D16" s="16" t="n"/>
-      <c r="E16" s="16" t="n"/>
-      <c r="F16" s="17" t="n"/>
-      <c r="G16" s="16" t="n"/>
-      <c r="H16" s="16" t="n"/>
-      <c r="I16" s="16" t="n"/>
-      <c r="J16" s="18" t="n"/>
-      <c r="K16" s="17" t="n"/>
+      <c r="A16" s="15" t="n"/>
+      <c r="B16" s="15" t="n"/>
+      <c r="C16" s="15" t="n"/>
+      <c r="D16" s="15" t="n"/>
+      <c r="E16" s="15" t="n"/>
+      <c r="F16" s="16" t="n"/>
+      <c r="G16" s="15" t="n"/>
+      <c r="H16" s="15" t="n"/>
+      <c r="I16" s="15" t="n"/>
+      <c r="J16" s="17" t="n"/>
+      <c r="K16" s="16" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="16" t="n"/>
-      <c r="B17" s="16" t="n"/>
-      <c r="C17" s="16" t="n"/>
-      <c r="D17" s="16" t="n"/>
-      <c r="E17" s="16" t="n"/>
-      <c r="F17" s="17" t="n"/>
-      <c r="G17" s="16" t="n"/>
-      <c r="H17" s="16" t="n"/>
-      <c r="I17" s="16" t="n"/>
-      <c r="J17" s="18" t="n"/>
-      <c r="K17" s="17" t="n"/>
+      <c r="A17" s="15" t="n"/>
+      <c r="B17" s="15" t="n"/>
+      <c r="C17" s="15" t="n"/>
+      <c r="D17" s="15" t="n"/>
+      <c r="E17" s="15" t="n"/>
+      <c r="F17" s="16" t="n"/>
+      <c r="G17" s="15" t="n"/>
+      <c r="H17" s="15" t="n"/>
+      <c r="I17" s="15" t="n"/>
+      <c r="J17" s="17" t="n"/>
+      <c r="K17" s="16" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="16" t="n"/>
-      <c r="B18" s="16" t="n"/>
-      <c r="C18" s="16" t="n"/>
-      <c r="D18" s="16" t="n"/>
-      <c r="E18" s="16" t="n"/>
-      <c r="F18" s="17" t="n"/>
-      <c r="G18" s="16" t="n"/>
-      <c r="H18" s="16" t="n"/>
-      <c r="I18" s="16" t="n"/>
-      <c r="J18" s="18" t="n"/>
-      <c r="K18" s="17" t="n"/>
+      <c r="A18" s="15" t="n"/>
+      <c r="B18" s="15" t="n"/>
+      <c r="C18" s="15" t="n"/>
+      <c r="D18" s="15" t="n"/>
+      <c r="E18" s="15" t="n"/>
+      <c r="F18" s="16" t="n"/>
+      <c r="G18" s="15" t="n"/>
+      <c r="H18" s="15" t="n"/>
+      <c r="I18" s="15" t="n"/>
+      <c r="J18" s="17" t="n"/>
+      <c r="K18" s="16" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="16" t="n"/>
-      <c r="B19" s="16" t="n"/>
-      <c r="C19" s="16" t="n"/>
-      <c r="D19" s="16" t="n"/>
-      <c r="E19" s="16" t="n"/>
-      <c r="F19" s="17" t="n"/>
-      <c r="G19" s="16" t="n"/>
-      <c r="H19" s="16" t="n"/>
-      <c r="I19" s="16" t="n"/>
-      <c r="J19" s="18" t="n"/>
-      <c r="K19" s="17" t="n"/>
+      <c r="A19" s="15" t="n"/>
+      <c r="B19" s="15" t="n"/>
+      <c r="C19" s="15" t="n"/>
+      <c r="D19" s="15" t="n"/>
+      <c r="E19" s="15" t="n"/>
+      <c r="F19" s="16" t="n"/>
+      <c r="G19" s="15" t="n"/>
+      <c r="H19" s="15" t="n"/>
+      <c r="I19" s="15" t="n"/>
+      <c r="J19" s="17" t="n"/>
+      <c r="K19" s="16" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="16" t="n"/>
-      <c r="B20" s="16" t="n"/>
-      <c r="C20" s="16" t="n"/>
-      <c r="D20" s="16" t="n"/>
-      <c r="E20" s="16" t="n"/>
-      <c r="F20" s="17" t="n"/>
-      <c r="G20" s="16" t="n"/>
-      <c r="H20" s="16" t="n"/>
-      <c r="I20" s="16" t="n"/>
-      <c r="J20" s="18" t="n"/>
-      <c r="K20" s="17" t="n"/>
+      <c r="A20" s="15" t="n"/>
+      <c r="B20" s="15" t="n"/>
+      <c r="C20" s="15" t="n"/>
+      <c r="D20" s="15" t="n"/>
+      <c r="E20" s="15" t="n"/>
+      <c r="F20" s="16" t="n"/>
+      <c r="G20" s="15" t="n"/>
+      <c r="H20" s="15" t="n"/>
+      <c r="I20" s="15" t="n"/>
+      <c r="J20" s="17" t="n"/>
+      <c r="K20" s="16" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="16" t="n"/>
-      <c r="B21" s="16" t="n"/>
-      <c r="C21" s="16" t="n"/>
-      <c r="D21" s="16" t="n"/>
-      <c r="E21" s="16" t="n"/>
-      <c r="F21" s="17" t="n"/>
-      <c r="G21" s="16" t="n"/>
-      <c r="H21" s="16" t="n"/>
-      <c r="I21" s="16" t="n"/>
-      <c r="J21" s="18" t="n"/>
-      <c r="K21" s="17" t="n"/>
+      <c r="A21" s="15" t="n"/>
+      <c r="B21" s="15" t="n"/>
+      <c r="C21" s="15" t="n"/>
+      <c r="D21" s="15" t="n"/>
+      <c r="E21" s="15" t="n"/>
+      <c r="F21" s="16" t="n"/>
+      <c r="G21" s="15" t="n"/>
+      <c r="H21" s="15" t="n"/>
+      <c r="I21" s="15" t="n"/>
+      <c r="J21" s="17" t="n"/>
+      <c r="K21" s="16" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="16" t="n"/>
-      <c r="B22" s="16" t="n"/>
-      <c r="C22" s="16" t="n"/>
-      <c r="D22" s="16" t="n"/>
-      <c r="E22" s="16" t="n"/>
-      <c r="F22" s="17" t="n"/>
-      <c r="G22" s="16" t="n"/>
-      <c r="H22" s="16" t="n"/>
-      <c r="I22" s="16" t="n"/>
-      <c r="J22" s="18" t="n"/>
-      <c r="K22" s="17" t="n"/>
+      <c r="A22" s="15" t="n"/>
+      <c r="B22" s="15" t="n"/>
+      <c r="C22" s="15" t="n"/>
+      <c r="D22" s="15" t="n"/>
+      <c r="E22" s="15" t="n"/>
+      <c r="F22" s="16" t="n"/>
+      <c r="G22" s="15" t="n"/>
+      <c r="H22" s="15" t="n"/>
+      <c r="I22" s="15" t="n"/>
+      <c r="J22" s="17" t="n"/>
+      <c r="K22" s="16" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="16" t="n"/>
-      <c r="B23" s="16" t="n"/>
-      <c r="C23" s="16" t="n"/>
-      <c r="D23" s="16" t="n"/>
-      <c r="E23" s="16" t="n"/>
-      <c r="F23" s="17" t="n"/>
-      <c r="G23" s="16" t="n"/>
-      <c r="H23" s="16" t="n"/>
-      <c r="I23" s="16" t="n"/>
-      <c r="J23" s="18" t="n"/>
-      <c r="K23" s="17" t="n"/>
+      <c r="A23" s="15" t="n"/>
+      <c r="B23" s="15" t="n"/>
+      <c r="C23" s="15" t="n"/>
+      <c r="D23" s="15" t="n"/>
+      <c r="E23" s="15" t="n"/>
+      <c r="F23" s="16" t="n"/>
+      <c r="G23" s="15" t="n"/>
+      <c r="H23" s="15" t="n"/>
+      <c r="I23" s="15" t="n"/>
+      <c r="J23" s="17" t="n"/>
+      <c r="K23" s="16" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="16" t="n"/>
-      <c r="B24" s="16" t="n"/>
-      <c r="C24" s="16" t="n"/>
-      <c r="D24" s="16" t="n"/>
-      <c r="E24" s="16" t="n"/>
-      <c r="F24" s="17" t="n"/>
-      <c r="G24" s="16" t="n"/>
-      <c r="H24" s="16" t="n"/>
-      <c r="I24" s="16" t="n"/>
-      <c r="J24" s="18" t="n"/>
-      <c r="K24" s="17" t="n"/>
+      <c r="A24" s="15" t="n"/>
+      <c r="B24" s="15" t="n"/>
+      <c r="C24" s="15" t="n"/>
+      <c r="D24" s="15" t="n"/>
+      <c r="E24" s="15" t="n"/>
+      <c r="F24" s="16" t="n"/>
+      <c r="G24" s="15" t="n"/>
+      <c r="H24" s="15" t="n"/>
+      <c r="I24" s="15" t="n"/>
+      <c r="J24" s="17" t="n"/>
+      <c r="K24" s="16" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="16" t="n"/>
-      <c r="B25" s="16" t="n"/>
-      <c r="C25" s="16" t="n"/>
-      <c r="D25" s="16" t="n"/>
-      <c r="E25" s="16" t="n"/>
-      <c r="F25" s="17" t="n"/>
-      <c r="G25" s="16" t="n"/>
-      <c r="H25" s="16" t="n"/>
-      <c r="I25" s="16" t="n"/>
-      <c r="J25" s="18" t="n"/>
-      <c r="K25" s="17" t="n"/>
+      <c r="A25" s="15" t="n"/>
+      <c r="B25" s="15" t="n"/>
+      <c r="C25" s="15" t="n"/>
+      <c r="D25" s="15" t="n"/>
+      <c r="E25" s="15" t="n"/>
+      <c r="F25" s="16" t="n"/>
+      <c r="G25" s="15" t="n"/>
+      <c r="H25" s="15" t="n"/>
+      <c r="I25" s="15" t="n"/>
+      <c r="J25" s="17" t="n"/>
+      <c r="K25" s="16" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="16" t="n"/>
-      <c r="B26" s="16" t="n"/>
-      <c r="C26" s="16" t="n"/>
-      <c r="D26" s="16" t="n"/>
-      <c r="E26" s="16" t="n"/>
-      <c r="F26" s="17" t="n"/>
-      <c r="G26" s="16" t="n"/>
-      <c r="H26" s="16" t="n"/>
-      <c r="I26" s="16" t="n"/>
-      <c r="J26" s="18" t="n"/>
-      <c r="K26" s="17" t="n"/>
+      <c r="A26" s="15" t="n"/>
+      <c r="B26" s="15" t="n"/>
+      <c r="C26" s="15" t="n"/>
+      <c r="D26" s="15" t="n"/>
+      <c r="E26" s="15" t="n"/>
+      <c r="F26" s="16" t="n"/>
+      <c r="G26" s="15" t="n"/>
+      <c r="H26" s="15" t="n"/>
+      <c r="I26" s="15" t="n"/>
+      <c r="J26" s="17" t="n"/>
+      <c r="K26" s="16" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="16" t="n"/>
-      <c r="B27" s="16" t="n"/>
-      <c r="C27" s="16" t="n"/>
-      <c r="D27" s="16" t="n"/>
-      <c r="E27" s="16" t="n"/>
-      <c r="F27" s="17" t="n"/>
-      <c r="G27" s="16" t="n"/>
-      <c r="H27" s="16" t="n"/>
-      <c r="I27" s="16" t="n"/>
-      <c r="J27" s="18" t="n"/>
-      <c r="K27" s="17" t="n"/>
+      <c r="A27" s="15" t="n"/>
+      <c r="B27" s="15" t="n"/>
+      <c r="C27" s="15" t="n"/>
+      <c r="D27" s="15" t="n"/>
+      <c r="E27" s="15" t="n"/>
+      <c r="F27" s="16" t="n"/>
+      <c r="G27" s="15" t="n"/>
+      <c r="H27" s="15" t="n"/>
+      <c r="I27" s="15" t="n"/>
+      <c r="J27" s="17" t="n"/>
+      <c r="K27" s="16" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="16" t="n"/>
-      <c r="B28" s="16" t="n"/>
-      <c r="C28" s="16" t="n"/>
-      <c r="D28" s="16" t="n"/>
-      <c r="E28" s="16" t="n"/>
-      <c r="F28" s="17" t="n"/>
-      <c r="G28" s="16" t="n"/>
-      <c r="H28" s="16" t="n"/>
-      <c r="I28" s="16" t="n"/>
-      <c r="J28" s="18" t="n"/>
-      <c r="K28" s="17" t="n"/>
+      <c r="A28" s="15" t="n"/>
+      <c r="B28" s="15" t="n"/>
+      <c r="C28" s="15" t="n"/>
+      <c r="D28" s="15" t="n"/>
+      <c r="E28" s="15" t="n"/>
+      <c r="F28" s="16" t="n"/>
+      <c r="G28" s="15" t="n"/>
+      <c r="H28" s="15" t="n"/>
+      <c r="I28" s="15" t="n"/>
+      <c r="J28" s="17" t="n"/>
+      <c r="K28" s="16" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="16" t="n"/>
-      <c r="B29" s="16" t="n"/>
-      <c r="C29" s="16" t="n"/>
-      <c r="D29" s="16" t="n"/>
-      <c r="E29" s="16" t="n"/>
-      <c r="F29" s="17" t="n"/>
-      <c r="G29" s="16" t="n"/>
-      <c r="H29" s="16" t="n"/>
-      <c r="I29" s="16" t="n"/>
-      <c r="J29" s="18" t="n"/>
-      <c r="K29" s="17" t="n"/>
+      <c r="A29" s="15" t="n"/>
+      <c r="B29" s="15" t="n"/>
+      <c r="C29" s="15" t="n"/>
+      <c r="D29" s="15" t="n"/>
+      <c r="E29" s="15" t="n"/>
+      <c r="F29" s="16" t="n"/>
+      <c r="G29" s="15" t="n"/>
+      <c r="H29" s="15" t="n"/>
+      <c r="I29" s="15" t="n"/>
+      <c r="J29" s="17" t="n"/>
+      <c r="K29" s="16" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="16" t="n"/>
-      <c r="B30" s="16" t="n"/>
-      <c r="C30" s="16" t="n"/>
-      <c r="D30" s="16" t="n"/>
-      <c r="E30" s="16" t="n"/>
-      <c r="F30" s="17" t="n"/>
-      <c r="G30" s="16" t="n"/>
-      <c r="H30" s="16" t="n"/>
-      <c r="I30" s="16" t="n"/>
-      <c r="J30" s="18" t="n"/>
-      <c r="K30" s="17" t="n"/>
+      <c r="A30" s="15" t="n"/>
+      <c r="B30" s="15" t="n"/>
+      <c r="C30" s="15" t="n"/>
+      <c r="D30" s="15" t="n"/>
+      <c r="E30" s="15" t="n"/>
+      <c r="F30" s="16" t="n"/>
+      <c r="G30" s="15" t="n"/>
+      <c r="H30" s="15" t="n"/>
+      <c r="I30" s="15" t="n"/>
+      <c r="J30" s="17" t="n"/>
+      <c r="K30" s="16" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="10" t="inlineStr">
+      <c r="A32" s="9" t="inlineStr">
         <is>
           <t>記入のしかた</t>
         </is>
@@ -3482,7 +3485,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>障害福祉サービスの個別積上げ</t>
         </is>
@@ -3496,7 +3499,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="10" t="inlineStr">
+      <c r="A5" s="9" t="inlineStr">
         <is>
           <t>1　居宅介護</t>
         </is>
@@ -3558,18 +3561,18 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C8" s="19" t="n">
+      <c r="C8" s="18" t="n">
         <v>4</v>
       </c>
-      <c r="D8" s="20">
+      <c r="D8" s="19">
         <f>C15</f>
         <v/>
       </c>
-      <c r="E8" s="20">
+      <c r="E8" s="19">
         <f>D15</f>
         <v/>
       </c>
-      <c r="F8" s="20">
+      <c r="F8" s="19">
         <f>E15</f>
         <v/>
       </c>
@@ -3590,10 +3593,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C9" s="21" t="n"/>
-      <c r="D9" s="19" t="n"/>
-      <c r="E9" s="19" t="n"/>
-      <c r="F9" s="19" t="n"/>
+      <c r="C9" s="20" t="n"/>
+      <c r="D9" s="18" t="n"/>
+      <c r="E9" s="18" t="n"/>
+      <c r="F9" s="18" t="n"/>
       <c r="G9" s="4" t="inlineStr">
         <is>
           <t>02_年齢到達者一覧から転記する</t>
@@ -3611,10 +3614,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C10" s="21" t="n"/>
-      <c r="D10" s="19" t="n"/>
-      <c r="E10" s="19" t="n"/>
-      <c r="F10" s="19" t="n"/>
+      <c r="C10" s="20" t="n"/>
+      <c r="D10" s="18" t="n"/>
+      <c r="E10" s="18" t="n"/>
+      <c r="F10" s="18" t="n"/>
       <c r="G10" s="4" t="inlineStr">
         <is>
           <t>移行予定者を個別に確認する</t>
@@ -3632,10 +3635,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C11" s="21" t="n"/>
-      <c r="D11" s="19" t="n"/>
-      <c r="E11" s="19" t="n"/>
-      <c r="F11" s="19" t="n"/>
+      <c r="C11" s="20" t="n"/>
+      <c r="D11" s="18" t="n"/>
+      <c r="E11" s="18" t="n"/>
+      <c r="F11" s="18" t="n"/>
       <c r="G11" s="4" t="inlineStr">
         <is>
           <t>相談支援事業所からの利用開始相談を含む</t>
@@ -3653,10 +3656,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C12" s="22" t="n"/>
-      <c r="D12" s="23" t="n"/>
-      <c r="E12" s="23" t="n"/>
-      <c r="F12" s="23" t="n"/>
+      <c r="C12" s="21" t="n"/>
+      <c r="D12" s="22" t="n"/>
+      <c r="E12" s="22" t="n"/>
+      <c r="F12" s="22" t="n"/>
       <c r="G12" s="4" t="inlineStr">
         <is>
           <t>06_65歳移行判定の結果を反映する。一律に減算しない</t>
@@ -3674,10 +3677,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C13" s="22" t="n"/>
-      <c r="D13" s="23" t="n"/>
-      <c r="E13" s="23" t="n"/>
-      <c r="F13" s="23" t="n"/>
+      <c r="C13" s="21" t="n"/>
+      <c r="D13" s="22" t="n"/>
+      <c r="E13" s="22" t="n"/>
+      <c r="F13" s="22" t="n"/>
       <c r="G13" s="4" t="inlineStr">
         <is>
           <t>就労移行支援からの一般就労等</t>
@@ -3695,10 +3698,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C14" s="22" t="n"/>
-      <c r="D14" s="23" t="n"/>
-      <c r="E14" s="23" t="n"/>
-      <c r="F14" s="23" t="n"/>
+      <c r="C14" s="21" t="n"/>
+      <c r="D14" s="22" t="n"/>
+      <c r="E14" s="22" t="n"/>
+      <c r="F14" s="22" t="n"/>
       <c r="G14" s="4" t="inlineStr">
         <is>
           <t>高齢化が進む本村では主要な減少要因</t>
@@ -3706,29 +3709,29 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="24" t="inlineStr">
+      <c r="A15" s="23" t="inlineStr">
         <is>
           <t>＝　利用者数</t>
         </is>
       </c>
-      <c r="B15" s="25" t="inlineStr">
-        <is>
-          <t>人／月</t>
-        </is>
-      </c>
-      <c r="C15" s="26">
+      <c r="B15" s="24" t="inlineStr">
+        <is>
+          <t>人／月</t>
+        </is>
+      </c>
+      <c r="C15" s="25">
         <f>C8</f>
         <v/>
       </c>
-      <c r="D15" s="26">
+      <c r="D15" s="25">
         <f>D8+SUM(D9:D11)-SUM(D12:D14)</f>
         <v/>
       </c>
-      <c r="E15" s="26">
+      <c r="E15" s="25">
         <f>E8+SUM(E9:E11)-SUM(E12:E14)</f>
         <v/>
       </c>
-      <c r="F15" s="26">
+      <c r="F15" s="25">
         <f>F8+SUM(F9:F11)-SUM(F12:F14)</f>
         <v/>
       </c>
@@ -3749,16 +3752,16 @@
           <t>時間／月</t>
         </is>
       </c>
-      <c r="C16" s="27" t="n">
+      <c r="C16" s="26" t="n">
         <v>10</v>
       </c>
-      <c r="D16" s="27" t="n">
+      <c r="D16" s="26" t="n">
         <v>10</v>
       </c>
-      <c r="E16" s="27" t="n">
+      <c r="E16" s="26" t="n">
         <v>10</v>
       </c>
-      <c r="F16" s="27" t="n">
+      <c r="F16" s="26" t="n">
         <v>10</v>
       </c>
       <c r="G16" s="4" t="inlineStr">
@@ -3768,29 +3771,29 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="24" t="inlineStr">
+      <c r="A17" s="23" t="inlineStr">
         <is>
           <t>＝　月間サービス量</t>
         </is>
       </c>
-      <c r="B17" s="25" t="inlineStr">
+      <c r="B17" s="24" t="inlineStr">
         <is>
           <t>時間／月</t>
         </is>
       </c>
-      <c r="C17" s="28">
+      <c r="C17" s="27">
         <f>ROUND(C15*C16,1)</f>
         <v/>
       </c>
-      <c r="D17" s="28">
+      <c r="D17" s="27">
         <f>ROUND(D15*D16,1)</f>
         <v/>
       </c>
-      <c r="E17" s="28">
+      <c r="E17" s="27">
         <f>ROUND(E15*E16,1)</f>
         <v/>
       </c>
-      <c r="F17" s="28">
+      <c r="F17" s="27">
         <f>ROUND(F15*F16,1)</f>
         <v/>
       </c>
@@ -3801,7 +3804,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="10" t="inlineStr">
+      <c r="A19" s="9" t="inlineStr">
         <is>
           <t>2　生活介護</t>
         </is>
@@ -3863,18 +3866,18 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C22" s="19" t="n">
+      <c r="C22" s="18" t="n">
         <v>6</v>
       </c>
-      <c r="D22" s="20">
+      <c r="D22" s="19">
         <f>C29</f>
         <v/>
       </c>
-      <c r="E22" s="20">
+      <c r="E22" s="19">
         <f>D29</f>
         <v/>
       </c>
-      <c r="F22" s="20">
+      <c r="F22" s="19">
         <f>E29</f>
         <v/>
       </c>
@@ -3895,10 +3898,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C23" s="21" t="n"/>
-      <c r="D23" s="19" t="n"/>
-      <c r="E23" s="19" t="n"/>
-      <c r="F23" s="19" t="n"/>
+      <c r="C23" s="20" t="n"/>
+      <c r="D23" s="18" t="n"/>
+      <c r="E23" s="18" t="n"/>
+      <c r="F23" s="18" t="n"/>
       <c r="G23" s="4" t="inlineStr">
         <is>
           <t>02_年齢到達者一覧から転記する</t>
@@ -3916,10 +3919,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C24" s="21" t="n"/>
-      <c r="D24" s="19" t="n"/>
-      <c r="E24" s="19" t="n"/>
-      <c r="F24" s="19" t="n"/>
+      <c r="C24" s="20" t="n"/>
+      <c r="D24" s="18" t="n"/>
+      <c r="E24" s="18" t="n"/>
+      <c r="F24" s="18" t="n"/>
       <c r="G24" s="4" t="inlineStr">
         <is>
           <t>移行予定者を個別に確認する</t>
@@ -3937,10 +3940,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C25" s="21" t="n"/>
-      <c r="D25" s="19" t="n"/>
-      <c r="E25" s="19" t="n"/>
-      <c r="F25" s="19" t="n"/>
+      <c r="C25" s="20" t="n"/>
+      <c r="D25" s="18" t="n"/>
+      <c r="E25" s="18" t="n"/>
+      <c r="F25" s="18" t="n"/>
       <c r="G25" s="4" t="inlineStr">
         <is>
           <t>相談支援事業所からの利用開始相談を含む</t>
@@ -3958,10 +3961,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C26" s="22" t="n"/>
-      <c r="D26" s="23" t="n"/>
-      <c r="E26" s="23" t="n"/>
-      <c r="F26" s="23" t="n"/>
+      <c r="C26" s="21" t="n"/>
+      <c r="D26" s="22" t="n"/>
+      <c r="E26" s="22" t="n"/>
+      <c r="F26" s="22" t="n"/>
       <c r="G26" s="4" t="inlineStr">
         <is>
           <t>06_65歳移行判定の結果を反映する。一律に減算しない</t>
@@ -3979,10 +3982,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C27" s="22" t="n"/>
-      <c r="D27" s="23" t="n"/>
-      <c r="E27" s="23" t="n"/>
-      <c r="F27" s="23" t="n"/>
+      <c r="C27" s="21" t="n"/>
+      <c r="D27" s="22" t="n"/>
+      <c r="E27" s="22" t="n"/>
+      <c r="F27" s="22" t="n"/>
       <c r="G27" s="4" t="inlineStr">
         <is>
           <t>就労移行支援からの一般就労等</t>
@@ -4000,10 +4003,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C28" s="22" t="n"/>
-      <c r="D28" s="23" t="n"/>
-      <c r="E28" s="23" t="n"/>
-      <c r="F28" s="23" t="n"/>
+      <c r="C28" s="21" t="n"/>
+      <c r="D28" s="22" t="n"/>
+      <c r="E28" s="22" t="n"/>
+      <c r="F28" s="22" t="n"/>
       <c r="G28" s="4" t="inlineStr">
         <is>
           <t>高齢化が進む本村では主要な減少要因</t>
@@ -4011,29 +4014,29 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="24" t="inlineStr">
+      <c r="A29" s="23" t="inlineStr">
         <is>
           <t>＝　利用者数</t>
         </is>
       </c>
-      <c r="B29" s="25" t="inlineStr">
-        <is>
-          <t>人／月</t>
-        </is>
-      </c>
-      <c r="C29" s="26">
+      <c r="B29" s="24" t="inlineStr">
+        <is>
+          <t>人／月</t>
+        </is>
+      </c>
+      <c r="C29" s="25">
         <f>C22</f>
         <v/>
       </c>
-      <c r="D29" s="26">
+      <c r="D29" s="25">
         <f>D22+SUM(D23:D25)-SUM(D26:D28)</f>
         <v/>
       </c>
-      <c r="E29" s="26">
+      <c r="E29" s="25">
         <f>E22+SUM(E23:E25)-SUM(E26:E28)</f>
         <v/>
       </c>
-      <c r="F29" s="26">
+      <c r="F29" s="25">
         <f>F22+SUM(F23:F25)-SUM(F26:F28)</f>
         <v/>
       </c>
@@ -4054,16 +4057,16 @@
           <t>人日／月</t>
         </is>
       </c>
-      <c r="C30" s="27" t="n">
+      <c r="C30" s="26" t="n">
         <v>19.7</v>
       </c>
-      <c r="D30" s="27" t="n">
+      <c r="D30" s="26" t="n">
         <v>19.7</v>
       </c>
-      <c r="E30" s="27" t="n">
+      <c r="E30" s="26" t="n">
         <v>19.7</v>
       </c>
-      <c r="F30" s="27" t="n">
+      <c r="F30" s="26" t="n">
         <v>19.7</v>
       </c>
       <c r="G30" s="4" t="inlineStr">
@@ -4073,29 +4076,29 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="24" t="inlineStr">
+      <c r="A31" s="23" t="inlineStr">
         <is>
           <t>＝　月間サービス量</t>
         </is>
       </c>
-      <c r="B31" s="25" t="inlineStr">
+      <c r="B31" s="24" t="inlineStr">
         <is>
           <t>人日／月</t>
         </is>
       </c>
-      <c r="C31" s="28">
+      <c r="C31" s="27">
         <f>ROUND(C29*C30,1)</f>
         <v/>
       </c>
-      <c r="D31" s="28">
+      <c r="D31" s="27">
         <f>ROUND(D29*D30,1)</f>
         <v/>
       </c>
-      <c r="E31" s="28">
+      <c r="E31" s="27">
         <f>ROUND(E29*E30,1)</f>
         <v/>
       </c>
-      <c r="F31" s="28">
+      <c r="F31" s="27">
         <f>ROUND(F29*F30,1)</f>
         <v/>
       </c>
@@ -4106,7 +4109,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="10" t="inlineStr">
+      <c r="A33" s="9" t="inlineStr">
         <is>
           <t>3　短期入所（福祉型）</t>
         </is>
@@ -4168,18 +4171,18 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C36" s="19" t="n">
+      <c r="C36" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="D36" s="20">
+      <c r="D36" s="19">
         <f>C43</f>
         <v/>
       </c>
-      <c r="E36" s="20">
+      <c r="E36" s="19">
         <f>D43</f>
         <v/>
       </c>
-      <c r="F36" s="20">
+      <c r="F36" s="19">
         <f>E43</f>
         <v/>
       </c>
@@ -4200,10 +4203,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C37" s="21" t="n"/>
-      <c r="D37" s="19" t="n"/>
-      <c r="E37" s="19" t="n"/>
-      <c r="F37" s="19" t="n"/>
+      <c r="C37" s="20" t="n"/>
+      <c r="D37" s="18" t="n"/>
+      <c r="E37" s="18" t="n"/>
+      <c r="F37" s="18" t="n"/>
       <c r="G37" s="4" t="inlineStr">
         <is>
           <t>02_年齢到達者一覧から転記する</t>
@@ -4221,10 +4224,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C38" s="21" t="n"/>
-      <c r="D38" s="19" t="n"/>
-      <c r="E38" s="19" t="n"/>
-      <c r="F38" s="19" t="n"/>
+      <c r="C38" s="20" t="n"/>
+      <c r="D38" s="18" t="n"/>
+      <c r="E38" s="18" t="n"/>
+      <c r="F38" s="18" t="n"/>
       <c r="G38" s="4" t="inlineStr">
         <is>
           <t>移行予定者を個別に確認する</t>
@@ -4242,10 +4245,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C39" s="21" t="n"/>
-      <c r="D39" s="19" t="n"/>
-      <c r="E39" s="19" t="n"/>
-      <c r="F39" s="19" t="n"/>
+      <c r="C39" s="20" t="n"/>
+      <c r="D39" s="18" t="n"/>
+      <c r="E39" s="18" t="n"/>
+      <c r="F39" s="18" t="n"/>
       <c r="G39" s="4" t="inlineStr">
         <is>
           <t>相談支援事業所からの利用開始相談を含む</t>
@@ -4263,10 +4266,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C40" s="22" t="n"/>
-      <c r="D40" s="23" t="n"/>
-      <c r="E40" s="23" t="n"/>
-      <c r="F40" s="23" t="n"/>
+      <c r="C40" s="21" t="n"/>
+      <c r="D40" s="22" t="n"/>
+      <c r="E40" s="22" t="n"/>
+      <c r="F40" s="22" t="n"/>
       <c r="G40" s="4" t="inlineStr">
         <is>
           <t>06_65歳移行判定の結果を反映する。一律に減算しない</t>
@@ -4284,10 +4287,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C41" s="22" t="n"/>
-      <c r="D41" s="23" t="n"/>
-      <c r="E41" s="23" t="n"/>
-      <c r="F41" s="23" t="n"/>
+      <c r="C41" s="21" t="n"/>
+      <c r="D41" s="22" t="n"/>
+      <c r="E41" s="22" t="n"/>
+      <c r="F41" s="22" t="n"/>
       <c r="G41" s="4" t="inlineStr">
         <is>
           <t>就労移行支援からの一般就労等</t>
@@ -4305,10 +4308,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C42" s="22" t="n"/>
-      <c r="D42" s="23" t="n"/>
-      <c r="E42" s="23" t="n"/>
-      <c r="F42" s="23" t="n"/>
+      <c r="C42" s="21" t="n"/>
+      <c r="D42" s="22" t="n"/>
+      <c r="E42" s="22" t="n"/>
+      <c r="F42" s="22" t="n"/>
       <c r="G42" s="4" t="inlineStr">
         <is>
           <t>高齢化が進む本村では主要な減少要因</t>
@@ -4316,29 +4319,29 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="24" t="inlineStr">
+      <c r="A43" s="23" t="inlineStr">
         <is>
           <t>＝　利用者数</t>
         </is>
       </c>
-      <c r="B43" s="25" t="inlineStr">
-        <is>
-          <t>人／月</t>
-        </is>
-      </c>
-      <c r="C43" s="26">
+      <c r="B43" s="24" t="inlineStr">
+        <is>
+          <t>人／月</t>
+        </is>
+      </c>
+      <c r="C43" s="25">
         <f>C36</f>
         <v/>
       </c>
-      <c r="D43" s="26">
+      <c r="D43" s="25">
         <f>D36+SUM(D37:D39)-SUM(D40:D42)</f>
         <v/>
       </c>
-      <c r="E43" s="26">
+      <c r="E43" s="25">
         <f>E36+SUM(E37:E39)-SUM(E40:E42)</f>
         <v/>
       </c>
-      <c r="F43" s="26">
+      <c r="F43" s="25">
         <f>F36+SUM(F37:F39)-SUM(F40:F42)</f>
         <v/>
       </c>
@@ -4359,10 +4362,10 @@
           <t>人日／月</t>
         </is>
       </c>
-      <c r="C44" s="27" t="n"/>
-      <c r="D44" s="27" t="n"/>
-      <c r="E44" s="27" t="n"/>
-      <c r="F44" s="27" t="n"/>
+      <c r="C44" s="26" t="n"/>
+      <c r="D44" s="26" t="n"/>
+      <c r="E44" s="26" t="n"/>
+      <c r="F44" s="26" t="n"/>
       <c r="G44" s="4" t="inlineStr">
         <is>
           <t>利用者ごとの月間予定量の平均</t>
@@ -4370,29 +4373,29 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="24" t="inlineStr">
+      <c r="A45" s="23" t="inlineStr">
         <is>
           <t>＝　月間サービス量</t>
         </is>
       </c>
-      <c r="B45" s="25" t="inlineStr">
+      <c r="B45" s="24" t="inlineStr">
         <is>
           <t>人日／月</t>
         </is>
       </c>
-      <c r="C45" s="28">
+      <c r="C45" s="27">
         <f>ROUND(C43*C44,1)</f>
         <v/>
       </c>
-      <c r="D45" s="28">
+      <c r="D45" s="27">
         <f>ROUND(D43*D44,1)</f>
         <v/>
       </c>
-      <c r="E45" s="28">
+      <c r="E45" s="27">
         <f>ROUND(E43*E44,1)</f>
         <v/>
       </c>
-      <c r="F45" s="28">
+      <c r="F45" s="27">
         <f>ROUND(F43*F44,1)</f>
         <v/>
       </c>
@@ -4403,7 +4406,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="10" t="inlineStr">
+      <c r="A47" s="9" t="inlineStr">
         <is>
           <t>4　自立訓練（生活訓練）</t>
         </is>
@@ -4465,18 +4468,18 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C50" s="19" t="n">
+      <c r="C50" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="D50" s="20">
+      <c r="D50" s="19">
         <f>C57</f>
         <v/>
       </c>
-      <c r="E50" s="20">
+      <c r="E50" s="19">
         <f>D57</f>
         <v/>
       </c>
-      <c r="F50" s="20">
+      <c r="F50" s="19">
         <f>E57</f>
         <v/>
       </c>
@@ -4497,10 +4500,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C51" s="21" t="n"/>
-      <c r="D51" s="19" t="n"/>
-      <c r="E51" s="19" t="n"/>
-      <c r="F51" s="19" t="n"/>
+      <c r="C51" s="20" t="n"/>
+      <c r="D51" s="18" t="n"/>
+      <c r="E51" s="18" t="n"/>
+      <c r="F51" s="18" t="n"/>
       <c r="G51" s="4" t="inlineStr">
         <is>
           <t>02_年齢到達者一覧から転記する</t>
@@ -4518,10 +4521,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C52" s="21" t="n"/>
-      <c r="D52" s="19" t="n"/>
-      <c r="E52" s="19" t="n"/>
-      <c r="F52" s="19" t="n"/>
+      <c r="C52" s="20" t="n"/>
+      <c r="D52" s="18" t="n"/>
+      <c r="E52" s="18" t="n"/>
+      <c r="F52" s="18" t="n"/>
       <c r="G52" s="4" t="inlineStr">
         <is>
           <t>移行予定者を個別に確認する</t>
@@ -4539,10 +4542,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C53" s="21" t="n"/>
-      <c r="D53" s="19" t="n"/>
-      <c r="E53" s="19" t="n"/>
-      <c r="F53" s="19" t="n"/>
+      <c r="C53" s="20" t="n"/>
+      <c r="D53" s="18" t="n"/>
+      <c r="E53" s="18" t="n"/>
+      <c r="F53" s="18" t="n"/>
       <c r="G53" s="4" t="inlineStr">
         <is>
           <t>相談支援事業所からの利用開始相談を含む</t>
@@ -4560,10 +4563,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C54" s="22" t="n"/>
-      <c r="D54" s="23" t="n"/>
-      <c r="E54" s="23" t="n"/>
-      <c r="F54" s="23" t="n"/>
+      <c r="C54" s="21" t="n"/>
+      <c r="D54" s="22" t="n"/>
+      <c r="E54" s="22" t="n"/>
+      <c r="F54" s="22" t="n"/>
       <c r="G54" s="4" t="inlineStr">
         <is>
           <t>06_65歳移行判定の結果を反映する。一律に減算しない</t>
@@ -4581,10 +4584,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C55" s="22" t="n"/>
-      <c r="D55" s="23" t="n"/>
-      <c r="E55" s="23" t="n"/>
-      <c r="F55" s="23" t="n"/>
+      <c r="C55" s="21" t="n"/>
+      <c r="D55" s="22" t="n"/>
+      <c r="E55" s="22" t="n"/>
+      <c r="F55" s="22" t="n"/>
       <c r="G55" s="4" t="inlineStr">
         <is>
           <t>就労移行支援からの一般就労等</t>
@@ -4602,10 +4605,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C56" s="22" t="n"/>
-      <c r="D56" s="23" t="n"/>
-      <c r="E56" s="23" t="n"/>
-      <c r="F56" s="23" t="n"/>
+      <c r="C56" s="21" t="n"/>
+      <c r="D56" s="22" t="n"/>
+      <c r="E56" s="22" t="n"/>
+      <c r="F56" s="22" t="n"/>
       <c r="G56" s="4" t="inlineStr">
         <is>
           <t>高齢化が進む本村では主要な減少要因</t>
@@ -4613,29 +4616,29 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="24" t="inlineStr">
+      <c r="A57" s="23" t="inlineStr">
         <is>
           <t>＝　利用者数</t>
         </is>
       </c>
-      <c r="B57" s="25" t="inlineStr">
-        <is>
-          <t>人／月</t>
-        </is>
-      </c>
-      <c r="C57" s="26">
+      <c r="B57" s="24" t="inlineStr">
+        <is>
+          <t>人／月</t>
+        </is>
+      </c>
+      <c r="C57" s="25">
         <f>C50</f>
         <v/>
       </c>
-      <c r="D57" s="26">
+      <c r="D57" s="25">
         <f>D50+SUM(D51:D53)-SUM(D54:D56)</f>
         <v/>
       </c>
-      <c r="E57" s="26">
+      <c r="E57" s="25">
         <f>E50+SUM(E51:E53)-SUM(E54:E56)</f>
         <v/>
       </c>
-      <c r="F57" s="26">
+      <c r="F57" s="25">
         <f>F50+SUM(F51:F53)-SUM(F54:F56)</f>
         <v/>
       </c>
@@ -4656,16 +4659,16 @@
           <t>人日／月</t>
         </is>
       </c>
-      <c r="C58" s="27" t="n">
+      <c r="C58" s="26" t="n">
         <v>12</v>
       </c>
-      <c r="D58" s="27" t="n">
+      <c r="D58" s="26" t="n">
         <v>12</v>
       </c>
-      <c r="E58" s="27" t="n">
+      <c r="E58" s="26" t="n">
         <v>12</v>
       </c>
-      <c r="F58" s="27" t="n">
+      <c r="F58" s="26" t="n">
         <v>12</v>
       </c>
       <c r="G58" s="4" t="inlineStr">
@@ -4675,29 +4678,29 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="24" t="inlineStr">
+      <c r="A59" s="23" t="inlineStr">
         <is>
           <t>＝　月間サービス量</t>
         </is>
       </c>
-      <c r="B59" s="25" t="inlineStr">
+      <c r="B59" s="24" t="inlineStr">
         <is>
           <t>人日／月</t>
         </is>
       </c>
-      <c r="C59" s="28">
+      <c r="C59" s="27">
         <f>ROUND(C57*C58,1)</f>
         <v/>
       </c>
-      <c r="D59" s="28">
+      <c r="D59" s="27">
         <f>ROUND(D57*D58,1)</f>
         <v/>
       </c>
-      <c r="E59" s="28">
+      <c r="E59" s="27">
         <f>ROUND(E57*E58,1)</f>
         <v/>
       </c>
-      <c r="F59" s="28">
+      <c r="F59" s="27">
         <f>ROUND(F57*F58,1)</f>
         <v/>
       </c>
@@ -4708,7 +4711,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="10" t="inlineStr">
+      <c r="A61" s="9" t="inlineStr">
         <is>
           <t>5　就労選択支援</t>
         </is>
@@ -4770,18 +4773,18 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C64" s="19" t="n">
+      <c r="C64" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="D64" s="20">
+      <c r="D64" s="19">
         <f>C71</f>
         <v/>
       </c>
-      <c r="E64" s="20">
+      <c r="E64" s="19">
         <f>D71</f>
         <v/>
       </c>
-      <c r="F64" s="20">
+      <c r="F64" s="19">
         <f>E71</f>
         <v/>
       </c>
@@ -4802,10 +4805,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C65" s="21" t="n"/>
-      <c r="D65" s="19" t="n"/>
-      <c r="E65" s="19" t="n"/>
-      <c r="F65" s="19" t="n"/>
+      <c r="C65" s="20" t="n"/>
+      <c r="D65" s="18" t="n"/>
+      <c r="E65" s="18" t="n"/>
+      <c r="F65" s="18" t="n"/>
       <c r="G65" s="4" t="inlineStr">
         <is>
           <t>02_年齢到達者一覧から転記する</t>
@@ -4823,10 +4826,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C66" s="21" t="n"/>
-      <c r="D66" s="19" t="n"/>
-      <c r="E66" s="19" t="n"/>
-      <c r="F66" s="19" t="n"/>
+      <c r="C66" s="20" t="n"/>
+      <c r="D66" s="18" t="n"/>
+      <c r="E66" s="18" t="n"/>
+      <c r="F66" s="18" t="n"/>
       <c r="G66" s="4" t="inlineStr">
         <is>
           <t>移行予定者を個別に確認する</t>
@@ -4844,10 +4847,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C67" s="21" t="n"/>
-      <c r="D67" s="19" t="n"/>
-      <c r="E67" s="19" t="n"/>
-      <c r="F67" s="19" t="n"/>
+      <c r="C67" s="20" t="n"/>
+      <c r="D67" s="18" t="n"/>
+      <c r="E67" s="18" t="n"/>
+      <c r="F67" s="18" t="n"/>
       <c r="G67" s="4" t="inlineStr">
         <is>
           <t>相談支援事業所からの利用開始相談を含む</t>
@@ -4865,10 +4868,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C68" s="22" t="n"/>
-      <c r="D68" s="23" t="n"/>
-      <c r="E68" s="23" t="n"/>
-      <c r="F68" s="23" t="n"/>
+      <c r="C68" s="21" t="n"/>
+      <c r="D68" s="22" t="n"/>
+      <c r="E68" s="22" t="n"/>
+      <c r="F68" s="22" t="n"/>
       <c r="G68" s="4" t="inlineStr">
         <is>
           <t>06_65歳移行判定の結果を反映する。一律に減算しない</t>
@@ -4886,10 +4889,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C69" s="22" t="n"/>
-      <c r="D69" s="23" t="n"/>
-      <c r="E69" s="23" t="n"/>
-      <c r="F69" s="23" t="n"/>
+      <c r="C69" s="21" t="n"/>
+      <c r="D69" s="22" t="n"/>
+      <c r="E69" s="22" t="n"/>
+      <c r="F69" s="22" t="n"/>
       <c r="G69" s="4" t="inlineStr">
         <is>
           <t>就労移行支援からの一般就労等</t>
@@ -4907,10 +4910,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C70" s="22" t="n"/>
-      <c r="D70" s="23" t="n"/>
-      <c r="E70" s="23" t="n"/>
-      <c r="F70" s="23" t="n"/>
+      <c r="C70" s="21" t="n"/>
+      <c r="D70" s="22" t="n"/>
+      <c r="E70" s="22" t="n"/>
+      <c r="F70" s="22" t="n"/>
       <c r="G70" s="4" t="inlineStr">
         <is>
           <t>高齢化が進む本村では主要な減少要因</t>
@@ -4918,29 +4921,29 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="24" t="inlineStr">
+      <c r="A71" s="23" t="inlineStr">
         <is>
           <t>＝　利用者数</t>
         </is>
       </c>
-      <c r="B71" s="25" t="inlineStr">
-        <is>
-          <t>人／月</t>
-        </is>
-      </c>
-      <c r="C71" s="26">
+      <c r="B71" s="24" t="inlineStr">
+        <is>
+          <t>人／月</t>
+        </is>
+      </c>
+      <c r="C71" s="25">
         <f>C64</f>
         <v/>
       </c>
-      <c r="D71" s="26">
+      <c r="D71" s="25">
         <f>D64+SUM(D65:D67)-SUM(D68:D70)</f>
         <v/>
       </c>
-      <c r="E71" s="26">
+      <c r="E71" s="25">
         <f>E64+SUM(E65:E67)-SUM(E68:E70)</f>
         <v/>
       </c>
-      <c r="F71" s="26">
+      <c r="F71" s="25">
         <f>F64+SUM(F65:F67)-SUM(F68:F70)</f>
         <v/>
       </c>
@@ -4961,10 +4964,10 @@
           <t>―</t>
         </is>
       </c>
-      <c r="C72" s="27" t="n"/>
-      <c r="D72" s="27" t="n"/>
-      <c r="E72" s="27" t="n"/>
-      <c r="F72" s="27" t="n"/>
+      <c r="C72" s="26" t="n"/>
+      <c r="D72" s="26" t="n"/>
+      <c r="E72" s="26" t="n"/>
+      <c r="F72" s="26" t="n"/>
       <c r="G72" s="4" t="inlineStr">
         <is>
           <t>利用者ごとの月間予定量の平均</t>
@@ -4972,29 +4975,29 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="24" t="inlineStr">
+      <c r="A73" s="23" t="inlineStr">
         <is>
           <t>＝　月間サービス量</t>
         </is>
       </c>
-      <c r="B73" s="25" t="inlineStr">
+      <c r="B73" s="24" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="C73" s="28">
+      <c r="C73" s="27">
         <f>ROUND(C71*C72,1)</f>
         <v/>
       </c>
-      <c r="D73" s="28">
+      <c r="D73" s="27">
         <f>ROUND(D71*D72,1)</f>
         <v/>
       </c>
-      <c r="E73" s="28">
+      <c r="E73" s="27">
         <f>ROUND(E71*E72,1)</f>
         <v/>
       </c>
-      <c r="F73" s="28">
+      <c r="F73" s="27">
         <f>ROUND(F71*F72,1)</f>
         <v/>
       </c>
@@ -5005,7 +5008,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="10" t="inlineStr">
+      <c r="A75" s="9" t="inlineStr">
         <is>
           <t>6　就労移行支援</t>
         </is>
@@ -5067,18 +5070,18 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C78" s="19" t="n">
+      <c r="C78" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="D78" s="20">
+      <c r="D78" s="19">
         <f>C85</f>
         <v/>
       </c>
-      <c r="E78" s="20">
+      <c r="E78" s="19">
         <f>D85</f>
         <v/>
       </c>
-      <c r="F78" s="20">
+      <c r="F78" s="19">
         <f>E85</f>
         <v/>
       </c>
@@ -5099,10 +5102,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C79" s="21" t="n"/>
-      <c r="D79" s="19" t="n"/>
-      <c r="E79" s="19" t="n"/>
-      <c r="F79" s="19" t="n"/>
+      <c r="C79" s="20" t="n"/>
+      <c r="D79" s="18" t="n"/>
+      <c r="E79" s="18" t="n"/>
+      <c r="F79" s="18" t="n"/>
       <c r="G79" s="4" t="inlineStr">
         <is>
           <t>02_年齢到達者一覧から転記する</t>
@@ -5120,10 +5123,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C80" s="21" t="n"/>
-      <c r="D80" s="19" t="n"/>
-      <c r="E80" s="19" t="n"/>
-      <c r="F80" s="19" t="n"/>
+      <c r="C80" s="20" t="n"/>
+      <c r="D80" s="18" t="n"/>
+      <c r="E80" s="18" t="n"/>
+      <c r="F80" s="18" t="n"/>
       <c r="G80" s="4" t="inlineStr">
         <is>
           <t>移行予定者を個別に確認する</t>
@@ -5141,10 +5144,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C81" s="21" t="n"/>
-      <c r="D81" s="19" t="n"/>
-      <c r="E81" s="19" t="n"/>
-      <c r="F81" s="19" t="n"/>
+      <c r="C81" s="20" t="n"/>
+      <c r="D81" s="18" t="n"/>
+      <c r="E81" s="18" t="n"/>
+      <c r="F81" s="18" t="n"/>
       <c r="G81" s="4" t="inlineStr">
         <is>
           <t>相談支援事業所からの利用開始相談を含む</t>
@@ -5162,10 +5165,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C82" s="22" t="n"/>
-      <c r="D82" s="23" t="n"/>
-      <c r="E82" s="23" t="n"/>
-      <c r="F82" s="23" t="n"/>
+      <c r="C82" s="21" t="n"/>
+      <c r="D82" s="22" t="n"/>
+      <c r="E82" s="22" t="n"/>
+      <c r="F82" s="22" t="n"/>
       <c r="G82" s="4" t="inlineStr">
         <is>
           <t>06_65歳移行判定の結果を反映する。一律に減算しない</t>
@@ -5183,10 +5186,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C83" s="22" t="n"/>
-      <c r="D83" s="23" t="n"/>
-      <c r="E83" s="23" t="n"/>
-      <c r="F83" s="23" t="n"/>
+      <c r="C83" s="21" t="n"/>
+      <c r="D83" s="22" t="n"/>
+      <c r="E83" s="22" t="n"/>
+      <c r="F83" s="22" t="n"/>
       <c r="G83" s="4" t="inlineStr">
         <is>
           <t>就労移行支援からの一般就労等</t>
@@ -5204,10 +5207,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C84" s="22" t="n"/>
-      <c r="D84" s="23" t="n"/>
-      <c r="E84" s="23" t="n"/>
-      <c r="F84" s="23" t="n"/>
+      <c r="C84" s="21" t="n"/>
+      <c r="D84" s="22" t="n"/>
+      <c r="E84" s="22" t="n"/>
+      <c r="F84" s="22" t="n"/>
       <c r="G84" s="4" t="inlineStr">
         <is>
           <t>高齢化が進む本村では主要な減少要因</t>
@@ -5215,29 +5218,29 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="24" t="inlineStr">
+      <c r="A85" s="23" t="inlineStr">
         <is>
           <t>＝　利用者数</t>
         </is>
       </c>
-      <c r="B85" s="25" t="inlineStr">
-        <is>
-          <t>人／月</t>
-        </is>
-      </c>
-      <c r="C85" s="26">
+      <c r="B85" s="24" t="inlineStr">
+        <is>
+          <t>人／月</t>
+        </is>
+      </c>
+      <c r="C85" s="25">
         <f>C78</f>
         <v/>
       </c>
-      <c r="D85" s="26">
+      <c r="D85" s="25">
         <f>D78+SUM(D79:D81)-SUM(D82:D84)</f>
         <v/>
       </c>
-      <c r="E85" s="26">
+      <c r="E85" s="25">
         <f>E78+SUM(E79:E81)-SUM(E82:E84)</f>
         <v/>
       </c>
-      <c r="F85" s="26">
+      <c r="F85" s="25">
         <f>F78+SUM(F79:F81)-SUM(F82:F84)</f>
         <v/>
       </c>
@@ -5258,16 +5261,16 @@
           <t>人日／月</t>
         </is>
       </c>
-      <c r="C86" s="27" t="n">
+      <c r="C86" s="26" t="n">
         <v>10</v>
       </c>
-      <c r="D86" s="27" t="n">
+      <c r="D86" s="26" t="n">
         <v>10</v>
       </c>
-      <c r="E86" s="27" t="n">
+      <c r="E86" s="26" t="n">
         <v>10</v>
       </c>
-      <c r="F86" s="27" t="n">
+      <c r="F86" s="26" t="n">
         <v>10</v>
       </c>
       <c r="G86" s="4" t="inlineStr">
@@ -5277,29 +5280,29 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="24" t="inlineStr">
+      <c r="A87" s="23" t="inlineStr">
         <is>
           <t>＝　月間サービス量</t>
         </is>
       </c>
-      <c r="B87" s="25" t="inlineStr">
+      <c r="B87" s="24" t="inlineStr">
         <is>
           <t>人日／月</t>
         </is>
       </c>
-      <c r="C87" s="28">
+      <c r="C87" s="27">
         <f>ROUND(C85*C86,1)</f>
         <v/>
       </c>
-      <c r="D87" s="28">
+      <c r="D87" s="27">
         <f>ROUND(D85*D86,1)</f>
         <v/>
       </c>
-      <c r="E87" s="28">
+      <c r="E87" s="27">
         <f>ROUND(E85*E86,1)</f>
         <v/>
       </c>
-      <c r="F87" s="28">
+      <c r="F87" s="27">
         <f>ROUND(F85*F86,1)</f>
         <v/>
       </c>
@@ -5310,7 +5313,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="10" t="inlineStr">
+      <c r="A89" s="9" t="inlineStr">
         <is>
           <t>7　就労継続支援A型</t>
         </is>
@@ -5372,18 +5375,18 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C92" s="19" t="n">
+      <c r="C92" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="D92" s="20">
+      <c r="D92" s="19">
         <f>C99</f>
         <v/>
       </c>
-      <c r="E92" s="20">
+      <c r="E92" s="19">
         <f>D99</f>
         <v/>
       </c>
-      <c r="F92" s="20">
+      <c r="F92" s="19">
         <f>E99</f>
         <v/>
       </c>
@@ -5404,10 +5407,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C93" s="21" t="n"/>
-      <c r="D93" s="19" t="n"/>
-      <c r="E93" s="19" t="n"/>
-      <c r="F93" s="19" t="n"/>
+      <c r="C93" s="20" t="n"/>
+      <c r="D93" s="18" t="n"/>
+      <c r="E93" s="18" t="n"/>
+      <c r="F93" s="18" t="n"/>
       <c r="G93" s="4" t="inlineStr">
         <is>
           <t>02_年齢到達者一覧から転記する</t>
@@ -5425,10 +5428,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C94" s="21" t="n"/>
-      <c r="D94" s="19" t="n"/>
-      <c r="E94" s="19" t="n"/>
-      <c r="F94" s="19" t="n"/>
+      <c r="C94" s="20" t="n"/>
+      <c r="D94" s="18" t="n"/>
+      <c r="E94" s="18" t="n"/>
+      <c r="F94" s="18" t="n"/>
       <c r="G94" s="4" t="inlineStr">
         <is>
           <t>移行予定者を個別に確認する</t>
@@ -5446,10 +5449,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C95" s="21" t="n"/>
-      <c r="D95" s="19" t="n"/>
-      <c r="E95" s="19" t="n"/>
-      <c r="F95" s="19" t="n"/>
+      <c r="C95" s="20" t="n"/>
+      <c r="D95" s="18" t="n"/>
+      <c r="E95" s="18" t="n"/>
+      <c r="F95" s="18" t="n"/>
       <c r="G95" s="4" t="inlineStr">
         <is>
           <t>相談支援事業所からの利用開始相談を含む</t>
@@ -5467,10 +5470,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C96" s="22" t="n"/>
-      <c r="D96" s="23" t="n"/>
-      <c r="E96" s="23" t="n"/>
-      <c r="F96" s="23" t="n"/>
+      <c r="C96" s="21" t="n"/>
+      <c r="D96" s="22" t="n"/>
+      <c r="E96" s="22" t="n"/>
+      <c r="F96" s="22" t="n"/>
       <c r="G96" s="4" t="inlineStr">
         <is>
           <t>06_65歳移行判定の結果を反映する。一律に減算しない</t>
@@ -5488,10 +5491,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C97" s="22" t="n"/>
-      <c r="D97" s="23" t="n"/>
-      <c r="E97" s="23" t="n"/>
-      <c r="F97" s="23" t="n"/>
+      <c r="C97" s="21" t="n"/>
+      <c r="D97" s="22" t="n"/>
+      <c r="E97" s="22" t="n"/>
+      <c r="F97" s="22" t="n"/>
       <c r="G97" s="4" t="inlineStr">
         <is>
           <t>就労移行支援からの一般就労等</t>
@@ -5509,10 +5512,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C98" s="22" t="n"/>
-      <c r="D98" s="23" t="n"/>
-      <c r="E98" s="23" t="n"/>
-      <c r="F98" s="23" t="n"/>
+      <c r="C98" s="21" t="n"/>
+      <c r="D98" s="22" t="n"/>
+      <c r="E98" s="22" t="n"/>
+      <c r="F98" s="22" t="n"/>
       <c r="G98" s="4" t="inlineStr">
         <is>
           <t>高齢化が進む本村では主要な減少要因</t>
@@ -5520,29 +5523,29 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="24" t="inlineStr">
+      <c r="A99" s="23" t="inlineStr">
         <is>
           <t>＝　利用者数</t>
         </is>
       </c>
-      <c r="B99" s="25" t="inlineStr">
-        <is>
-          <t>人／月</t>
-        </is>
-      </c>
-      <c r="C99" s="26">
+      <c r="B99" s="24" t="inlineStr">
+        <is>
+          <t>人／月</t>
+        </is>
+      </c>
+      <c r="C99" s="25">
         <f>C92</f>
         <v/>
       </c>
-      <c r="D99" s="26">
+      <c r="D99" s="25">
         <f>D92+SUM(D93:D95)-SUM(D96:D98)</f>
         <v/>
       </c>
-      <c r="E99" s="26">
+      <c r="E99" s="25">
         <f>E92+SUM(E93:E95)-SUM(E96:E98)</f>
         <v/>
       </c>
-      <c r="F99" s="26">
+      <c r="F99" s="25">
         <f>F92+SUM(F93:F95)-SUM(F96:F98)</f>
         <v/>
       </c>
@@ -5563,16 +5566,16 @@
           <t>人日／月</t>
         </is>
       </c>
-      <c r="C100" s="27" t="n">
+      <c r="C100" s="26" t="n">
         <v>19</v>
       </c>
-      <c r="D100" s="27" t="n">
+      <c r="D100" s="26" t="n">
         <v>19</v>
       </c>
-      <c r="E100" s="27" t="n">
+      <c r="E100" s="26" t="n">
         <v>19</v>
       </c>
-      <c r="F100" s="27" t="n">
+      <c r="F100" s="26" t="n">
         <v>19</v>
       </c>
       <c r="G100" s="4" t="inlineStr">
@@ -5582,29 +5585,29 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="24" t="inlineStr">
+      <c r="A101" s="23" t="inlineStr">
         <is>
           <t>＝　月間サービス量</t>
         </is>
       </c>
-      <c r="B101" s="25" t="inlineStr">
+      <c r="B101" s="24" t="inlineStr">
         <is>
           <t>人日／月</t>
         </is>
       </c>
-      <c r="C101" s="28">
+      <c r="C101" s="27">
         <f>ROUND(C99*C100,1)</f>
         <v/>
       </c>
-      <c r="D101" s="28">
+      <c r="D101" s="27">
         <f>ROUND(D99*D100,1)</f>
         <v/>
       </c>
-      <c r="E101" s="28">
+      <c r="E101" s="27">
         <f>ROUND(E99*E100,1)</f>
         <v/>
       </c>
-      <c r="F101" s="28">
+      <c r="F101" s="27">
         <f>ROUND(F99*F100,1)</f>
         <v/>
       </c>
@@ -5615,7 +5618,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="10" t="inlineStr">
+      <c r="A103" s="9" t="inlineStr">
         <is>
           <t>8　就労継続支援B型</t>
         </is>
@@ -5677,18 +5680,18 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C106" s="19" t="n">
+      <c r="C106" s="18" t="n">
         <v>11</v>
       </c>
-      <c r="D106" s="20">
+      <c r="D106" s="19">
         <f>C113</f>
         <v/>
       </c>
-      <c r="E106" s="20">
+      <c r="E106" s="19">
         <f>D113</f>
         <v/>
       </c>
-      <c r="F106" s="20">
+      <c r="F106" s="19">
         <f>E113</f>
         <v/>
       </c>
@@ -5709,10 +5712,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C107" s="21" t="n"/>
-      <c r="D107" s="19" t="n"/>
-      <c r="E107" s="19" t="n"/>
-      <c r="F107" s="19" t="n"/>
+      <c r="C107" s="20" t="n"/>
+      <c r="D107" s="18" t="n"/>
+      <c r="E107" s="18" t="n"/>
+      <c r="F107" s="18" t="n"/>
       <c r="G107" s="4" t="inlineStr">
         <is>
           <t>02_年齢到達者一覧から転記する</t>
@@ -5730,10 +5733,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C108" s="21" t="n"/>
-      <c r="D108" s="19" t="n"/>
-      <c r="E108" s="19" t="n"/>
-      <c r="F108" s="19" t="n"/>
+      <c r="C108" s="20" t="n"/>
+      <c r="D108" s="18" t="n"/>
+      <c r="E108" s="18" t="n"/>
+      <c r="F108" s="18" t="n"/>
       <c r="G108" s="4" t="inlineStr">
         <is>
           <t>移行予定者を個別に確認する</t>
@@ -5751,10 +5754,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C109" s="21" t="n"/>
-      <c r="D109" s="19" t="n"/>
-      <c r="E109" s="19" t="n"/>
-      <c r="F109" s="19" t="n"/>
+      <c r="C109" s="20" t="n"/>
+      <c r="D109" s="18" t="n"/>
+      <c r="E109" s="18" t="n"/>
+      <c r="F109" s="18" t="n"/>
       <c r="G109" s="4" t="inlineStr">
         <is>
           <t>相談支援事業所からの利用開始相談を含む</t>
@@ -5772,10 +5775,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C110" s="22" t="n"/>
-      <c r="D110" s="23" t="n"/>
-      <c r="E110" s="23" t="n"/>
-      <c r="F110" s="23" t="n"/>
+      <c r="C110" s="21" t="n"/>
+      <c r="D110" s="22" t="n"/>
+      <c r="E110" s="22" t="n"/>
+      <c r="F110" s="22" t="n"/>
       <c r="G110" s="4" t="inlineStr">
         <is>
           <t>06_65歳移行判定の結果を反映する。一律に減算しない</t>
@@ -5793,10 +5796,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C111" s="22" t="n"/>
-      <c r="D111" s="23" t="n"/>
-      <c r="E111" s="23" t="n"/>
-      <c r="F111" s="23" t="n"/>
+      <c r="C111" s="21" t="n"/>
+      <c r="D111" s="22" t="n"/>
+      <c r="E111" s="22" t="n"/>
+      <c r="F111" s="22" t="n"/>
       <c r="G111" s="4" t="inlineStr">
         <is>
           <t>就労移行支援からの一般就労等</t>
@@ -5814,10 +5817,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C112" s="22" t="n"/>
-      <c r="D112" s="23" t="n"/>
-      <c r="E112" s="23" t="n"/>
-      <c r="F112" s="23" t="n"/>
+      <c r="C112" s="21" t="n"/>
+      <c r="D112" s="22" t="n"/>
+      <c r="E112" s="22" t="n"/>
+      <c r="F112" s="22" t="n"/>
       <c r="G112" s="4" t="inlineStr">
         <is>
           <t>高齢化が進む本村では主要な減少要因</t>
@@ -5825,29 +5828,29 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="24" t="inlineStr">
+      <c r="A113" s="23" t="inlineStr">
         <is>
           <t>＝　利用者数</t>
         </is>
       </c>
-      <c r="B113" s="25" t="inlineStr">
-        <is>
-          <t>人／月</t>
-        </is>
-      </c>
-      <c r="C113" s="26">
+      <c r="B113" s="24" t="inlineStr">
+        <is>
+          <t>人／月</t>
+        </is>
+      </c>
+      <c r="C113" s="25">
         <f>C106</f>
         <v/>
       </c>
-      <c r="D113" s="26">
+      <c r="D113" s="25">
         <f>D106+SUM(D107:D109)-SUM(D110:D112)</f>
         <v/>
       </c>
-      <c r="E113" s="26">
+      <c r="E113" s="25">
         <f>E106+SUM(E107:E109)-SUM(E110:E112)</f>
         <v/>
       </c>
-      <c r="F113" s="26">
+      <c r="F113" s="25">
         <f>F106+SUM(F107:F109)-SUM(F110:F112)</f>
         <v/>
       </c>
@@ -5868,16 +5871,16 @@
           <t>人日／月</t>
         </is>
       </c>
-      <c r="C114" s="27" t="n">
+      <c r="C114" s="26" t="n">
         <v>18.2</v>
       </c>
-      <c r="D114" s="27" t="n">
+      <c r="D114" s="26" t="n">
         <v>18.2</v>
       </c>
-      <c r="E114" s="27" t="n">
+      <c r="E114" s="26" t="n">
         <v>18.2</v>
       </c>
-      <c r="F114" s="27" t="n">
+      <c r="F114" s="26" t="n">
         <v>18.2</v>
       </c>
       <c r="G114" s="4" t="inlineStr">
@@ -5887,29 +5890,29 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="24" t="inlineStr">
+      <c r="A115" s="23" t="inlineStr">
         <is>
           <t>＝　月間サービス量</t>
         </is>
       </c>
-      <c r="B115" s="25" t="inlineStr">
+      <c r="B115" s="24" t="inlineStr">
         <is>
           <t>人日／月</t>
         </is>
       </c>
-      <c r="C115" s="28">
+      <c r="C115" s="27">
         <f>ROUND(C113*C114,1)</f>
         <v/>
       </c>
-      <c r="D115" s="28">
+      <c r="D115" s="27">
         <f>ROUND(D113*D114,1)</f>
         <v/>
       </c>
-      <c r="E115" s="28">
+      <c r="E115" s="27">
         <f>ROUND(E113*E114,1)</f>
         <v/>
       </c>
-      <c r="F115" s="28">
+      <c r="F115" s="27">
         <f>ROUND(F113*F114,1)</f>
         <v/>
       </c>
@@ -5920,7 +5923,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="10" t="inlineStr">
+      <c r="A117" s="9" t="inlineStr">
         <is>
           <t>9　就労定着支援</t>
         </is>
@@ -5982,18 +5985,18 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C120" s="19" t="n">
+      <c r="C120" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="D120" s="20">
+      <c r="D120" s="19">
         <f>C127</f>
         <v/>
       </c>
-      <c r="E120" s="20">
+      <c r="E120" s="19">
         <f>D127</f>
         <v/>
       </c>
-      <c r="F120" s="20">
+      <c r="F120" s="19">
         <f>E127</f>
         <v/>
       </c>
@@ -6014,10 +6017,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C121" s="21" t="n"/>
-      <c r="D121" s="19" t="n"/>
-      <c r="E121" s="19" t="n"/>
-      <c r="F121" s="19" t="n"/>
+      <c r="C121" s="20" t="n"/>
+      <c r="D121" s="18" t="n"/>
+      <c r="E121" s="18" t="n"/>
+      <c r="F121" s="18" t="n"/>
       <c r="G121" s="4" t="inlineStr">
         <is>
           <t>02_年齢到達者一覧から転記する</t>
@@ -6035,10 +6038,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C122" s="21" t="n"/>
-      <c r="D122" s="19" t="n"/>
-      <c r="E122" s="19" t="n"/>
-      <c r="F122" s="19" t="n"/>
+      <c r="C122" s="20" t="n"/>
+      <c r="D122" s="18" t="n"/>
+      <c r="E122" s="18" t="n"/>
+      <c r="F122" s="18" t="n"/>
       <c r="G122" s="4" t="inlineStr">
         <is>
           <t>移行予定者を個別に確認する</t>
@@ -6056,10 +6059,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C123" s="21" t="n"/>
-      <c r="D123" s="19" t="n"/>
-      <c r="E123" s="19" t="n"/>
-      <c r="F123" s="19" t="n"/>
+      <c r="C123" s="20" t="n"/>
+      <c r="D123" s="18" t="n"/>
+      <c r="E123" s="18" t="n"/>
+      <c r="F123" s="18" t="n"/>
       <c r="G123" s="4" t="inlineStr">
         <is>
           <t>相談支援事業所からの利用開始相談を含む</t>
@@ -6077,10 +6080,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C124" s="22" t="n"/>
-      <c r="D124" s="23" t="n"/>
-      <c r="E124" s="23" t="n"/>
-      <c r="F124" s="23" t="n"/>
+      <c r="C124" s="21" t="n"/>
+      <c r="D124" s="22" t="n"/>
+      <c r="E124" s="22" t="n"/>
+      <c r="F124" s="22" t="n"/>
       <c r="G124" s="4" t="inlineStr">
         <is>
           <t>06_65歳移行判定の結果を反映する。一律に減算しない</t>
@@ -6098,10 +6101,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C125" s="22" t="n"/>
-      <c r="D125" s="23" t="n"/>
-      <c r="E125" s="23" t="n"/>
-      <c r="F125" s="23" t="n"/>
+      <c r="C125" s="21" t="n"/>
+      <c r="D125" s="22" t="n"/>
+      <c r="E125" s="22" t="n"/>
+      <c r="F125" s="22" t="n"/>
       <c r="G125" s="4" t="inlineStr">
         <is>
           <t>就労移行支援からの一般就労等</t>
@@ -6119,10 +6122,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C126" s="22" t="n"/>
-      <c r="D126" s="23" t="n"/>
-      <c r="E126" s="23" t="n"/>
-      <c r="F126" s="23" t="n"/>
+      <c r="C126" s="21" t="n"/>
+      <c r="D126" s="22" t="n"/>
+      <c r="E126" s="22" t="n"/>
+      <c r="F126" s="22" t="n"/>
       <c r="G126" s="4" t="inlineStr">
         <is>
           <t>高齢化が進む本村では主要な減少要因</t>
@@ -6130,29 +6133,29 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="24" t="inlineStr">
+      <c r="A127" s="23" t="inlineStr">
         <is>
           <t>＝　利用者数</t>
         </is>
       </c>
-      <c r="B127" s="25" t="inlineStr">
-        <is>
-          <t>人／月</t>
-        </is>
-      </c>
-      <c r="C127" s="26">
+      <c r="B127" s="24" t="inlineStr">
+        <is>
+          <t>人／月</t>
+        </is>
+      </c>
+      <c r="C127" s="25">
         <f>C120</f>
         <v/>
       </c>
-      <c r="D127" s="26">
+      <c r="D127" s="25">
         <f>D120+SUM(D121:D123)-SUM(D124:D126)</f>
         <v/>
       </c>
-      <c r="E127" s="26">
+      <c r="E127" s="25">
         <f>E120+SUM(E121:E123)-SUM(E124:E126)</f>
         <v/>
       </c>
-      <c r="F127" s="26">
+      <c r="F127" s="25">
         <f>F120+SUM(F121:F123)-SUM(F124:F126)</f>
         <v/>
       </c>
@@ -6173,10 +6176,10 @@
           <t>―</t>
         </is>
       </c>
-      <c r="C128" s="27" t="n"/>
-      <c r="D128" s="27" t="n"/>
-      <c r="E128" s="27" t="n"/>
-      <c r="F128" s="27" t="n"/>
+      <c r="C128" s="26" t="n"/>
+      <c r="D128" s="26" t="n"/>
+      <c r="E128" s="26" t="n"/>
+      <c r="F128" s="26" t="n"/>
       <c r="G128" s="4" t="inlineStr">
         <is>
           <t>利用者ごとの月間予定量の平均</t>
@@ -6184,29 +6187,29 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="24" t="inlineStr">
+      <c r="A129" s="23" t="inlineStr">
         <is>
           <t>＝　月間サービス量</t>
         </is>
       </c>
-      <c r="B129" s="25" t="inlineStr">
+      <c r="B129" s="24" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="C129" s="28">
+      <c r="C129" s="27">
         <f>ROUND(C127*C128,1)</f>
         <v/>
       </c>
-      <c r="D129" s="28">
+      <c r="D129" s="27">
         <f>ROUND(D127*D128,1)</f>
         <v/>
       </c>
-      <c r="E129" s="28">
+      <c r="E129" s="27">
         <f>ROUND(E127*E128,1)</f>
         <v/>
       </c>
-      <c r="F129" s="28">
+      <c r="F129" s="27">
         <f>ROUND(F127*F128,1)</f>
         <v/>
       </c>
@@ -6217,7 +6220,7 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="10" t="inlineStr">
+      <c r="A131" s="9" t="inlineStr">
         <is>
           <t>10　共同生活援助</t>
         </is>
@@ -6279,18 +6282,18 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C134" s="19" t="n">
+      <c r="C134" s="18" t="n">
         <v>8</v>
       </c>
-      <c r="D134" s="20">
+      <c r="D134" s="19">
         <f>C141</f>
         <v/>
       </c>
-      <c r="E134" s="20">
+      <c r="E134" s="19">
         <f>D141</f>
         <v/>
       </c>
-      <c r="F134" s="20">
+      <c r="F134" s="19">
         <f>E141</f>
         <v/>
       </c>
@@ -6311,10 +6314,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C135" s="21" t="n"/>
-      <c r="D135" s="19" t="n"/>
-      <c r="E135" s="19" t="n"/>
-      <c r="F135" s="19" t="n"/>
+      <c r="C135" s="20" t="n"/>
+      <c r="D135" s="18" t="n"/>
+      <c r="E135" s="18" t="n"/>
+      <c r="F135" s="18" t="n"/>
       <c r="G135" s="4" t="inlineStr">
         <is>
           <t>02_年齢到達者一覧から転記する</t>
@@ -6332,10 +6335,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C136" s="21" t="n"/>
-      <c r="D136" s="19" t="n"/>
-      <c r="E136" s="19" t="n"/>
-      <c r="F136" s="19" t="n"/>
+      <c r="C136" s="20" t="n"/>
+      <c r="D136" s="18" t="n"/>
+      <c r="E136" s="18" t="n"/>
+      <c r="F136" s="18" t="n"/>
       <c r="G136" s="4" t="inlineStr">
         <is>
           <t>移行予定者を個別に確認する</t>
@@ -6353,10 +6356,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C137" s="21" t="n"/>
-      <c r="D137" s="19" t="n"/>
-      <c r="E137" s="19" t="n"/>
-      <c r="F137" s="19" t="n"/>
+      <c r="C137" s="20" t="n"/>
+      <c r="D137" s="18" t="n"/>
+      <c r="E137" s="18" t="n"/>
+      <c r="F137" s="18" t="n"/>
       <c r="G137" s="4" t="inlineStr">
         <is>
           <t>相談支援事業所からの利用開始相談を含む</t>
@@ -6374,10 +6377,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C138" s="22" t="n"/>
-      <c r="D138" s="23" t="n"/>
-      <c r="E138" s="23" t="n"/>
-      <c r="F138" s="23" t="n"/>
+      <c r="C138" s="21" t="n"/>
+      <c r="D138" s="22" t="n"/>
+      <c r="E138" s="22" t="n"/>
+      <c r="F138" s="22" t="n"/>
       <c r="G138" s="4" t="inlineStr">
         <is>
           <t>06_65歳移行判定の結果を反映する。一律に減算しない</t>
@@ -6395,10 +6398,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C139" s="22" t="n"/>
-      <c r="D139" s="23" t="n"/>
-      <c r="E139" s="23" t="n"/>
-      <c r="F139" s="23" t="n"/>
+      <c r="C139" s="21" t="n"/>
+      <c r="D139" s="22" t="n"/>
+      <c r="E139" s="22" t="n"/>
+      <c r="F139" s="22" t="n"/>
       <c r="G139" s="4" t="inlineStr">
         <is>
           <t>就労移行支援からの一般就労等</t>
@@ -6416,10 +6419,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C140" s="22" t="n"/>
-      <c r="D140" s="23" t="n"/>
-      <c r="E140" s="23" t="n"/>
-      <c r="F140" s="23" t="n"/>
+      <c r="C140" s="21" t="n"/>
+      <c r="D140" s="22" t="n"/>
+      <c r="E140" s="22" t="n"/>
+      <c r="F140" s="22" t="n"/>
       <c r="G140" s="4" t="inlineStr">
         <is>
           <t>高齢化が進む本村では主要な減少要因</t>
@@ -6427,29 +6430,29 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="24" t="inlineStr">
+      <c r="A141" s="23" t="inlineStr">
         <is>
           <t>＝　利用者数</t>
         </is>
       </c>
-      <c r="B141" s="25" t="inlineStr">
-        <is>
-          <t>人／月</t>
-        </is>
-      </c>
-      <c r="C141" s="26">
+      <c r="B141" s="24" t="inlineStr">
+        <is>
+          <t>人／月</t>
+        </is>
+      </c>
+      <c r="C141" s="25">
         <f>C134</f>
         <v/>
       </c>
-      <c r="D141" s="26">
+      <c r="D141" s="25">
         <f>D134+SUM(D135:D137)-SUM(D138:D140)</f>
         <v/>
       </c>
-      <c r="E141" s="26">
+      <c r="E141" s="25">
         <f>E134+SUM(E135:E137)-SUM(E138:E140)</f>
         <v/>
       </c>
-      <c r="F141" s="26">
+      <c r="F141" s="25">
         <f>F134+SUM(F135:F137)-SUM(F138:F140)</f>
         <v/>
       </c>
@@ -6470,10 +6473,10 @@
           <t>―</t>
         </is>
       </c>
-      <c r="C142" s="27" t="n"/>
-      <c r="D142" s="27" t="n"/>
-      <c r="E142" s="27" t="n"/>
-      <c r="F142" s="27" t="n"/>
+      <c r="C142" s="26" t="n"/>
+      <c r="D142" s="26" t="n"/>
+      <c r="E142" s="26" t="n"/>
+      <c r="F142" s="26" t="n"/>
       <c r="G142" s="4" t="inlineStr">
         <is>
           <t>利用者ごとの月間予定量の平均</t>
@@ -6481,29 +6484,29 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="24" t="inlineStr">
+      <c r="A143" s="23" t="inlineStr">
         <is>
           <t>＝　月間サービス量</t>
         </is>
       </c>
-      <c r="B143" s="25" t="inlineStr">
+      <c r="B143" s="24" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="C143" s="28">
+      <c r="C143" s="27">
         <f>ROUND(C141*C142,1)</f>
         <v/>
       </c>
-      <c r="D143" s="28">
+      <c r="D143" s="27">
         <f>ROUND(D141*D142,1)</f>
         <v/>
       </c>
-      <c r="E143" s="28">
+      <c r="E143" s="27">
         <f>ROUND(E141*E142,1)</f>
         <v/>
       </c>
-      <c r="F143" s="28">
+      <c r="F143" s="27">
         <f>ROUND(F141*F142,1)</f>
         <v/>
       </c>
@@ -6514,7 +6517,7 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="10" t="inlineStr">
+      <c r="A145" s="9" t="inlineStr">
         <is>
           <t>11　施設入所支援</t>
         </is>
@@ -6576,18 +6579,18 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C148" s="19" t="n">
+      <c r="C148" s="18" t="n">
         <v>4</v>
       </c>
-      <c r="D148" s="20">
+      <c r="D148" s="19">
         <f>C155</f>
         <v/>
       </c>
-      <c r="E148" s="20">
+      <c r="E148" s="19">
         <f>D155</f>
         <v/>
       </c>
-      <c r="F148" s="20">
+      <c r="F148" s="19">
         <f>E155</f>
         <v/>
       </c>
@@ -6608,10 +6611,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C149" s="21" t="n"/>
-      <c r="D149" s="19" t="n"/>
-      <c r="E149" s="19" t="n"/>
-      <c r="F149" s="19" t="n"/>
+      <c r="C149" s="20" t="n"/>
+      <c r="D149" s="18" t="n"/>
+      <c r="E149" s="18" t="n"/>
+      <c r="F149" s="18" t="n"/>
       <c r="G149" s="4" t="inlineStr">
         <is>
           <t>02_年齢到達者一覧から転記する</t>
@@ -6629,10 +6632,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C150" s="21" t="n"/>
-      <c r="D150" s="19" t="n"/>
-      <c r="E150" s="19" t="n"/>
-      <c r="F150" s="19" t="n"/>
+      <c r="C150" s="20" t="n"/>
+      <c r="D150" s="18" t="n"/>
+      <c r="E150" s="18" t="n"/>
+      <c r="F150" s="18" t="n"/>
       <c r="G150" s="4" t="inlineStr">
         <is>
           <t>移行予定者を個別に確認する</t>
@@ -6650,10 +6653,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C151" s="21" t="n"/>
-      <c r="D151" s="19" t="n"/>
-      <c r="E151" s="19" t="n"/>
-      <c r="F151" s="19" t="n"/>
+      <c r="C151" s="20" t="n"/>
+      <c r="D151" s="18" t="n"/>
+      <c r="E151" s="18" t="n"/>
+      <c r="F151" s="18" t="n"/>
       <c r="G151" s="4" t="inlineStr">
         <is>
           <t>相談支援事業所からの利用開始相談を含む</t>
@@ -6671,10 +6674,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C152" s="22" t="n"/>
-      <c r="D152" s="23" t="n"/>
-      <c r="E152" s="23" t="n"/>
-      <c r="F152" s="23" t="n"/>
+      <c r="C152" s="21" t="n"/>
+      <c r="D152" s="22" t="n"/>
+      <c r="E152" s="22" t="n"/>
+      <c r="F152" s="22" t="n"/>
       <c r="G152" s="4" t="inlineStr">
         <is>
           <t>06_65歳移行判定の結果を反映する。一律に減算しない</t>
@@ -6692,10 +6695,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C153" s="22" t="n"/>
-      <c r="D153" s="23" t="n"/>
-      <c r="E153" s="23" t="n"/>
-      <c r="F153" s="23" t="n"/>
+      <c r="C153" s="21" t="n"/>
+      <c r="D153" s="22" t="n"/>
+      <c r="E153" s="22" t="n"/>
+      <c r="F153" s="22" t="n"/>
       <c r="G153" s="4" t="inlineStr">
         <is>
           <t>就労移行支援からの一般就労等</t>
@@ -6713,10 +6716,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C154" s="22" t="n"/>
-      <c r="D154" s="23" t="n"/>
-      <c r="E154" s="23" t="n"/>
-      <c r="F154" s="23" t="n"/>
+      <c r="C154" s="21" t="n"/>
+      <c r="D154" s="22" t="n"/>
+      <c r="E154" s="22" t="n"/>
+      <c r="F154" s="22" t="n"/>
       <c r="G154" s="4" t="inlineStr">
         <is>
           <t>高齢化が進む本村では主要な減少要因</t>
@@ -6724,29 +6727,29 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="24" t="inlineStr">
+      <c r="A155" s="23" t="inlineStr">
         <is>
           <t>＝　利用者数</t>
         </is>
       </c>
-      <c r="B155" s="25" t="inlineStr">
-        <is>
-          <t>人／月</t>
-        </is>
-      </c>
-      <c r="C155" s="26">
+      <c r="B155" s="24" t="inlineStr">
+        <is>
+          <t>人／月</t>
+        </is>
+      </c>
+      <c r="C155" s="25">
         <f>C148</f>
         <v/>
       </c>
-      <c r="D155" s="26">
+      <c r="D155" s="25">
         <f>D148+SUM(D149:D151)-SUM(D152:D154)</f>
         <v/>
       </c>
-      <c r="E155" s="26">
+      <c r="E155" s="25">
         <f>E148+SUM(E149:E151)-SUM(E152:E154)</f>
         <v/>
       </c>
-      <c r="F155" s="26">
+      <c r="F155" s="25">
         <f>F148+SUM(F149:F151)-SUM(F152:F154)</f>
         <v/>
       </c>
@@ -6767,10 +6770,10 @@
           <t>―</t>
         </is>
       </c>
-      <c r="C156" s="27" t="n"/>
-      <c r="D156" s="27" t="n"/>
-      <c r="E156" s="27" t="n"/>
-      <c r="F156" s="27" t="n"/>
+      <c r="C156" s="26" t="n"/>
+      <c r="D156" s="26" t="n"/>
+      <c r="E156" s="26" t="n"/>
+      <c r="F156" s="26" t="n"/>
       <c r="G156" s="4" t="inlineStr">
         <is>
           <t>利用者ごとの月間予定量の平均</t>
@@ -6778,29 +6781,29 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="24" t="inlineStr">
+      <c r="A157" s="23" t="inlineStr">
         <is>
           <t>＝　月間サービス量</t>
         </is>
       </c>
-      <c r="B157" s="25" t="inlineStr">
+      <c r="B157" s="24" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="C157" s="28">
+      <c r="C157" s="27">
         <f>ROUND(C155*C156,1)</f>
         <v/>
       </c>
-      <c r="D157" s="28">
+      <c r="D157" s="27">
         <f>ROUND(D155*D156,1)</f>
         <v/>
       </c>
-      <c r="E157" s="28">
+      <c r="E157" s="27">
         <f>ROUND(E155*E156,1)</f>
         <v/>
       </c>
-      <c r="F157" s="28">
+      <c r="F157" s="27">
         <f>ROUND(F155*F156,1)</f>
         <v/>
       </c>
@@ -6811,7 +6814,7 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="10" t="inlineStr">
+      <c r="A159" s="9" t="inlineStr">
         <is>
           <t>12　計画相談支援</t>
         </is>
@@ -6873,18 +6876,18 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C162" s="19" t="n">
+      <c r="C162" s="18" t="n">
         <v>22</v>
       </c>
-      <c r="D162" s="20">
+      <c r="D162" s="19">
         <f>C169</f>
         <v/>
       </c>
-      <c r="E162" s="20">
+      <c r="E162" s="19">
         <f>D169</f>
         <v/>
       </c>
-      <c r="F162" s="20">
+      <c r="F162" s="19">
         <f>E169</f>
         <v/>
       </c>
@@ -6905,10 +6908,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C163" s="21" t="n"/>
-      <c r="D163" s="19" t="n"/>
-      <c r="E163" s="19" t="n"/>
-      <c r="F163" s="19" t="n"/>
+      <c r="C163" s="20" t="n"/>
+      <c r="D163" s="18" t="n"/>
+      <c r="E163" s="18" t="n"/>
+      <c r="F163" s="18" t="n"/>
       <c r="G163" s="4" t="inlineStr">
         <is>
           <t>02_年齢到達者一覧から転記する</t>
@@ -6926,10 +6929,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C164" s="21" t="n"/>
-      <c r="D164" s="19" t="n"/>
-      <c r="E164" s="19" t="n"/>
-      <c r="F164" s="19" t="n"/>
+      <c r="C164" s="20" t="n"/>
+      <c r="D164" s="18" t="n"/>
+      <c r="E164" s="18" t="n"/>
+      <c r="F164" s="18" t="n"/>
       <c r="G164" s="4" t="inlineStr">
         <is>
           <t>移行予定者を個別に確認する</t>
@@ -6947,10 +6950,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C165" s="21" t="n"/>
-      <c r="D165" s="19" t="n"/>
-      <c r="E165" s="19" t="n"/>
-      <c r="F165" s="19" t="n"/>
+      <c r="C165" s="20" t="n"/>
+      <c r="D165" s="18" t="n"/>
+      <c r="E165" s="18" t="n"/>
+      <c r="F165" s="18" t="n"/>
       <c r="G165" s="4" t="inlineStr">
         <is>
           <t>相談支援事業所からの利用開始相談を含む</t>
@@ -6968,10 +6971,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C166" s="22" t="n"/>
-      <c r="D166" s="23" t="n"/>
-      <c r="E166" s="23" t="n"/>
-      <c r="F166" s="23" t="n"/>
+      <c r="C166" s="21" t="n"/>
+      <c r="D166" s="22" t="n"/>
+      <c r="E166" s="22" t="n"/>
+      <c r="F166" s="22" t="n"/>
       <c r="G166" s="4" t="inlineStr">
         <is>
           <t>06_65歳移行判定の結果を反映する。一律に減算しない</t>
@@ -6989,10 +6992,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C167" s="22" t="n"/>
-      <c r="D167" s="23" t="n"/>
-      <c r="E167" s="23" t="n"/>
-      <c r="F167" s="23" t="n"/>
+      <c r="C167" s="21" t="n"/>
+      <c r="D167" s="22" t="n"/>
+      <c r="E167" s="22" t="n"/>
+      <c r="F167" s="22" t="n"/>
       <c r="G167" s="4" t="inlineStr">
         <is>
           <t>就労移行支援からの一般就労等</t>
@@ -7010,10 +7013,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C168" s="22" t="n"/>
-      <c r="D168" s="23" t="n"/>
-      <c r="E168" s="23" t="n"/>
-      <c r="F168" s="23" t="n"/>
+      <c r="C168" s="21" t="n"/>
+      <c r="D168" s="22" t="n"/>
+      <c r="E168" s="22" t="n"/>
+      <c r="F168" s="22" t="n"/>
       <c r="G168" s="4" t="inlineStr">
         <is>
           <t>高齢化が進む本村では主要な減少要因</t>
@@ -7021,29 +7024,29 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="24" t="inlineStr">
+      <c r="A169" s="23" t="inlineStr">
         <is>
           <t>＝　利用者数</t>
         </is>
       </c>
-      <c r="B169" s="25" t="inlineStr">
-        <is>
-          <t>人／月</t>
-        </is>
-      </c>
-      <c r="C169" s="26">
+      <c r="B169" s="24" t="inlineStr">
+        <is>
+          <t>人／月</t>
+        </is>
+      </c>
+      <c r="C169" s="25">
         <f>C162</f>
         <v/>
       </c>
-      <c r="D169" s="26">
+      <c r="D169" s="25">
         <f>D162+SUM(D163:D165)-SUM(D166:D168)</f>
         <v/>
       </c>
-      <c r="E169" s="26">
+      <c r="E169" s="25">
         <f>E162+SUM(E163:E165)-SUM(E166:E168)</f>
         <v/>
       </c>
-      <c r="F169" s="26">
+      <c r="F169" s="25">
         <f>F162+SUM(F163:F165)-SUM(F166:F168)</f>
         <v/>
       </c>
@@ -7064,10 +7067,10 @@
           <t>―</t>
         </is>
       </c>
-      <c r="C170" s="27" t="n"/>
-      <c r="D170" s="27" t="n"/>
-      <c r="E170" s="27" t="n"/>
-      <c r="F170" s="27" t="n"/>
+      <c r="C170" s="26" t="n"/>
+      <c r="D170" s="26" t="n"/>
+      <c r="E170" s="26" t="n"/>
+      <c r="F170" s="26" t="n"/>
       <c r="G170" s="4" t="inlineStr">
         <is>
           <t>利用者ごとの月間予定量の平均</t>
@@ -7075,29 +7078,29 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="24" t="inlineStr">
+      <c r="A171" s="23" t="inlineStr">
         <is>
           <t>＝　月間サービス量</t>
         </is>
       </c>
-      <c r="B171" s="25" t="inlineStr">
+      <c r="B171" s="24" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="C171" s="28">
+      <c r="C171" s="27">
         <f>ROUND(C169*C170,1)</f>
         <v/>
       </c>
-      <c r="D171" s="28">
+      <c r="D171" s="27">
         <f>ROUND(D169*D170,1)</f>
         <v/>
       </c>
-      <c r="E171" s="28">
+      <c r="E171" s="27">
         <f>ROUND(E169*E170,1)</f>
         <v/>
       </c>
-      <c r="F171" s="28">
+      <c r="F171" s="27">
         <f>ROUND(F169*F170,1)</f>
         <v/>
       </c>
@@ -7167,7 +7170,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>障がい児通所支援等の個別積上げ</t>
         </is>
@@ -7181,7 +7184,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="29" t="inlineStr">
+      <c r="A5" s="28" t="inlineStr">
         <is>
           <t>1　児童発達支援</t>
         </is>
@@ -7243,18 +7246,18 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C8" s="19" t="n">
+      <c r="C8" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="D8" s="20">
+      <c r="D8" s="19">
         <f>C14</f>
         <v/>
       </c>
-      <c r="E8" s="20">
+      <c r="E8" s="19">
         <f>D14</f>
         <v/>
       </c>
-      <c r="F8" s="20">
+      <c r="F8" s="19">
         <f>E14</f>
         <v/>
       </c>
@@ -7275,10 +7278,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C9" s="21" t="n"/>
-      <c r="D9" s="19" t="n"/>
-      <c r="E9" s="19" t="n"/>
-      <c r="F9" s="19" t="n"/>
+      <c r="C9" s="20" t="n"/>
+      <c r="D9" s="18" t="n"/>
+      <c r="E9" s="18" t="n"/>
+      <c r="F9" s="18" t="n"/>
       <c r="G9" s="4" t="inlineStr">
         <is>
           <t>新規の発達相談・診断からの流入</t>
@@ -7296,10 +7299,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C10" s="21" t="n"/>
-      <c r="D10" s="19" t="n"/>
-      <c r="E10" s="19" t="n"/>
-      <c r="F10" s="19" t="n"/>
+      <c r="C10" s="20" t="n"/>
+      <c r="D10" s="18" t="n"/>
+      <c r="E10" s="18" t="n"/>
+      <c r="F10" s="18" t="n"/>
       <c r="G10" s="4" t="inlineStr">
         <is>
           <t>児童発達支援から放課後等デイサービスへの移行等</t>
@@ -7317,10 +7320,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C11" s="22" t="n"/>
-      <c r="D11" s="23" t="n"/>
-      <c r="E11" s="23" t="n"/>
-      <c r="F11" s="23" t="n"/>
+      <c r="C11" s="21" t="n"/>
+      <c r="D11" s="22" t="n"/>
+      <c r="E11" s="22" t="n"/>
+      <c r="F11" s="22" t="n"/>
       <c r="G11" s="4" t="inlineStr">
         <is>
           <t>児童発達支援からの流出</t>
@@ -7338,10 +7341,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C12" s="22" t="n"/>
-      <c r="D12" s="23" t="n"/>
-      <c r="E12" s="23" t="n"/>
-      <c r="F12" s="23" t="n"/>
+      <c r="C12" s="21" t="n"/>
+      <c r="D12" s="22" t="n"/>
+      <c r="E12" s="22" t="n"/>
+      <c r="F12" s="22" t="n"/>
       <c r="G12" s="4" t="inlineStr">
         <is>
           <t>成人の障害福祉サービスへ。03の流入と一致させる</t>
@@ -7359,36 +7362,36 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C13" s="22" t="n"/>
-      <c r="D13" s="23" t="n"/>
-      <c r="E13" s="23" t="n"/>
-      <c r="F13" s="23" t="n"/>
+      <c r="C13" s="21" t="n"/>
+      <c r="D13" s="22" t="n"/>
+      <c r="E13" s="22" t="n"/>
+      <c r="F13" s="22" t="n"/>
       <c r="G13" s="4" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="24" t="inlineStr">
+      <c r="A14" s="23" t="inlineStr">
         <is>
           <t>＝　利用者数</t>
         </is>
       </c>
-      <c r="B14" s="25" t="inlineStr">
-        <is>
-          <t>人／月</t>
-        </is>
-      </c>
-      <c r="C14" s="26">
+      <c r="B14" s="24" t="inlineStr">
+        <is>
+          <t>人／月</t>
+        </is>
+      </c>
+      <c r="C14" s="25">
         <f>C8</f>
         <v/>
       </c>
-      <c r="D14" s="26">
+      <c r="D14" s="25">
         <f>D8+SUM(D9:D10)-SUM(D11:D13)</f>
         <v/>
       </c>
-      <c r="E14" s="26">
+      <c r="E14" s="25">
         <f>E8+SUM(E9:E10)-SUM(E11:E13)</f>
         <v/>
       </c>
-      <c r="F14" s="26">
+      <c r="F14" s="25">
         <f>F8+SUM(F9:F10)-SUM(F11:F13)</f>
         <v/>
       </c>
@@ -7409,10 +7412,10 @@
           <t>人日／月</t>
         </is>
       </c>
-      <c r="C15" s="27" t="n"/>
-      <c r="D15" s="27" t="n"/>
-      <c r="E15" s="27" t="n"/>
-      <c r="F15" s="27" t="n"/>
+      <c r="C15" s="26" t="n"/>
+      <c r="D15" s="26" t="n"/>
+      <c r="E15" s="26" t="n"/>
+      <c r="F15" s="26" t="n"/>
       <c r="G15" s="4" t="inlineStr">
         <is>
           <t>利用者ごとの月間予定量の平均</t>
@@ -7420,29 +7423,29 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="24" t="inlineStr">
+      <c r="A16" s="23" t="inlineStr">
         <is>
           <t>＝　月間サービス量</t>
         </is>
       </c>
-      <c r="B16" s="25" t="inlineStr">
+      <c r="B16" s="24" t="inlineStr">
         <is>
           <t>人日／月</t>
         </is>
       </c>
-      <c r="C16" s="28">
+      <c r="C16" s="27">
         <f>ROUND(C14*C15,1)</f>
         <v/>
       </c>
-      <c r="D16" s="28">
+      <c r="D16" s="27">
         <f>ROUND(D14*D15,1)</f>
         <v/>
       </c>
-      <c r="E16" s="28">
+      <c r="E16" s="27">
         <f>ROUND(E14*E15,1)</f>
         <v/>
       </c>
-      <c r="F16" s="28">
+      <c r="F16" s="27">
         <f>ROUND(F14*F15,1)</f>
         <v/>
       </c>
@@ -7453,7 +7456,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="29" t="inlineStr">
+      <c r="A18" s="28" t="inlineStr">
         <is>
           <t>2　放課後等デイサービス</t>
         </is>
@@ -7515,18 +7518,18 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C21" s="19" t="n">
+      <c r="C21" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="D21" s="20">
+      <c r="D21" s="19">
         <f>C27</f>
         <v/>
       </c>
-      <c r="E21" s="20">
+      <c r="E21" s="19">
         <f>D27</f>
         <v/>
       </c>
-      <c r="F21" s="20">
+      <c r="F21" s="19">
         <f>E27</f>
         <v/>
       </c>
@@ -7547,10 +7550,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C22" s="21" t="n"/>
-      <c r="D22" s="19" t="n"/>
-      <c r="E22" s="19" t="n"/>
-      <c r="F22" s="19" t="n"/>
+      <c r="C22" s="20" t="n"/>
+      <c r="D22" s="18" t="n"/>
+      <c r="E22" s="18" t="n"/>
+      <c r="F22" s="18" t="n"/>
       <c r="G22" s="4" t="inlineStr">
         <is>
           <t>新規の発達相談・診断からの流入</t>
@@ -7568,10 +7571,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C23" s="21" t="n"/>
-      <c r="D23" s="19" t="n"/>
-      <c r="E23" s="19" t="n"/>
-      <c r="F23" s="19" t="n"/>
+      <c r="C23" s="20" t="n"/>
+      <c r="D23" s="18" t="n"/>
+      <c r="E23" s="18" t="n"/>
+      <c r="F23" s="18" t="n"/>
       <c r="G23" s="4" t="inlineStr">
         <is>
           <t>児童発達支援から放課後等デイサービスへの移行等</t>
@@ -7589,10 +7592,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C24" s="22" t="n"/>
-      <c r="D24" s="23" t="n"/>
-      <c r="E24" s="23" t="n"/>
-      <c r="F24" s="23" t="n"/>
+      <c r="C24" s="21" t="n"/>
+      <c r="D24" s="22" t="n"/>
+      <c r="E24" s="22" t="n"/>
+      <c r="F24" s="22" t="n"/>
       <c r="G24" s="4" t="inlineStr">
         <is>
           <t>児童発達支援からの流出</t>
@@ -7610,10 +7613,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C25" s="22" t="n"/>
-      <c r="D25" s="23" t="n"/>
-      <c r="E25" s="23" t="n"/>
-      <c r="F25" s="23" t="n"/>
+      <c r="C25" s="21" t="n"/>
+      <c r="D25" s="22" t="n"/>
+      <c r="E25" s="22" t="n"/>
+      <c r="F25" s="22" t="n"/>
       <c r="G25" s="4" t="inlineStr">
         <is>
           <t>成人の障害福祉サービスへ。03の流入と一致させる</t>
@@ -7631,36 +7634,36 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C26" s="22" t="n"/>
-      <c r="D26" s="23" t="n"/>
-      <c r="E26" s="23" t="n"/>
-      <c r="F26" s="23" t="n"/>
+      <c r="C26" s="21" t="n"/>
+      <c r="D26" s="22" t="n"/>
+      <c r="E26" s="22" t="n"/>
+      <c r="F26" s="22" t="n"/>
       <c r="G26" s="4" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="24" t="inlineStr">
+      <c r="A27" s="23" t="inlineStr">
         <is>
           <t>＝　利用者数</t>
         </is>
       </c>
-      <c r="B27" s="25" t="inlineStr">
-        <is>
-          <t>人／月</t>
-        </is>
-      </c>
-      <c r="C27" s="26">
+      <c r="B27" s="24" t="inlineStr">
+        <is>
+          <t>人／月</t>
+        </is>
+      </c>
+      <c r="C27" s="25">
         <f>C21</f>
         <v/>
       </c>
-      <c r="D27" s="26">
+      <c r="D27" s="25">
         <f>D21+SUM(D22:D23)-SUM(D24:D26)</f>
         <v/>
       </c>
-      <c r="E27" s="26">
+      <c r="E27" s="25">
         <f>E21+SUM(E22:E23)-SUM(E24:E26)</f>
         <v/>
       </c>
-      <c r="F27" s="26">
+      <c r="F27" s="25">
         <f>F21+SUM(F22:F23)-SUM(F24:F26)</f>
         <v/>
       </c>
@@ -7681,16 +7684,16 @@
           <t>人日／月</t>
         </is>
       </c>
-      <c r="C28" s="27" t="n">
+      <c r="C28" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="D28" s="27" t="n">
+      <c r="D28" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="E28" s="27" t="n">
+      <c r="E28" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="F28" s="27" t="n">
+      <c r="F28" s="26" t="n">
         <v>2</v>
       </c>
       <c r="G28" s="4" t="inlineStr">
@@ -7700,29 +7703,29 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="24" t="inlineStr">
+      <c r="A29" s="23" t="inlineStr">
         <is>
           <t>＝　月間サービス量</t>
         </is>
       </c>
-      <c r="B29" s="25" t="inlineStr">
+      <c r="B29" s="24" t="inlineStr">
         <is>
           <t>人日／月</t>
         </is>
       </c>
-      <c r="C29" s="28">
+      <c r="C29" s="27">
         <f>ROUND(C27*C28,1)</f>
         <v/>
       </c>
-      <c r="D29" s="28">
+      <c r="D29" s="27">
         <f>ROUND(D27*D28,1)</f>
         <v/>
       </c>
-      <c r="E29" s="28">
+      <c r="E29" s="27">
         <f>ROUND(E27*E28,1)</f>
         <v/>
       </c>
-      <c r="F29" s="28">
+      <c r="F29" s="27">
         <f>ROUND(F27*F28,1)</f>
         <v/>
       </c>
@@ -7733,7 +7736,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="29" t="inlineStr">
+      <c r="A31" s="28" t="inlineStr">
         <is>
           <t>3　保育所等訪問支援</t>
         </is>
@@ -7795,18 +7798,18 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C34" s="19" t="n">
+      <c r="C34" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="D34" s="20">
+      <c r="D34" s="19">
         <f>C40</f>
         <v/>
       </c>
-      <c r="E34" s="20">
+      <c r="E34" s="19">
         <f>D40</f>
         <v/>
       </c>
-      <c r="F34" s="20">
+      <c r="F34" s="19">
         <f>E40</f>
         <v/>
       </c>
@@ -7827,10 +7830,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C35" s="21" t="n"/>
-      <c r="D35" s="19" t="n"/>
-      <c r="E35" s="19" t="n"/>
-      <c r="F35" s="19" t="n"/>
+      <c r="C35" s="20" t="n"/>
+      <c r="D35" s="18" t="n"/>
+      <c r="E35" s="18" t="n"/>
+      <c r="F35" s="18" t="n"/>
       <c r="G35" s="4" t="inlineStr">
         <is>
           <t>新規の発達相談・診断からの流入</t>
@@ -7848,10 +7851,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C36" s="21" t="n"/>
-      <c r="D36" s="19" t="n"/>
-      <c r="E36" s="19" t="n"/>
-      <c r="F36" s="19" t="n"/>
+      <c r="C36" s="20" t="n"/>
+      <c r="D36" s="18" t="n"/>
+      <c r="E36" s="18" t="n"/>
+      <c r="F36" s="18" t="n"/>
       <c r="G36" s="4" t="inlineStr">
         <is>
           <t>児童発達支援から放課後等デイサービスへの移行等</t>
@@ -7869,10 +7872,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C37" s="22" t="n"/>
-      <c r="D37" s="23" t="n"/>
-      <c r="E37" s="23" t="n"/>
-      <c r="F37" s="23" t="n"/>
+      <c r="C37" s="21" t="n"/>
+      <c r="D37" s="22" t="n"/>
+      <c r="E37" s="22" t="n"/>
+      <c r="F37" s="22" t="n"/>
       <c r="G37" s="4" t="inlineStr">
         <is>
           <t>児童発達支援からの流出</t>
@@ -7890,10 +7893,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C38" s="22" t="n"/>
-      <c r="D38" s="23" t="n"/>
-      <c r="E38" s="23" t="n"/>
-      <c r="F38" s="23" t="n"/>
+      <c r="C38" s="21" t="n"/>
+      <c r="D38" s="22" t="n"/>
+      <c r="E38" s="22" t="n"/>
+      <c r="F38" s="22" t="n"/>
       <c r="G38" s="4" t="inlineStr">
         <is>
           <t>成人の障害福祉サービスへ。03の流入と一致させる</t>
@@ -7911,36 +7914,36 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C39" s="22" t="n"/>
-      <c r="D39" s="23" t="n"/>
-      <c r="E39" s="23" t="n"/>
-      <c r="F39" s="23" t="n"/>
+      <c r="C39" s="21" t="n"/>
+      <c r="D39" s="22" t="n"/>
+      <c r="E39" s="22" t="n"/>
+      <c r="F39" s="22" t="n"/>
       <c r="G39" s="4" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="24" t="inlineStr">
+      <c r="A40" s="23" t="inlineStr">
         <is>
           <t>＝　利用者数</t>
         </is>
       </c>
-      <c r="B40" s="25" t="inlineStr">
-        <is>
-          <t>人／月</t>
-        </is>
-      </c>
-      <c r="C40" s="26">
+      <c r="B40" s="24" t="inlineStr">
+        <is>
+          <t>人／月</t>
+        </is>
+      </c>
+      <c r="C40" s="25">
         <f>C34</f>
         <v/>
       </c>
-      <c r="D40" s="26">
+      <c r="D40" s="25">
         <f>D34+SUM(D35:D36)-SUM(D37:D39)</f>
         <v/>
       </c>
-      <c r="E40" s="26">
+      <c r="E40" s="25">
         <f>E34+SUM(E35:E36)-SUM(E37:E39)</f>
         <v/>
       </c>
-      <c r="F40" s="26">
+      <c r="F40" s="25">
         <f>F34+SUM(F35:F36)-SUM(F37:F39)</f>
         <v/>
       </c>
@@ -7961,10 +7964,10 @@
           <t>―</t>
         </is>
       </c>
-      <c r="C41" s="27" t="n"/>
-      <c r="D41" s="27" t="n"/>
-      <c r="E41" s="27" t="n"/>
-      <c r="F41" s="27" t="n"/>
+      <c r="C41" s="26" t="n"/>
+      <c r="D41" s="26" t="n"/>
+      <c r="E41" s="26" t="n"/>
+      <c r="F41" s="26" t="n"/>
       <c r="G41" s="4" t="inlineStr">
         <is>
           <t>利用者ごとの月間予定量の平均</t>
@@ -7972,29 +7975,29 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="24" t="inlineStr">
+      <c r="A42" s="23" t="inlineStr">
         <is>
           <t>＝　月間サービス量</t>
         </is>
       </c>
-      <c r="B42" s="25" t="inlineStr">
+      <c r="B42" s="24" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="C42" s="28">
+      <c r="C42" s="27">
         <f>ROUND(C40*C41,1)</f>
         <v/>
       </c>
-      <c r="D42" s="28">
+      <c r="D42" s="27">
         <f>ROUND(D40*D41,1)</f>
         <v/>
       </c>
-      <c r="E42" s="28">
+      <c r="E42" s="27">
         <f>ROUND(E40*E41,1)</f>
         <v/>
       </c>
-      <c r="F42" s="28">
+      <c r="F42" s="27">
         <f>ROUND(F40*F41,1)</f>
         <v/>
       </c>
@@ -8005,7 +8008,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="29" t="inlineStr">
+      <c r="A44" s="28" t="inlineStr">
         <is>
           <t>4　居宅訪問型児童発達支援</t>
         </is>
@@ -8067,18 +8070,18 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C47" s="19" t="n">
+      <c r="C47" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="D47" s="20">
+      <c r="D47" s="19">
         <f>C53</f>
         <v/>
       </c>
-      <c r="E47" s="20">
+      <c r="E47" s="19">
         <f>D53</f>
         <v/>
       </c>
-      <c r="F47" s="20">
+      <c r="F47" s="19">
         <f>E53</f>
         <v/>
       </c>
@@ -8099,10 +8102,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C48" s="21" t="n"/>
-      <c r="D48" s="19" t="n"/>
-      <c r="E48" s="19" t="n"/>
-      <c r="F48" s="19" t="n"/>
+      <c r="C48" s="20" t="n"/>
+      <c r="D48" s="18" t="n"/>
+      <c r="E48" s="18" t="n"/>
+      <c r="F48" s="18" t="n"/>
       <c r="G48" s="4" t="inlineStr">
         <is>
           <t>新規の発達相談・診断からの流入</t>
@@ -8120,10 +8123,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C49" s="21" t="n"/>
-      <c r="D49" s="19" t="n"/>
-      <c r="E49" s="19" t="n"/>
-      <c r="F49" s="19" t="n"/>
+      <c r="C49" s="20" t="n"/>
+      <c r="D49" s="18" t="n"/>
+      <c r="E49" s="18" t="n"/>
+      <c r="F49" s="18" t="n"/>
       <c r="G49" s="4" t="inlineStr">
         <is>
           <t>児童発達支援から放課後等デイサービスへの移行等</t>
@@ -8141,10 +8144,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C50" s="22" t="n"/>
-      <c r="D50" s="23" t="n"/>
-      <c r="E50" s="23" t="n"/>
-      <c r="F50" s="23" t="n"/>
+      <c r="C50" s="21" t="n"/>
+      <c r="D50" s="22" t="n"/>
+      <c r="E50" s="22" t="n"/>
+      <c r="F50" s="22" t="n"/>
       <c r="G50" s="4" t="inlineStr">
         <is>
           <t>児童発達支援からの流出</t>
@@ -8162,10 +8165,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C51" s="22" t="n"/>
-      <c r="D51" s="23" t="n"/>
-      <c r="E51" s="23" t="n"/>
-      <c r="F51" s="23" t="n"/>
+      <c r="C51" s="21" t="n"/>
+      <c r="D51" s="22" t="n"/>
+      <c r="E51" s="22" t="n"/>
+      <c r="F51" s="22" t="n"/>
       <c r="G51" s="4" t="inlineStr">
         <is>
           <t>成人の障害福祉サービスへ。03の流入と一致させる</t>
@@ -8183,36 +8186,36 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C52" s="22" t="n"/>
-      <c r="D52" s="23" t="n"/>
-      <c r="E52" s="23" t="n"/>
-      <c r="F52" s="23" t="n"/>
+      <c r="C52" s="21" t="n"/>
+      <c r="D52" s="22" t="n"/>
+      <c r="E52" s="22" t="n"/>
+      <c r="F52" s="22" t="n"/>
       <c r="G52" s="4" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="24" t="inlineStr">
+      <c r="A53" s="23" t="inlineStr">
         <is>
           <t>＝　利用者数</t>
         </is>
       </c>
-      <c r="B53" s="25" t="inlineStr">
-        <is>
-          <t>人／月</t>
-        </is>
-      </c>
-      <c r="C53" s="26">
+      <c r="B53" s="24" t="inlineStr">
+        <is>
+          <t>人／月</t>
+        </is>
+      </c>
+      <c r="C53" s="25">
         <f>C47</f>
         <v/>
       </c>
-      <c r="D53" s="26">
+      <c r="D53" s="25">
         <f>D47+SUM(D48:D49)-SUM(D50:D52)</f>
         <v/>
       </c>
-      <c r="E53" s="26">
+      <c r="E53" s="25">
         <f>E47+SUM(E48:E49)-SUM(E50:E52)</f>
         <v/>
       </c>
-      <c r="F53" s="26">
+      <c r="F53" s="25">
         <f>F47+SUM(F48:F49)-SUM(F50:F52)</f>
         <v/>
       </c>
@@ -8233,10 +8236,10 @@
           <t>―</t>
         </is>
       </c>
-      <c r="C54" s="27" t="n"/>
-      <c r="D54" s="27" t="n"/>
-      <c r="E54" s="27" t="n"/>
-      <c r="F54" s="27" t="n"/>
+      <c r="C54" s="26" t="n"/>
+      <c r="D54" s="26" t="n"/>
+      <c r="E54" s="26" t="n"/>
+      <c r="F54" s="26" t="n"/>
       <c r="G54" s="4" t="inlineStr">
         <is>
           <t>利用者ごとの月間予定量の平均</t>
@@ -8244,29 +8247,29 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="24" t="inlineStr">
+      <c r="A55" s="23" t="inlineStr">
         <is>
           <t>＝　月間サービス量</t>
         </is>
       </c>
-      <c r="B55" s="25" t="inlineStr">
+      <c r="B55" s="24" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="C55" s="28">
+      <c r="C55" s="27">
         <f>ROUND(C53*C54,1)</f>
         <v/>
       </c>
-      <c r="D55" s="28">
+      <c r="D55" s="27">
         <f>ROUND(D53*D54,1)</f>
         <v/>
       </c>
-      <c r="E55" s="28">
+      <c r="E55" s="27">
         <f>ROUND(E53*E54,1)</f>
         <v/>
       </c>
-      <c r="F55" s="28">
+      <c r="F55" s="27">
         <f>ROUND(F53*F54,1)</f>
         <v/>
       </c>
@@ -8277,7 +8280,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="29" t="inlineStr">
+      <c r="A57" s="28" t="inlineStr">
         <is>
           <t>5　医療型児童発達支援</t>
         </is>
@@ -8339,18 +8342,18 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C60" s="19" t="n">
+      <c r="C60" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="D60" s="20">
+      <c r="D60" s="19">
         <f>C66</f>
         <v/>
       </c>
-      <c r="E60" s="20">
+      <c r="E60" s="19">
         <f>D66</f>
         <v/>
       </c>
-      <c r="F60" s="20">
+      <c r="F60" s="19">
         <f>E66</f>
         <v/>
       </c>
@@ -8371,10 +8374,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C61" s="21" t="n"/>
-      <c r="D61" s="19" t="n"/>
-      <c r="E61" s="19" t="n"/>
-      <c r="F61" s="19" t="n"/>
+      <c r="C61" s="20" t="n"/>
+      <c r="D61" s="18" t="n"/>
+      <c r="E61" s="18" t="n"/>
+      <c r="F61" s="18" t="n"/>
       <c r="G61" s="4" t="inlineStr">
         <is>
           <t>新規の発達相談・診断からの流入</t>
@@ -8392,10 +8395,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C62" s="21" t="n"/>
-      <c r="D62" s="19" t="n"/>
-      <c r="E62" s="19" t="n"/>
-      <c r="F62" s="19" t="n"/>
+      <c r="C62" s="20" t="n"/>
+      <c r="D62" s="18" t="n"/>
+      <c r="E62" s="18" t="n"/>
+      <c r="F62" s="18" t="n"/>
       <c r="G62" s="4" t="inlineStr">
         <is>
           <t>児童発達支援から放課後等デイサービスへの移行等</t>
@@ -8413,10 +8416,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C63" s="22" t="n"/>
-      <c r="D63" s="23" t="n"/>
-      <c r="E63" s="23" t="n"/>
-      <c r="F63" s="23" t="n"/>
+      <c r="C63" s="21" t="n"/>
+      <c r="D63" s="22" t="n"/>
+      <c r="E63" s="22" t="n"/>
+      <c r="F63" s="22" t="n"/>
       <c r="G63" s="4" t="inlineStr">
         <is>
           <t>児童発達支援からの流出</t>
@@ -8434,10 +8437,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C64" s="22" t="n"/>
-      <c r="D64" s="23" t="n"/>
-      <c r="E64" s="23" t="n"/>
-      <c r="F64" s="23" t="n"/>
+      <c r="C64" s="21" t="n"/>
+      <c r="D64" s="22" t="n"/>
+      <c r="E64" s="22" t="n"/>
+      <c r="F64" s="22" t="n"/>
       <c r="G64" s="4" t="inlineStr">
         <is>
           <t>成人の障害福祉サービスへ。03の流入と一致させる</t>
@@ -8455,36 +8458,36 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C65" s="22" t="n"/>
-      <c r="D65" s="23" t="n"/>
-      <c r="E65" s="23" t="n"/>
-      <c r="F65" s="23" t="n"/>
+      <c r="C65" s="21" t="n"/>
+      <c r="D65" s="22" t="n"/>
+      <c r="E65" s="22" t="n"/>
+      <c r="F65" s="22" t="n"/>
       <c r="G65" s="4" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" s="24" t="inlineStr">
+      <c r="A66" s="23" t="inlineStr">
         <is>
           <t>＝　利用者数</t>
         </is>
       </c>
-      <c r="B66" s="25" t="inlineStr">
-        <is>
-          <t>人／月</t>
-        </is>
-      </c>
-      <c r="C66" s="26">
+      <c r="B66" s="24" t="inlineStr">
+        <is>
+          <t>人／月</t>
+        </is>
+      </c>
+      <c r="C66" s="25">
         <f>C60</f>
         <v/>
       </c>
-      <c r="D66" s="26">
+      <c r="D66" s="25">
         <f>D60+SUM(D61:D62)-SUM(D63:D65)</f>
         <v/>
       </c>
-      <c r="E66" s="26">
+      <c r="E66" s="25">
         <f>E60+SUM(E61:E62)-SUM(E63:E65)</f>
         <v/>
       </c>
-      <c r="F66" s="26">
+      <c r="F66" s="25">
         <f>F60+SUM(F61:F62)-SUM(F63:F65)</f>
         <v/>
       </c>
@@ -8505,10 +8508,10 @@
           <t>―</t>
         </is>
       </c>
-      <c r="C67" s="27" t="n"/>
-      <c r="D67" s="27" t="n"/>
-      <c r="E67" s="27" t="n"/>
-      <c r="F67" s="27" t="n"/>
+      <c r="C67" s="26" t="n"/>
+      <c r="D67" s="26" t="n"/>
+      <c r="E67" s="26" t="n"/>
+      <c r="F67" s="26" t="n"/>
       <c r="G67" s="4" t="inlineStr">
         <is>
           <t>利用者ごとの月間予定量の平均</t>
@@ -8516,29 +8519,29 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="24" t="inlineStr">
+      <c r="A68" s="23" t="inlineStr">
         <is>
           <t>＝　月間サービス量</t>
         </is>
       </c>
-      <c r="B68" s="25" t="inlineStr">
+      <c r="B68" s="24" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="C68" s="28">
+      <c r="C68" s="27">
         <f>ROUND(C66*C67,1)</f>
         <v/>
       </c>
-      <c r="D68" s="28">
+      <c r="D68" s="27">
         <f>ROUND(D66*D67,1)</f>
         <v/>
       </c>
-      <c r="E68" s="28">
+      <c r="E68" s="27">
         <f>ROUND(E66*E67,1)</f>
         <v/>
       </c>
-      <c r="F68" s="28">
+      <c r="F68" s="27">
         <f>ROUND(F66*F67,1)</f>
         <v/>
       </c>
@@ -8549,7 +8552,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="29" t="inlineStr">
+      <c r="A70" s="28" t="inlineStr">
         <is>
           <t>6　障がい児相談支援</t>
         </is>
@@ -8611,18 +8614,18 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C73" s="19" t="n">
+      <c r="C73" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="D73" s="20">
+      <c r="D73" s="19">
         <f>C79</f>
         <v/>
       </c>
-      <c r="E73" s="20">
+      <c r="E73" s="19">
         <f>D79</f>
         <v/>
       </c>
-      <c r="F73" s="20">
+      <c r="F73" s="19">
         <f>E79</f>
         <v/>
       </c>
@@ -8643,10 +8646,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C74" s="21" t="n"/>
-      <c r="D74" s="19" t="n"/>
-      <c r="E74" s="19" t="n"/>
-      <c r="F74" s="19" t="n"/>
+      <c r="C74" s="20" t="n"/>
+      <c r="D74" s="18" t="n"/>
+      <c r="E74" s="18" t="n"/>
+      <c r="F74" s="18" t="n"/>
       <c r="G74" s="4" t="inlineStr">
         <is>
           <t>新規の発達相談・診断からの流入</t>
@@ -8664,10 +8667,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C75" s="21" t="n"/>
-      <c r="D75" s="19" t="n"/>
-      <c r="E75" s="19" t="n"/>
-      <c r="F75" s="19" t="n"/>
+      <c r="C75" s="20" t="n"/>
+      <c r="D75" s="18" t="n"/>
+      <c r="E75" s="18" t="n"/>
+      <c r="F75" s="18" t="n"/>
       <c r="G75" s="4" t="inlineStr">
         <is>
           <t>児童発達支援から放課後等デイサービスへの移行等</t>
@@ -8685,10 +8688,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C76" s="22" t="n"/>
-      <c r="D76" s="23" t="n"/>
-      <c r="E76" s="23" t="n"/>
-      <c r="F76" s="23" t="n"/>
+      <c r="C76" s="21" t="n"/>
+      <c r="D76" s="22" t="n"/>
+      <c r="E76" s="22" t="n"/>
+      <c r="F76" s="22" t="n"/>
       <c r="G76" s="4" t="inlineStr">
         <is>
           <t>児童発達支援からの流出</t>
@@ -8706,10 +8709,10 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C77" s="22" t="n"/>
-      <c r="D77" s="23" t="n"/>
-      <c r="E77" s="23" t="n"/>
-      <c r="F77" s="23" t="n"/>
+      <c r="C77" s="21" t="n"/>
+      <c r="D77" s="22" t="n"/>
+      <c r="E77" s="22" t="n"/>
+      <c r="F77" s="22" t="n"/>
       <c r="G77" s="4" t="inlineStr">
         <is>
           <t>成人の障害福祉サービスへ。03の流入と一致させる</t>
@@ -8727,36 +8730,36 @@
           <t>人／月</t>
         </is>
       </c>
-      <c r="C78" s="22" t="n"/>
-      <c r="D78" s="23" t="n"/>
-      <c r="E78" s="23" t="n"/>
-      <c r="F78" s="23" t="n"/>
+      <c r="C78" s="21" t="n"/>
+      <c r="D78" s="22" t="n"/>
+      <c r="E78" s="22" t="n"/>
+      <c r="F78" s="22" t="n"/>
       <c r="G78" s="4" t="inlineStr"/>
     </row>
     <row r="79">
-      <c r="A79" s="24" t="inlineStr">
+      <c r="A79" s="23" t="inlineStr">
         <is>
           <t>＝　利用者数</t>
         </is>
       </c>
-      <c r="B79" s="25" t="inlineStr">
-        <is>
-          <t>人／月</t>
-        </is>
-      </c>
-      <c r="C79" s="26">
+      <c r="B79" s="24" t="inlineStr">
+        <is>
+          <t>人／月</t>
+        </is>
+      </c>
+      <c r="C79" s="25">
         <f>C73</f>
         <v/>
       </c>
-      <c r="D79" s="26">
+      <c r="D79" s="25">
         <f>D73+SUM(D74:D75)-SUM(D76:D78)</f>
         <v/>
       </c>
-      <c r="E79" s="26">
+      <c r="E79" s="25">
         <f>E73+SUM(E74:E75)-SUM(E76:E78)</f>
         <v/>
       </c>
-      <c r="F79" s="26">
+      <c r="F79" s="25">
         <f>F73+SUM(F74:F75)-SUM(F76:F78)</f>
         <v/>
       </c>
@@ -8777,10 +8780,10 @@
           <t>―</t>
         </is>
       </c>
-      <c r="C80" s="27" t="n"/>
-      <c r="D80" s="27" t="n"/>
-      <c r="E80" s="27" t="n"/>
-      <c r="F80" s="27" t="n"/>
+      <c r="C80" s="26" t="n"/>
+      <c r="D80" s="26" t="n"/>
+      <c r="E80" s="26" t="n"/>
+      <c r="F80" s="26" t="n"/>
       <c r="G80" s="4" t="inlineStr">
         <is>
           <t>利用者ごとの月間予定量の平均</t>
@@ -8788,29 +8791,29 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="24" t="inlineStr">
+      <c r="A81" s="23" t="inlineStr">
         <is>
           <t>＝　月間サービス量</t>
         </is>
       </c>
-      <c r="B81" s="25" t="inlineStr">
+      <c r="B81" s="24" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="C81" s="28">
+      <c r="C81" s="27">
         <f>ROUND(C79*C80,1)</f>
         <v/>
       </c>
-      <c r="D81" s="28">
+      <c r="D81" s="27">
         <f>ROUND(D79*D80,1)</f>
         <v/>
       </c>
-      <c r="E81" s="28">
+      <c r="E81" s="27">
         <f>ROUND(E79*E80,1)</f>
         <v/>
       </c>
-      <c r="F81" s="28">
+      <c r="F81" s="27">
         <f>ROUND(F79*F80,1)</f>
         <v/>
       </c>
@@ -8868,7 +8871,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>実績ゼロのサービスの確認</t>
         </is>
@@ -8925,13 +8928,13 @@
           <t>重度訪問介護</t>
         </is>
       </c>
-      <c r="B6" s="21" t="n">
+      <c r="B6" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="C6" s="19" t="n"/>
-      <c r="D6" s="19" t="n"/>
-      <c r="E6" s="19" t="n"/>
-      <c r="F6" s="16" t="n"/>
+      <c r="C6" s="18" t="n"/>
+      <c r="D6" s="18" t="n"/>
+      <c r="E6" s="18" t="n"/>
+      <c r="F6" s="15" t="n"/>
       <c r="G6" s="4" t="inlineStr">
         <is>
           <t>重度の肢体不自由者等。対象者の有無を個別に確認</t>
@@ -8944,13 +8947,13 @@
           <t>同行援護</t>
         </is>
       </c>
-      <c r="B7" s="30" t="n">
+      <c r="B7" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="C7" s="19" t="n"/>
-      <c r="D7" s="19" t="n"/>
-      <c r="E7" s="19" t="n"/>
-      <c r="F7" s="16" t="n"/>
+      <c r="C7" s="18" t="n"/>
+      <c r="D7" s="18" t="n"/>
+      <c r="E7" s="18" t="n"/>
+      <c r="F7" s="15" t="n"/>
       <c r="G7" s="6" t="inlineStr">
         <is>
           <t>視覚障がい者の外出支援。介護保険に相当サービスなし</t>
@@ -8963,13 +8966,13 @@
           <t>行動援護</t>
         </is>
       </c>
-      <c r="B8" s="21" t="n">
+      <c r="B8" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="C8" s="19" t="n"/>
-      <c r="D8" s="19" t="n"/>
-      <c r="E8" s="19" t="n"/>
-      <c r="F8" s="16" t="n"/>
+      <c r="C8" s="18" t="n"/>
+      <c r="D8" s="18" t="n"/>
+      <c r="E8" s="18" t="n"/>
+      <c r="F8" s="15" t="n"/>
       <c r="G8" s="4" t="inlineStr">
         <is>
           <t>強度行動障害等。介護保険に相当サービスなし</t>
@@ -8982,13 +8985,13 @@
           <t>重度障がい者等包括支援</t>
         </is>
       </c>
-      <c r="B9" s="30" t="n">
+      <c r="B9" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="C9" s="19" t="n"/>
-      <c r="D9" s="19" t="n"/>
-      <c r="E9" s="19" t="n"/>
-      <c r="F9" s="16" t="n"/>
+      <c r="C9" s="18" t="n"/>
+      <c r="D9" s="18" t="n"/>
+      <c r="E9" s="18" t="n"/>
+      <c r="F9" s="15" t="n"/>
       <c r="G9" s="6" t="inlineStr">
         <is>
           <t>最重度者向け。圏域の供給を確認</t>
@@ -9001,13 +9004,13 @@
           <t>療養介護</t>
         </is>
       </c>
-      <c r="B10" s="21" t="n">
+      <c r="B10" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="C10" s="19" t="n"/>
-      <c r="D10" s="19" t="n"/>
-      <c r="E10" s="19" t="n"/>
-      <c r="F10" s="16" t="n"/>
+      <c r="C10" s="18" t="n"/>
+      <c r="D10" s="18" t="n"/>
+      <c r="E10" s="18" t="n"/>
+      <c r="F10" s="15" t="n"/>
       <c r="G10" s="4" t="inlineStr">
         <is>
           <t>医療機関での長期療養。対象者の有無を確認</t>
@@ -9020,13 +9023,13 @@
           <t>自立訓練（機能訓練）</t>
         </is>
       </c>
-      <c r="B11" s="30" t="n">
+      <c r="B11" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="C11" s="19" t="n"/>
-      <c r="D11" s="19" t="n"/>
-      <c r="E11" s="19" t="n"/>
-      <c r="F11" s="16" t="n"/>
+      <c r="C11" s="18" t="n"/>
+      <c r="D11" s="18" t="n"/>
+      <c r="E11" s="18" t="n"/>
+      <c r="F11" s="15" t="n"/>
       <c r="G11" s="6" t="inlineStr">
         <is>
           <t>リハビリ需要は介護保険側に流れている可能性</t>
@@ -9039,13 +9042,13 @@
           <t>自立生活援助</t>
         </is>
       </c>
-      <c r="B12" s="21" t="n">
+      <c r="B12" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="C12" s="19" t="n"/>
-      <c r="D12" s="19" t="n"/>
-      <c r="E12" s="19" t="n"/>
-      <c r="F12" s="16" t="n"/>
+      <c r="C12" s="18" t="n"/>
+      <c r="D12" s="18" t="n"/>
+      <c r="E12" s="18" t="n"/>
+      <c r="F12" s="15" t="n"/>
       <c r="G12" s="4" t="inlineStr">
         <is>
           <t>一人暮らしへの移行支援。地域移行と連動</t>
@@ -9058,13 +9061,13 @@
           <t>地域移行支援</t>
         </is>
       </c>
-      <c r="B13" s="30" t="n">
+      <c r="B13" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="C13" s="19" t="n"/>
-      <c r="D13" s="19" t="n"/>
-      <c r="E13" s="19" t="n"/>
-      <c r="F13" s="16" t="n"/>
+      <c r="C13" s="18" t="n"/>
+      <c r="D13" s="18" t="n"/>
+      <c r="E13" s="18" t="n"/>
+      <c r="F13" s="15" t="n"/>
       <c r="G13" s="6" t="inlineStr">
         <is>
           <t>施設・精神科病院からの地域移行。成果目標（１）（２）と連動</t>
@@ -9077,13 +9080,13 @@
           <t>地域定着支援</t>
         </is>
       </c>
-      <c r="B14" s="21" t="n">
+      <c r="B14" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="C14" s="19" t="n"/>
-      <c r="D14" s="19" t="n"/>
-      <c r="E14" s="19" t="n"/>
-      <c r="F14" s="16" t="n"/>
+      <c r="C14" s="18" t="n"/>
+      <c r="D14" s="18" t="n"/>
+      <c r="E14" s="18" t="n"/>
+      <c r="F14" s="15" t="n"/>
       <c r="G14" s="4" t="inlineStr">
         <is>
           <t>単身生活者の緊急時対応。地域生活支援拠点と連動</t>
@@ -9124,7 +9127,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>65歳到達に伴う介護保険への移行判定</t>
         </is>
@@ -9138,7 +9141,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="10" t="inlineStr">
+      <c r="A5" s="9" t="inlineStr">
         <is>
           <t>1. サービス区分（制度整理・確定）</t>
         </is>
@@ -9173,7 +9176,7 @@
           <t>居宅介護</t>
         </is>
       </c>
-      <c r="B7" s="31" t="inlineStr">
+      <c r="B7" s="30" t="inlineStr">
         <is>
           <t>相当あり</t>
         </is>
@@ -9196,7 +9199,7 @@
           <t>生活介護</t>
         </is>
       </c>
-      <c r="B8" s="31" t="inlineStr">
+      <c r="B8" s="30" t="inlineStr">
         <is>
           <t>相当あり</t>
         </is>
@@ -9219,7 +9222,7 @@
           <t>短期入所</t>
         </is>
       </c>
-      <c r="B9" s="31" t="inlineStr">
+      <c r="B9" s="30" t="inlineStr">
         <is>
           <t>相当あり</t>
         </is>
@@ -9242,7 +9245,7 @@
           <t>自立訓練（機能訓練）</t>
         </is>
       </c>
-      <c r="B10" s="31" t="inlineStr">
+      <c r="B10" s="30" t="inlineStr">
         <is>
           <t>相当あり</t>
         </is>
@@ -9265,7 +9268,7 @@
           <t>共同生活援助</t>
         </is>
       </c>
-      <c r="B11" s="32" t="inlineStr">
+      <c r="B11" s="31" t="inlineStr">
         <is>
           <t>相当なし</t>
         </is>
@@ -9288,7 +9291,7 @@
           <t>施設入所支援</t>
         </is>
       </c>
-      <c r="B12" s="32" t="inlineStr">
+      <c r="B12" s="31" t="inlineStr">
         <is>
           <t>相当なし</t>
         </is>
@@ -9311,7 +9314,7 @@
           <t>就労移行支援</t>
         </is>
       </c>
-      <c r="B13" s="32" t="inlineStr">
+      <c r="B13" s="31" t="inlineStr">
         <is>
           <t>相当なし</t>
         </is>
@@ -9334,7 +9337,7 @@
           <t>就労継続支援A型・B型</t>
         </is>
       </c>
-      <c r="B14" s="32" t="inlineStr">
+      <c r="B14" s="31" t="inlineStr">
         <is>
           <t>相当なし</t>
         </is>
@@ -9357,7 +9360,7 @@
           <t>就労定着支援・就労選択支援</t>
         </is>
       </c>
-      <c r="B15" s="32" t="inlineStr">
+      <c r="B15" s="31" t="inlineStr">
         <is>
           <t>相当なし</t>
         </is>
@@ -9380,7 +9383,7 @@
           <t>同行援護・行動援護</t>
         </is>
       </c>
-      <c r="B16" s="32" t="inlineStr">
+      <c r="B16" s="31" t="inlineStr">
         <is>
           <t>相当なし</t>
         </is>
@@ -9426,7 +9429,7 @@
           <t>計画相談支援</t>
         </is>
       </c>
-      <c r="B18" s="31" t="inlineStr">
+      <c r="B18" s="30" t="inlineStr">
         <is>
           <t>相当あり</t>
         </is>
@@ -9444,7 +9447,7 @@
       <c r="E18" s="6" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="10" t="inlineStr">
+      <c r="A20" s="9" t="inlineStr">
         <is>
           <t>2. 到達者別の判定（入力）</t>
         </is>
@@ -9478,91 +9481,91 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="16" t="n"/>
-      <c r="B22" s="16" t="n"/>
-      <c r="C22" s="17" t="n"/>
-      <c r="D22" s="17" t="n"/>
-      <c r="E22" s="18" t="n"/>
+      <c r="A22" s="15" t="n"/>
+      <c r="B22" s="15" t="n"/>
+      <c r="C22" s="16" t="n"/>
+      <c r="D22" s="16" t="n"/>
+      <c r="E22" s="17" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="16" t="n"/>
-      <c r="B23" s="16" t="n"/>
-      <c r="C23" s="17" t="n"/>
-      <c r="D23" s="17" t="n"/>
-      <c r="E23" s="18" t="n"/>
+      <c r="A23" s="15" t="n"/>
+      <c r="B23" s="15" t="n"/>
+      <c r="C23" s="16" t="n"/>
+      <c r="D23" s="16" t="n"/>
+      <c r="E23" s="17" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="16" t="n"/>
-      <c r="B24" s="16" t="n"/>
-      <c r="C24" s="17" t="n"/>
-      <c r="D24" s="17" t="n"/>
-      <c r="E24" s="18" t="n"/>
+      <c r="A24" s="15" t="n"/>
+      <c r="B24" s="15" t="n"/>
+      <c r="C24" s="16" t="n"/>
+      <c r="D24" s="16" t="n"/>
+      <c r="E24" s="17" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="16" t="n"/>
-      <c r="B25" s="16" t="n"/>
-      <c r="C25" s="17" t="n"/>
-      <c r="D25" s="17" t="n"/>
-      <c r="E25" s="18" t="n"/>
+      <c r="A25" s="15" t="n"/>
+      <c r="B25" s="15" t="n"/>
+      <c r="C25" s="16" t="n"/>
+      <c r="D25" s="16" t="n"/>
+      <c r="E25" s="17" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="16" t="n"/>
-      <c r="B26" s="16" t="n"/>
-      <c r="C26" s="17" t="n"/>
-      <c r="D26" s="17" t="n"/>
-      <c r="E26" s="18" t="n"/>
+      <c r="A26" s="15" t="n"/>
+      <c r="B26" s="15" t="n"/>
+      <c r="C26" s="16" t="n"/>
+      <c r="D26" s="16" t="n"/>
+      <c r="E26" s="17" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="16" t="n"/>
-      <c r="B27" s="16" t="n"/>
-      <c r="C27" s="17" t="n"/>
-      <c r="D27" s="17" t="n"/>
-      <c r="E27" s="18" t="n"/>
+      <c r="A27" s="15" t="n"/>
+      <c r="B27" s="15" t="n"/>
+      <c r="C27" s="16" t="n"/>
+      <c r="D27" s="16" t="n"/>
+      <c r="E27" s="17" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="16" t="n"/>
-      <c r="B28" s="16" t="n"/>
-      <c r="C28" s="17" t="n"/>
-      <c r="D28" s="17" t="n"/>
-      <c r="E28" s="18" t="n"/>
+      <c r="A28" s="15" t="n"/>
+      <c r="B28" s="15" t="n"/>
+      <c r="C28" s="16" t="n"/>
+      <c r="D28" s="16" t="n"/>
+      <c r="E28" s="17" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="16" t="n"/>
-      <c r="B29" s="16" t="n"/>
-      <c r="C29" s="17" t="n"/>
-      <c r="D29" s="17" t="n"/>
-      <c r="E29" s="18" t="n"/>
+      <c r="A29" s="15" t="n"/>
+      <c r="B29" s="15" t="n"/>
+      <c r="C29" s="16" t="n"/>
+      <c r="D29" s="16" t="n"/>
+      <c r="E29" s="17" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="16" t="n"/>
-      <c r="B30" s="16" t="n"/>
-      <c r="C30" s="17" t="n"/>
-      <c r="D30" s="17" t="n"/>
-      <c r="E30" s="18" t="n"/>
+      <c r="A30" s="15" t="n"/>
+      <c r="B30" s="15" t="n"/>
+      <c r="C30" s="16" t="n"/>
+      <c r="D30" s="16" t="n"/>
+      <c r="E30" s="17" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="16" t="n"/>
-      <c r="B31" s="16" t="n"/>
-      <c r="C31" s="17" t="n"/>
-      <c r="D31" s="17" t="n"/>
-      <c r="E31" s="18" t="n"/>
+      <c r="A31" s="15" t="n"/>
+      <c r="B31" s="15" t="n"/>
+      <c r="C31" s="16" t="n"/>
+      <c r="D31" s="16" t="n"/>
+      <c r="E31" s="17" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="16" t="n"/>
-      <c r="B32" s="16" t="n"/>
-      <c r="C32" s="17" t="n"/>
-      <c r="D32" s="17" t="n"/>
-      <c r="E32" s="18" t="n"/>
+      <c r="A32" s="15" t="n"/>
+      <c r="B32" s="15" t="n"/>
+      <c r="C32" s="16" t="n"/>
+      <c r="D32" s="16" t="n"/>
+      <c r="E32" s="17" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="16" t="n"/>
-      <c r="B33" s="16" t="n"/>
-      <c r="C33" s="17" t="n"/>
-      <c r="D33" s="17" t="n"/>
-      <c r="E33" s="18" t="n"/>
+      <c r="A33" s="15" t="n"/>
+      <c r="B33" s="15" t="n"/>
+      <c r="C33" s="16" t="n"/>
+      <c r="D33" s="16" t="n"/>
+      <c r="E33" s="17" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="10" t="inlineStr">
+      <c r="A35" s="9" t="inlineStr">
         <is>
           <t>3. 判定にあたって確認する事項</t>
         </is>
@@ -9594,9 +9597,9 @@
           <t>支援内容・時間・専門性が介護保険サービスで代替できるか。代替できない場合は障害福祉を継続する</t>
         </is>
       </c>
-      <c r="C37" s="33" t="n"/>
-      <c r="D37" s="33" t="n"/>
-      <c r="E37" s="34" t="n"/>
+      <c r="C37" s="32" t="n"/>
+      <c r="D37" s="32" t="n"/>
+      <c r="E37" s="33" t="n"/>
     </row>
     <row r="38" ht="40" customHeight="1">
       <c r="A38" s="6" t="inlineStr">
@@ -9609,9 +9612,9 @@
           <t>村内に事業所がないため、圏域の介護保険事業所が受け入れ可能かを確認する。共生型サービスの指定を受けている事業所があれば、同一事業所での継続利用が可能</t>
         </is>
       </c>
-      <c r="C38" s="33" t="n"/>
-      <c r="D38" s="33" t="n"/>
-      <c r="E38" s="34" t="n"/>
+      <c r="C38" s="32" t="n"/>
+      <c r="D38" s="32" t="n"/>
+      <c r="E38" s="33" t="n"/>
     </row>
     <row r="39" ht="40" customHeight="1">
       <c r="A39" s="4" t="inlineStr">
@@ -9624,9 +9627,9 @@
           <t>①65歳に達する日前5年間の支給決定 ②65歳に達する日の前日の属する年度の市町村民税非課税または生活保護 ③65歳に達する日の前日に障害支援区分2以上 ④65歳まで介護保険サービス未利用。該当すれば介護保険移行後の利用者負担が償還される</t>
         </is>
       </c>
-      <c r="C39" s="33" t="n"/>
-      <c r="D39" s="33" t="n"/>
-      <c r="E39" s="34" t="n"/>
+      <c r="C39" s="32" t="n"/>
+      <c r="D39" s="32" t="n"/>
+      <c r="E39" s="33" t="n"/>
     </row>
     <row r="40" ht="40" customHeight="1">
       <c r="A40" s="6" t="inlineStr">
@@ -9639,9 +9642,9 @@
           <t>介護保険の支給限度基準額では必要量に満たない場合、不足分を障害福祉サービスで上乗せできる。この場合は障害福祉の見込量から全額を減らさない</t>
         </is>
       </c>
-      <c r="C40" s="33" t="n"/>
-      <c r="D40" s="33" t="n"/>
-      <c r="E40" s="34" t="n"/>
+      <c r="C40" s="32" t="n"/>
+      <c r="D40" s="32" t="n"/>
+      <c r="E40" s="33" t="n"/>
     </row>
     <row r="41" ht="40" customHeight="1">
       <c r="A41" s="4" t="inlineStr">
@@ -9654,9 +9657,9 @@
           <t>本人・家族の意向を聴取したうえで支給決定を行う</t>
         </is>
       </c>
-      <c r="C41" s="33" t="n"/>
-      <c r="D41" s="33" t="n"/>
-      <c r="E41" s="34" t="n"/>
+      <c r="C41" s="32" t="n"/>
+      <c r="D41" s="32" t="n"/>
+      <c r="E41" s="33" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -9694,7 +9697,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>未特定の潜在需要（第3層）</t>
         </is>
@@ -9755,9 +9758,9 @@
           <t>全サービス</t>
         </is>
       </c>
-      <c r="C6" s="27" t="n"/>
-      <c r="D6" s="27" t="n"/>
-      <c r="E6" s="27" t="n"/>
+      <c r="C6" s="26" t="n"/>
+      <c r="D6" s="26" t="n"/>
+      <c r="E6" s="26" t="n"/>
       <c r="F6" s="4" t="inlineStr">
         <is>
           <t>アンケート問29-2・問33</t>
@@ -9780,9 +9783,9 @@
           <t>計画相談支援、各サービス</t>
         </is>
       </c>
-      <c r="C7" s="27" t="n"/>
-      <c r="D7" s="27" t="n"/>
-      <c r="E7" s="27" t="n"/>
+      <c r="C7" s="26" t="n"/>
+      <c r="D7" s="26" t="n"/>
+      <c r="E7" s="26" t="n"/>
       <c r="F7" s="6" t="inlineStr">
         <is>
           <t>相談実績（村資料待ち）</t>
@@ -9805,9 +9808,9 @@
           <t>移動支援、日中一時支援等</t>
         </is>
       </c>
-      <c r="C8" s="27" t="n"/>
-      <c r="D8" s="27" t="n"/>
-      <c r="E8" s="27" t="n"/>
+      <c r="C8" s="26" t="n"/>
+      <c r="D8" s="26" t="n"/>
+      <c r="E8" s="26" t="n"/>
       <c r="F8" s="4" t="inlineStr">
         <is>
           <t>アンケート自由記述</t>
@@ -9830,9 +9833,9 @@
           <t>障害児通所支援、精神関係</t>
         </is>
       </c>
-      <c r="C9" s="27" t="n"/>
-      <c r="D9" s="27" t="n"/>
-      <c r="E9" s="27" t="n"/>
+      <c r="C9" s="26" t="n"/>
+      <c r="D9" s="26" t="n"/>
+      <c r="E9" s="26" t="n"/>
       <c r="F9" s="6" t="inlineStr">
         <is>
           <t>手帳交付実績（村資料待ち）</t>
@@ -9855,9 +9858,9 @@
           <t>全サービス</t>
         </is>
       </c>
-      <c r="C10" s="27" t="n"/>
-      <c r="D10" s="27" t="n"/>
-      <c r="E10" s="27" t="n"/>
+      <c r="C10" s="26" t="n"/>
+      <c r="D10" s="26" t="n"/>
+      <c r="E10" s="26" t="n"/>
       <c r="F10" s="4" t="inlineStr">
         <is>
           <t>圏域4町村の協議</t>
@@ -9880,9 +9883,9 @@
           <t>短期入所、共同生活援助、施設入所支援</t>
         </is>
       </c>
-      <c r="C11" s="27" t="n"/>
-      <c r="D11" s="27" t="n"/>
-      <c r="E11" s="27" t="n"/>
+      <c r="C11" s="26" t="n"/>
+      <c r="D11" s="26" t="n"/>
+      <c r="E11" s="26" t="n"/>
       <c r="F11" s="6" t="inlineStr">
         <is>
           <t>アンケート問8〜問11</t>
@@ -9930,7 +9933,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>供給制約（利用希望量と利用可能量の分離）</t>
         </is>
@@ -9992,10 +9995,10 @@
           <t>圏域（喜多方市・会津若松市等）</t>
         </is>
       </c>
-      <c r="C6" s="19" t="n"/>
-      <c r="D6" s="19" t="n"/>
-      <c r="E6" s="16" t="n"/>
-      <c r="F6" s="16" t="n"/>
+      <c r="C6" s="18" t="n"/>
+      <c r="D6" s="18" t="n"/>
+      <c r="E6" s="15" t="n"/>
+      <c r="F6" s="15" t="n"/>
       <c r="G6" s="4" t="inlineStr">
         <is>
           <t>特別支援学校卒業者の受入枠。送迎範囲に北塩原村が含まれるか</t>
@@ -10013,10 +10016,10 @@
           <t>喜多方市・会津若松市等</t>
         </is>
       </c>
-      <c r="C7" s="19" t="n"/>
-      <c r="D7" s="19" t="n"/>
-      <c r="E7" s="16" t="n"/>
-      <c r="F7" s="16" t="n"/>
+      <c r="C7" s="18" t="n"/>
+      <c r="D7" s="18" t="n"/>
+      <c r="E7" s="15" t="n"/>
+      <c r="F7" s="15" t="n"/>
       <c r="G7" s="6" t="inlineStr">
         <is>
           <t>給付費が令和2年度比2.08倍。定員に対する余力を確認</t>
@@ -10034,10 +10037,10 @@
           <t>圏域（協議会設置圏域ごとに設置）</t>
         </is>
       </c>
-      <c r="C8" s="19" t="n"/>
-      <c r="D8" s="19" t="n"/>
-      <c r="E8" s="16" t="n"/>
-      <c r="F8" s="16" t="n"/>
+      <c r="C8" s="18" t="n"/>
+      <c r="D8" s="18" t="n"/>
+      <c r="E8" s="15" t="n"/>
+      <c r="F8" s="15" t="n"/>
       <c r="G8" s="4" t="inlineStr">
         <is>
           <t>圏域内に事業所があるか。ない場合の確保方策</t>
@@ -10055,10 +10058,10 @@
           <t>圏域</t>
         </is>
       </c>
-      <c r="C9" s="19" t="n"/>
-      <c r="D9" s="19" t="n"/>
-      <c r="E9" s="16" t="n"/>
-      <c r="F9" s="16" t="n"/>
+      <c r="C9" s="18" t="n"/>
+      <c r="D9" s="18" t="n"/>
+      <c r="E9" s="15" t="n"/>
+      <c r="F9" s="15" t="n"/>
       <c r="G9" s="6" t="inlineStr">
         <is>
           <t>空室の有無。親亡き後の受入余力</t>
@@ -10076,10 +10079,10 @@
           <t>圏域</t>
         </is>
       </c>
-      <c r="C10" s="19" t="n"/>
-      <c r="D10" s="19" t="n"/>
-      <c r="E10" s="16" t="n"/>
-      <c r="F10" s="16" t="n"/>
+      <c r="C10" s="18" t="n"/>
+      <c r="D10" s="18" t="n"/>
+      <c r="E10" s="15" t="n"/>
+      <c r="F10" s="15" t="n"/>
       <c r="G10" s="4" t="inlineStr">
         <is>
           <t>緊急時の受入可否。地域生活支援拠点と連動</t>
@@ -10097,10 +10100,10 @@
           <t>圏域</t>
         </is>
       </c>
-      <c r="C11" s="19" t="n"/>
-      <c r="D11" s="19" t="n"/>
-      <c r="E11" s="16" t="n"/>
-      <c r="F11" s="16" t="n"/>
+      <c r="C11" s="18" t="n"/>
+      <c r="D11" s="18" t="n"/>
+      <c r="E11" s="15" t="n"/>
+      <c r="F11" s="15" t="n"/>
       <c r="G11" s="6" t="inlineStr">
         <is>
           <t>訪問可能地区。冬季の提供体制</t>
@@ -10118,10 +10121,10 @@
           <t>猪苗代町・喜多方市等</t>
         </is>
       </c>
-      <c r="C12" s="19" t="n"/>
-      <c r="D12" s="19" t="n"/>
-      <c r="E12" s="16" t="n"/>
-      <c r="F12" s="16" t="n"/>
+      <c r="C12" s="18" t="n"/>
+      <c r="D12" s="18" t="n"/>
+      <c r="E12" s="15" t="n"/>
+      <c r="F12" s="15" t="n"/>
       <c r="G12" s="4" t="inlineStr">
         <is>
           <t>相談支援専門員の担当可能件数。セルフプラン解消の可否</t>
@@ -10139,10 +10142,10 @@
           <t>圏域（村内0か所）</t>
         </is>
       </c>
-      <c r="C13" s="19" t="n"/>
-      <c r="D13" s="19" t="n"/>
-      <c r="E13" s="16" t="n"/>
-      <c r="F13" s="16" t="n"/>
+      <c r="C13" s="18" t="n"/>
+      <c r="D13" s="18" t="n"/>
+      <c r="E13" s="15" t="n"/>
+      <c r="F13" s="15" t="n"/>
       <c r="G13" s="6" t="inlineStr">
         <is>
           <t>通所距離と保護者の送迎負担</t>
@@ -10160,10 +10163,10 @@
           <t>圏域</t>
         </is>
       </c>
-      <c r="C14" s="19" t="n"/>
-      <c r="D14" s="19" t="n"/>
-      <c r="E14" s="16" t="n"/>
-      <c r="F14" s="16" t="n"/>
+      <c r="C14" s="18" t="n"/>
+      <c r="D14" s="18" t="n"/>
+      <c r="E14" s="15" t="n"/>
+      <c r="F14" s="15" t="n"/>
       <c r="G14" s="4" t="inlineStr">
         <is>
           <t>長期休暇中の受入。送迎</t>
@@ -10181,10 +10184,10 @@
           <t>圏域</t>
         </is>
       </c>
-      <c r="C15" s="19" t="n"/>
-      <c r="D15" s="19" t="n"/>
-      <c r="E15" s="16" t="n"/>
-      <c r="F15" s="16" t="n"/>
+      <c r="C15" s="18" t="n"/>
+      <c r="D15" s="18" t="n"/>
+      <c r="E15" s="15" t="n"/>
+      <c r="F15" s="15" t="n"/>
       <c r="G15" s="6" t="inlineStr">
         <is>
           <t>訪問可能範囲</t>
@@ -10202,10 +10205,10 @@
           <t>圏域</t>
         </is>
       </c>
-      <c r="C16" s="19" t="n"/>
-      <c r="D16" s="19" t="n"/>
-      <c r="E16" s="16" t="n"/>
-      <c r="F16" s="16" t="n"/>
+      <c r="C16" s="18" t="n"/>
+      <c r="D16" s="18" t="n"/>
+      <c r="E16" s="15" t="n"/>
+      <c r="F16" s="15" t="n"/>
       <c r="G16" s="4" t="inlineStr">
         <is>
           <t>65歳移行後の受け皿。共生型サービスの指定を受けているか</t>

--- a/output/北塩原村_サービス見込量.xlsx
+++ b/output/北塩原村_サービス見込量.xlsx
@@ -2367,7 +2367,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -2521,15 +2521,22 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="34" customHeight="1">
+    <row r="18" ht="46" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>※ 別表第五が対象とするのは「特定障害福祉サービス」及び「特定障害児通所支援」であり、全サービスではない。該当サービスの範囲は障害者総合支援法第88条第10項及び児童福祉法第21条の5の15第2項の定義による。</t>
+          <t>※ 別表第五が対象とするのは「特定障害福祉サービス」及び「特定障害児通所支援」であり、全サービスではない。該当サービスの範囲は障害者総合支援法第88条第10項及び児童福祉法第21条の5の15第2項の定義による。「障害福祉計画策定に係る実態調査及びPDCAサイクルに関するマニュアル」（令和8年8月）P.22 は、対象を 生活介護、就労継続支援A型、就労継続支援B型、児童発達支援、放課後等デイサービス、共同生活援助 の6サービスと明示している。本村はこの6サービスすべてに実績がある。</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="60" customHeight="1">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>※ 上記マニュアル P.22 手順Ⅰは「要件1と要件2の両方に該当しない場合は、18ページの内容を参考として、サービスに必要な見込量を算出してください」としており、全部過疎市町村である本村が地域差是正の算定方法の対象外であることを確認できる。同 P.21 は、実績値が小さい場合は「実績値の変化により推計値の値が変化しやすい」、実績値が極端に増減している場合は「幾何平均による算出では2年後・3年後の推計値が過大（過少）に推計されてしまう可能性がある」と留意点を示しており、利用者が各サービス数人規模の本村で個別積上げ方式を採る根拠になる。原典は source/実態調査PDCAマニュアル/、確認結果は docs/北塩原村_実態調査PDCAマニュアル_確認結果.md。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A5:D5"/>
     <mergeCell ref="A9:D9"/>
@@ -2540,6 +2547,7 @@
     <mergeCell ref="A7:D7"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A19:D19"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
